--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,6 +2261,7167 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129670652</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>651866</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6626192</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129670602</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>651892</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6626058</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129670575</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>651902</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6626042</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129670653</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>651890</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6626144</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129670584</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>651906</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6626091</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129670611</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>651780</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6626166</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129670618</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>651850</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6626173</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129670655</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>651655</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6626179</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129670638</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>651788</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6626118</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129670656</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>651804</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6626213</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129670586</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92271</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>651896</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6626042</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129670612</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>651783</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6626160</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129670607</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>651794</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6626119</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129670588</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92271</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>651868</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6626205</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129670620</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>651894</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6626133</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129670577</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>651934</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6626035</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129670582</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>651839</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6626178</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129670625</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>651793</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6626135</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129670592</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>651842</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6626152</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129670657</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92206</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>651836</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6626075</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129670644</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>651725</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6626217</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129670651</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>651804</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6626204</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129670601</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>651723</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6626229</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129670585</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>651912</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6626052</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129670640</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>651783</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6626130</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129670610</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>651780</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6626169</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129670599</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>651890</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6626039</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129670647</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>651851</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6626154</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129670654</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>651893</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6626104</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129670649</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83004</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>308</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>651934</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6626028</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129670619</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>651882</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6626177</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129670626</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91851</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>658</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>651935</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6626058</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129670627</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91851</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>658</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>651922</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6626059</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129670608</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>651799</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6626199</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129670613</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>651827</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6626081</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129670590</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>651906</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6626033</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129670579</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>651794</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6626119</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129670621</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>651904</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6626101</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129670628</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91851</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>658</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>651867</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6626099</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129670587</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92271</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>651796</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6626068</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129670637</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>651703</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6626171</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129670650</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>651923</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6626100</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129670609</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>651777</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6626177</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129670622</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>651922</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6626011</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129670580</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>651826</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6626121</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129670615</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>651823</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6626169</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129670578</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>651796</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6626108</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129670605</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>651938</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6626032</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129670576</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>651928</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6626010</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129670623</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>651877</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6626056</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129670624</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>651791</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6626110</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129670645</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>651662</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6626158</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129670572</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>651860</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6626196</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129670643</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>651826</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6626121</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129670635</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>651924</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6626060</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129670583</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>651907</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6626130</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129670600</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>651666</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6626239</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129670574</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>651813</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6626139</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129670658</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92206</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>651860</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6626084</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129670573</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>651828</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6626081</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129670629</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>651815</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6626081</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129670614</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>651826</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6626121</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129670598</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>651789</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6626199</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129670630</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>651671</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6626205</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129670659</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92244</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>898</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>651798</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6626111</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129670617</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>651843</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6626170</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129670636</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>651666</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6626156</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129670581</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>651836</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6626151</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129670639</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>651700</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6626184</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129670616</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>651831</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6626150</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129670606</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>651875</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6626072</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129670646</v>
+      </c>
+      <c r="B85" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>651847</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6626179</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129670591</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>651709</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6626216</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670652</v>
+        <v>129670602</v>
       </c>
       <c r="B14" t="n">
-        <v>92203</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651866</v>
+        <v>651892</v>
       </c>
       <c r="R14" t="n">
-        <v>6626192</v>
+        <v>6626058</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,6 +2334,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2360,32 +2365,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670602</v>
+        <v>129670652</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>92231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651892</v>
+        <v>651866</v>
       </c>
       <c r="R15" t="n">
-        <v>6626058</v>
+        <v>6626192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2431,11 +2436,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2465,7 +2465,7 @@
         <v>129670575</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129670653</v>
       </c>
       <c r="B17" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129670584</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670611</v>
+        <v>129670586</v>
       </c>
       <c r="B19" t="n">
-        <v>92006</v>
+        <v>92299</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651780</v>
+        <v>651896</v>
       </c>
       <c r="R19" t="n">
-        <v>6626166</v>
+        <v>6626042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,32 +2850,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670618</v>
+        <v>129670655</v>
       </c>
       <c r="B20" t="n">
-        <v>92006</v>
+        <v>100945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651850</v>
+        <v>651655</v>
       </c>
       <c r="R20" t="n">
-        <v>6626173</v>
+        <v>6626179</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,32 +2947,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670655</v>
+        <v>129670638</v>
       </c>
       <c r="B21" t="n">
-        <v>100916</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651655</v>
+        <v>651788</v>
       </c>
       <c r="R21" t="n">
-        <v>6626179</v>
+        <v>6626118</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3018,6 +3018,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3044,32 +3049,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670638</v>
+        <v>129670656</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>100945</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651788</v>
+        <v>651804</v>
       </c>
       <c r="R22" t="n">
-        <v>6626118</v>
+        <v>6626213</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3115,11 +3120,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3146,32 +3146,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670656</v>
+        <v>129670611</v>
       </c>
       <c r="B23" t="n">
-        <v>100916</v>
+        <v>92034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651804</v>
+        <v>651780</v>
       </c>
       <c r="R23" t="n">
-        <v>6626213</v>
+        <v>6626166</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3243,32 +3243,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670586</v>
+        <v>129670618</v>
       </c>
       <c r="B24" t="n">
-        <v>92271</v>
+        <v>92034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651896</v>
+        <v>651850</v>
       </c>
       <c r="R24" t="n">
-        <v>6626042</v>
+        <v>6626173</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3343,7 +3343,7 @@
         <v>129670612</v>
       </c>
       <c r="B25" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>129670607</v>
       </c>
       <c r="B26" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>129670577</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>129670592</v>
       </c>
       <c r="B32" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>129670657</v>
       </c>
       <c r="B33" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>129670651</v>
       </c>
       <c r="B35" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670601</v>
+        <v>129670585</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>91581</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,21 +4423,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651723</v>
+        <v>651912</v>
       </c>
       <c r="R36" t="n">
-        <v>6626229</v>
+        <v>6626052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4483,11 +4483,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4514,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670585</v>
+        <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4520,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651912</v>
+        <v>651723</v>
       </c>
       <c r="R37" t="n">
-        <v>6626052</v>
+        <v>6626229</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4585,6 +4580,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B39" t="n">
-        <v>92006</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R39" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,6 +4779,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,7 +4813,7 @@
         <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4907,32 +4912,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4978,11 +4983,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,7 +5012,7 @@
         <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>129670649</v>
       </c>
       <c r="B43" t="n">
-        <v>83004</v>
+        <v>83031</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>129670619</v>
       </c>
       <c r="B44" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>129670626</v>
       </c>
       <c r="B45" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>129670627</v>
       </c>
       <c r="B46" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670590</v>
+        <v>129670587</v>
       </c>
       <c r="B49" t="n">
-        <v>91574</v>
+        <v>92299</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651906</v>
+        <v>651796</v>
       </c>
       <c r="R49" t="n">
-        <v>6626033</v>
+        <v>6626068</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5788,7 +5788,7 @@
         <v>129670579</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129670621</v>
       </c>
       <c r="B51" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129670628</v>
       </c>
       <c r="B52" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670587</v>
+        <v>129670650</v>
       </c>
       <c r="B53" t="n">
-        <v>92271</v>
+        <v>92231</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651796</v>
+        <v>651923</v>
       </c>
       <c r="R53" t="n">
-        <v>6626068</v>
+        <v>6626100</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6176,7 +6176,7 @@
         <v>129670637</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6275,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670650</v>
+        <v>129670590</v>
       </c>
       <c r="B55" t="n">
-        <v>92203</v>
+        <v>91602</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1339</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651923</v>
+        <v>651906</v>
       </c>
       <c r="R55" t="n">
-        <v>6626100</v>
+        <v>6626033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129670645</v>
       </c>
       <c r="B64" t="n">
-        <v>92006</v>
+        <v>4779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651662</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626158</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,6 +7219,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7245,32 +7250,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670645</v>
+        <v>129670624</v>
       </c>
       <c r="B65" t="n">
-        <v>4779</v>
+        <v>92034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7285,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651662</v>
+        <v>651791</v>
       </c>
       <c r="R65" t="n">
-        <v>6626158</v>
+        <v>6626110</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7316,11 +7321,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7350,7 +7350,7 @@
         <v>129670572</v>
       </c>
       <c r="B66" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7546,32 +7546,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670635</v>
+        <v>129670600</v>
       </c>
       <c r="B68" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651924</v>
+        <v>651666</v>
       </c>
       <c r="R68" t="n">
-        <v>6626060</v>
+        <v>6626239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7651,7 +7651,7 @@
         <v>129670583</v>
       </c>
       <c r="B69" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670600</v>
+        <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651666</v>
+        <v>651924</v>
       </c>
       <c r="R70" t="n">
-        <v>6626239</v>
+        <v>6626060</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7850,7 +7850,7 @@
         <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7949,32 +7949,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670658</v>
+        <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>92206</v>
+        <v>91581</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651860</v>
+        <v>651828</v>
       </c>
       <c r="R72" t="n">
-        <v>6626084</v>
+        <v>6626081</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8046,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670573</v>
+        <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>91553</v>
+        <v>92234</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651828</v>
+        <v>651860</v>
       </c>
       <c r="R73" t="n">
-        <v>6626081</v>
+        <v>6626084</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670614</v>
+        <v>129670630</v>
       </c>
       <c r="B75" t="n">
-        <v>92006</v>
+        <v>91354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651826</v>
+        <v>651671</v>
       </c>
       <c r="R75" t="n">
-        <v>6626121</v>
+        <v>6626205</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8340,7 +8340,7 @@
         <v>129670598</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8439,32 +8439,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670630</v>
+        <v>129670614</v>
       </c>
       <c r="B77" t="n">
-        <v>91326</v>
+        <v>92034</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3215</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651671</v>
+        <v>651826</v>
       </c>
       <c r="R77" t="n">
-        <v>6626205</v>
+        <v>6626121</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8539,7 +8539,7 @@
         <v>129670659</v>
       </c>
       <c r="B78" t="n">
-        <v>92244</v>
+        <v>92272</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>129670617</v>
       </c>
       <c r="B79" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8730,32 +8730,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670636</v>
+        <v>129670581</v>
       </c>
       <c r="B80" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651666</v>
+        <v>651836</v>
       </c>
       <c r="R80" t="n">
-        <v>6626156</v>
+        <v>6626151</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8801,11 +8801,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8832,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670581</v>
+        <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651836</v>
+        <v>651666</v>
       </c>
       <c r="R81" t="n">
-        <v>6626151</v>
+        <v>6626156</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8903,6 +8898,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8932,7 +8932,7 @@
         <v>129670639</v>
       </c>
       <c r="B82" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>129670616</v>
       </c>
       <c r="B83" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670606</v>
+        <v>129670646</v>
       </c>
       <c r="B84" t="n">
-        <v>92006</v>
+        <v>4779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651875</v>
+        <v>651847</v>
       </c>
       <c r="R84" t="n">
-        <v>6626072</v>
+        <v>6626179</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9199,6 +9199,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9225,32 +9230,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670646</v>
+        <v>129670606</v>
       </c>
       <c r="B85" t="n">
-        <v>4779</v>
+        <v>92034</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9265,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651847</v>
+        <v>651875</v>
       </c>
       <c r="R85" t="n">
-        <v>6626179</v>
+        <v>6626072</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9296,11 +9301,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9330,7 +9330,7 @@
         <v>129670591</v>
       </c>
       <c r="B86" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B34" t="n">
-        <v>4779</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R34" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670651</v>
+        <v>129670644</v>
       </c>
       <c r="B35" t="n">
-        <v>92231</v>
+        <v>4779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651804</v>
+        <v>651725</v>
       </c>
       <c r="R35" t="n">
-        <v>6626204</v>
+        <v>6626217</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,6 +4386,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,32 +4417,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670585</v>
+        <v>129670651</v>
       </c>
       <c r="B36" t="n">
-        <v>91581</v>
+        <v>92231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4452,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651912</v>
+        <v>651804</v>
       </c>
       <c r="R36" t="n">
-        <v>6626052</v>
+        <v>6626204</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670601</v>
+        <v>129670585</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651723</v>
+        <v>651912</v>
       </c>
       <c r="R37" t="n">
-        <v>6626229</v>
+        <v>6626052</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4580,11 +4585,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670630</v>
+        <v>129670636</v>
       </c>
       <c r="B75" t="n">
-        <v>91354</v>
+        <v>98756</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651671</v>
+        <v>651666</v>
       </c>
       <c r="R75" t="n">
-        <v>6626205</v>
+        <v>6626156</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8311,6 +8311,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8337,32 +8342,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670598</v>
+        <v>129670630</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>91354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651789</v>
+        <v>651671</v>
       </c>
       <c r="R76" t="n">
-        <v>6626199</v>
+        <v>6626205</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8408,11 +8413,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8439,32 +8439,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670614</v>
+        <v>129670598</v>
       </c>
       <c r="B77" t="n">
-        <v>92034</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651826</v>
+        <v>651789</v>
       </c>
       <c r="R77" t="n">
-        <v>6626121</v>
+        <v>6626199</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8510,6 +8510,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8536,10 +8541,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670659</v>
+        <v>129670614</v>
       </c>
       <c r="B78" t="n">
-        <v>92272</v>
+        <v>92034</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8547,21 +8552,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8576,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651798</v>
+        <v>651826</v>
       </c>
       <c r="R78" t="n">
-        <v>6626111</v>
+        <v>6626121</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8633,10 +8638,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670617</v>
+        <v>129670659</v>
       </c>
       <c r="B79" t="n">
-        <v>92034</v>
+        <v>92272</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8644,21 +8649,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8668,10 +8673,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651843</v>
+        <v>651798</v>
       </c>
       <c r="R79" t="n">
-        <v>6626170</v>
+        <v>6626111</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8730,32 +8735,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B80" t="n">
-        <v>91581</v>
+        <v>92034</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8770,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R80" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8827,32 +8832,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670636</v>
+        <v>129670581</v>
       </c>
       <c r="B81" t="n">
-        <v>98756</v>
+        <v>91581</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651666</v>
+        <v>651836</v>
       </c>
       <c r="R81" t="n">
-        <v>6626156</v>
+        <v>6626151</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8898,11 +8903,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B82" t="n">
-        <v>98756</v>
+        <v>92034</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R82" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,11 +9000,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9031,10 +9026,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>92034</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9042,21 +9037,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R83" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9102,6 +9097,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670602</v>
+        <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>92237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651892</v>
+        <v>651866</v>
       </c>
       <c r="R14" t="n">
-        <v>6626058</v>
+        <v>6626192</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,11 +2334,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,32 +2360,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>92231</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R15" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2462,32 +2457,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670575</v>
+        <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>91581</v>
+        <v>92237</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2497,10 +2492,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651902</v>
+        <v>651890</v>
       </c>
       <c r="R16" t="n">
-        <v>6626042</v>
+        <v>6626144</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2559,32 +2554,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670653</v>
+        <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>92231</v>
+        <v>91587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651890</v>
+        <v>651906</v>
       </c>
       <c r="R17" t="n">
-        <v>6626144</v>
+        <v>6626091</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2656,10 +2651,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670584</v>
+        <v>129670602</v>
       </c>
       <c r="B18" t="n">
-        <v>91581</v>
+        <v>57732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,21 +2662,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2691,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651906</v>
+        <v>651892</v>
       </c>
       <c r="R18" t="n">
-        <v>6626091</v>
+        <v>6626058</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2727,6 +2722,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670586</v>
+        <v>129670638</v>
       </c>
       <c r="B19" t="n">
-        <v>92299</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651896</v>
+        <v>651788</v>
       </c>
       <c r="R19" t="n">
-        <v>6626042</v>
+        <v>6626118</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,6 +2824,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,10 +2855,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670655</v>
+        <v>129670586</v>
       </c>
       <c r="B20" t="n">
-        <v>100945</v>
+        <v>92305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2861,21 +2866,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651655</v>
+        <v>651896</v>
       </c>
       <c r="R20" t="n">
-        <v>6626179</v>
+        <v>6626042</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,32 +2952,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670638</v>
+        <v>129670655</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>100957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651788</v>
+        <v>651655</v>
       </c>
       <c r="R21" t="n">
-        <v>6626118</v>
+        <v>6626179</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3018,11 +3023,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3052,7 +3052,7 @@
         <v>129670656</v>
       </c>
       <c r="B22" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>129670611</v>
       </c>
       <c r="B23" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>129670618</v>
       </c>
       <c r="B24" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>129670612</v>
       </c>
       <c r="B25" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>129670607</v>
       </c>
       <c r="B26" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>129670577</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670592</v>
+        <v>129670657</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>92240</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651842</v>
+        <v>651836</v>
       </c>
       <c r="R32" t="n">
-        <v>6626152</v>
+        <v>6626075</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670657</v>
+        <v>129670592</v>
       </c>
       <c r="B33" t="n">
-        <v>92234</v>
+        <v>91608</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651836</v>
+        <v>651842</v>
       </c>
       <c r="R33" t="n">
-        <v>6626075</v>
+        <v>6626152</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670601</v>
+        <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>92237</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651723</v>
+        <v>651804</v>
       </c>
       <c r="R34" t="n">
-        <v>6626229</v>
+        <v>6626204</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,11 +4284,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,32 +4310,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670644</v>
+        <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>4779</v>
+        <v>91587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4345,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651725</v>
+        <v>651912</v>
       </c>
       <c r="R35" t="n">
-        <v>6626217</v>
+        <v>6626052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,11 +4381,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,32 +4407,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670651</v>
+        <v>129670601</v>
       </c>
       <c r="B36" t="n">
-        <v>92231</v>
+        <v>57732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4452,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651804</v>
+        <v>651723</v>
       </c>
       <c r="R36" t="n">
-        <v>6626204</v>
+        <v>6626229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4488,6 +4478,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4514,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670585</v>
+        <v>129670644</v>
       </c>
       <c r="B37" t="n">
-        <v>91581</v>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651912</v>
+        <v>651725</v>
       </c>
       <c r="R37" t="n">
-        <v>6626052</v>
+        <v>6626217</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4585,6 +4580,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>92040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R39" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,11 +4779,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4813,7 +4808,7 @@
         <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B41" t="n">
-        <v>92034</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R41" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4983,6 +4978,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,7 +5012,7 @@
         <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670649</v>
+        <v>129670619</v>
       </c>
       <c r="B43" t="n">
-        <v>83031</v>
+        <v>92040</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651934</v>
+        <v>651882</v>
       </c>
       <c r="R43" t="n">
-        <v>6626028</v>
+        <v>6626177</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670619</v>
+        <v>129670626</v>
       </c>
       <c r="B44" t="n">
-        <v>92034</v>
+        <v>91885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651882</v>
+        <v>651935</v>
       </c>
       <c r="R44" t="n">
-        <v>6626177</v>
+        <v>6626058</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670626</v>
+        <v>129670627</v>
       </c>
       <c r="B45" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651935</v>
+        <v>651922</v>
       </c>
       <c r="R45" t="n">
-        <v>6626058</v>
+        <v>6626059</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670627</v>
+        <v>129670649</v>
       </c>
       <c r="B46" t="n">
-        <v>91879</v>
+        <v>83036</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651922</v>
+        <v>651934</v>
       </c>
       <c r="R46" t="n">
-        <v>6626059</v>
+        <v>6626028</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>129670587</v>
       </c>
       <c r="B49" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5785,10 +5785,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670579</v>
+        <v>129670590</v>
       </c>
       <c r="B50" t="n">
-        <v>91581</v>
+        <v>91608</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5796,21 +5796,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651794</v>
+        <v>651906</v>
       </c>
       <c r="R50" t="n">
-        <v>6626119</v>
+        <v>6626033</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670621</v>
+        <v>129670637</v>
       </c>
       <c r="B51" t="n">
-        <v>92034</v>
+        <v>98768</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651904</v>
+        <v>651703</v>
       </c>
       <c r="R51" t="n">
-        <v>6626101</v>
+        <v>6626171</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5953,6 +5953,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5979,10 +5984,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670628</v>
+        <v>129670579</v>
       </c>
       <c r="B52" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5990,21 +5995,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651867</v>
+        <v>651794</v>
       </c>
       <c r="R52" t="n">
-        <v>6626099</v>
+        <v>6626119</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,32 +6081,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670650</v>
+        <v>129670621</v>
       </c>
       <c r="B53" t="n">
-        <v>92231</v>
+        <v>92040</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651923</v>
+        <v>651904</v>
       </c>
       <c r="R53" t="n">
-        <v>6626100</v>
+        <v>6626101</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6173,32 +6178,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670637</v>
+        <v>129670628</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>91885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651703</v>
+        <v>651867</v>
       </c>
       <c r="R54" t="n">
-        <v>6626171</v>
+        <v>6626099</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6244,11 +6249,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6275,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670590</v>
+        <v>129670650</v>
       </c>
       <c r="B55" t="n">
-        <v>91602</v>
+        <v>92237</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>1339</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651906</v>
+        <v>651923</v>
       </c>
       <c r="R55" t="n">
-        <v>6626033</v>
+        <v>6626100</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670645</v>
+        <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>4779</v>
+        <v>92040</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651662</v>
+        <v>651791</v>
       </c>
       <c r="R64" t="n">
-        <v>6626158</v>
+        <v>6626110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,11 +7219,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7250,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>92034</v>
+        <v>91551</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R65" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7347,10 +7342,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670572</v>
+        <v>129670645</v>
       </c>
       <c r="B66" t="n">
-        <v>91545</v>
+        <v>4779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7358,21 +7353,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7377,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651860</v>
+        <v>651662</v>
       </c>
       <c r="R66" t="n">
-        <v>6626196</v>
+        <v>6626158</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7418,6 +7413,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>91587</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,10 +7643,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B69" t="n">
-        <v>91581</v>
+        <v>57732</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7659,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R69" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7719,6 +7714,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7748,7 +7748,7 @@
         <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7847,32 +7847,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670574</v>
+        <v>129670658</v>
       </c>
       <c r="B71" t="n">
-        <v>91581</v>
+        <v>92240</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651813</v>
+        <v>651860</v>
       </c>
       <c r="R71" t="n">
-        <v>6626139</v>
+        <v>6626084</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,11 +7918,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7949,10 +7944,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670573</v>
+        <v>129670574</v>
       </c>
       <c r="B72" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651828</v>
+        <v>651813</v>
       </c>
       <c r="R72" t="n">
-        <v>6626081</v>
+        <v>6626139</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8020,6 +8015,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8046,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670658</v>
+        <v>129670573</v>
       </c>
       <c r="B73" t="n">
-        <v>92234</v>
+        <v>91587</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651860</v>
+        <v>651828</v>
       </c>
       <c r="R73" t="n">
-        <v>6626084</v>
+        <v>6626081</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>129670636</v>
       </c>
       <c r="B75" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8342,32 +8342,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670630</v>
+        <v>129670614</v>
       </c>
       <c r="B76" t="n">
-        <v>91354</v>
+        <v>92040</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3215</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651671</v>
+        <v>651826</v>
       </c>
       <c r="R76" t="n">
-        <v>6626205</v>
+        <v>6626121</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8439,32 +8439,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670598</v>
+        <v>129670659</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>92278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>898</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651789</v>
+        <v>651798</v>
       </c>
       <c r="R77" t="n">
-        <v>6626199</v>
+        <v>6626111</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8510,11 +8510,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8541,10 +8536,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670614</v>
+        <v>129670617</v>
       </c>
       <c r="B78" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8576,10 +8571,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651826</v>
+        <v>651843</v>
       </c>
       <c r="R78" t="n">
-        <v>6626121</v>
+        <v>6626170</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8638,32 +8633,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670659</v>
+        <v>129670581</v>
       </c>
       <c r="B79" t="n">
-        <v>92272</v>
+        <v>91587</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8673,10 +8668,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651798</v>
+        <v>651836</v>
       </c>
       <c r="R79" t="n">
-        <v>6626111</v>
+        <v>6626151</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8735,32 +8730,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670617</v>
+        <v>129670630</v>
       </c>
       <c r="B80" t="n">
-        <v>92034</v>
+        <v>91360</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651843</v>
+        <v>651671</v>
       </c>
       <c r="R80" t="n">
-        <v>6626170</v>
+        <v>6626205</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8832,10 +8827,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670581</v>
+        <v>129670598</v>
       </c>
       <c r="B81" t="n">
-        <v>91581</v>
+        <v>57732</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8843,21 +8838,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651836</v>
+        <v>651789</v>
       </c>
       <c r="R81" t="n">
-        <v>6626151</v>
+        <v>6626199</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8903,6 +8898,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B82" t="n">
-        <v>92034</v>
+        <v>98768</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R82" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,6 +9000,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9026,10 +9031,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B83" t="n">
-        <v>98756</v>
+        <v>92040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9037,21 +9042,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9061,10 +9066,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R83" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9097,11 +9102,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670646</v>
+        <v>129670606</v>
       </c>
       <c r="B84" t="n">
-        <v>4779</v>
+        <v>92040</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651847</v>
+        <v>651875</v>
       </c>
       <c r="R84" t="n">
-        <v>6626179</v>
+        <v>6626072</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9199,11 +9199,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9230,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670606</v>
+        <v>129670591</v>
       </c>
       <c r="B85" t="n">
-        <v>92034</v>
+        <v>91608</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9265,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651875</v>
+        <v>651709</v>
       </c>
       <c r="R85" t="n">
-        <v>6626072</v>
+        <v>6626216</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9327,32 +9322,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670591</v>
+        <v>129670646</v>
       </c>
       <c r="B86" t="n">
-        <v>91602</v>
+        <v>4779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651709</v>
+        <v>651847</v>
       </c>
       <c r="R86" t="n">
-        <v>6626216</v>
+        <v>6626179</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9400,6 +9395,11 @@
           <t>2025-11-12</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9421,6 +9421,3512 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129717141</v>
+      </c>
+      <c r="B87" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>651809</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6626096</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129718132</v>
+      </c>
+      <c r="B88" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>651797</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6626076</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129718176</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>651797</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6626076</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129718056</v>
+      </c>
+      <c r="B90" t="n">
+        <v>105834</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>651824</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6626153</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129716221</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>651948</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6626068</v>
+      </c>
+      <c r="S91" t="n">
+        <v>15</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129717174</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>651792</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6626129</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129717108</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>651840</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6626075</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129716933</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>658</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>651888</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6626032</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129716639</v>
+      </c>
+      <c r="B95" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>651940</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6626011</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129716926</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>658</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>651937</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6626030</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129716486</v>
+      </c>
+      <c r="B97" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>651945</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6626052</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129716724</v>
+      </c>
+      <c r="B98" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>651937</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6626030</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129716946</v>
+      </c>
+      <c r="B99" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>651888</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6626032</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129717145</v>
+      </c>
+      <c r="B100" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>651809</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6626096</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129717884</v>
+      </c>
+      <c r="B101" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>651824</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6626153</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129717137</v>
+      </c>
+      <c r="B102" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>651809</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6626096</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129717904</v>
+      </c>
+      <c r="B103" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>651836</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6626167</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129716568</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>651940</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6626011</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129717005</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>651874</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6626042</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129716641</v>
+      </c>
+      <c r="B106" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>651940</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6626011</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129717132</v>
+      </c>
+      <c r="B107" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>651809</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6626096</v>
+      </c>
+      <c r="S107" t="n">
+        <v>15</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129717100</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>651840</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6626075</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129729579</v>
+      </c>
+      <c r="B109" t="n">
+        <v>92240</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>651841</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6626143</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129729569</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91608</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>651836</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6626143</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129729573</v>
+      </c>
+      <c r="B111" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>651931</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6626008</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129729567</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>651833</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6626148</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129729577</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>651837</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6626143</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129729576</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>658</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>651923</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6626013</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129729563</v>
+      </c>
+      <c r="B115" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>651787</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6626109</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129729565</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>651830</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6626219</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129729575</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>658</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>651890</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6626043</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129729570</v>
+      </c>
+      <c r="B118" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>651833</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6626152</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129729571</v>
+      </c>
+      <c r="B119" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>651915</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6626012</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129729566</v>
+      </c>
+      <c r="B120" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>651831</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6626182</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129729564</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>651819</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6626182</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129729568</v>
+      </c>
+      <c r="B122" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>651923</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6626013</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2457,32 +2457,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670653</v>
+        <v>129670584</v>
       </c>
       <c r="B16" t="n">
-        <v>92237</v>
+        <v>91588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651890</v>
+        <v>651906</v>
       </c>
       <c r="R16" t="n">
-        <v>6626144</v>
+        <v>6626091</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670584</v>
+        <v>129670602</v>
       </c>
       <c r="B17" t="n">
-        <v>91587</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651906</v>
+        <v>651892</v>
       </c>
       <c r="R17" t="n">
-        <v>6626091</v>
+        <v>6626058</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2625,6 +2625,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2651,32 +2656,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670602</v>
+        <v>129670653</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>92238</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2686,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651892</v>
+        <v>651890</v>
       </c>
       <c r="R18" t="n">
-        <v>6626058</v>
+        <v>6626144</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2722,11 +2727,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,10 +2753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670638</v>
+        <v>129670611</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>92041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,21 +2764,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651788</v>
+        <v>651780</v>
       </c>
       <c r="R19" t="n">
-        <v>6626118</v>
+        <v>6626166</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,11 +2824,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,32 +2850,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670586</v>
+        <v>129670618</v>
       </c>
       <c r="B20" t="n">
-        <v>92305</v>
+        <v>92041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651896</v>
+        <v>651850</v>
       </c>
       <c r="R20" t="n">
-        <v>6626042</v>
+        <v>6626173</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2952,32 +2947,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670655</v>
+        <v>129670612</v>
       </c>
       <c r="B21" t="n">
-        <v>100957</v>
+        <v>92041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651655</v>
+        <v>651783</v>
       </c>
       <c r="R21" t="n">
-        <v>6626179</v>
+        <v>6626160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3049,32 +3044,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670656</v>
+        <v>129670607</v>
       </c>
       <c r="B22" t="n">
-        <v>100957</v>
+        <v>92041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3084,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651804</v>
+        <v>651794</v>
       </c>
       <c r="R22" t="n">
-        <v>6626213</v>
+        <v>6626119</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3146,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670611</v>
+        <v>129670586</v>
       </c>
       <c r="B23" t="n">
-        <v>92040</v>
+        <v>92306</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651780</v>
+        <v>651896</v>
       </c>
       <c r="R23" t="n">
-        <v>6626166</v>
+        <v>6626042</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3243,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670618</v>
+        <v>129670638</v>
       </c>
       <c r="B24" t="n">
-        <v>92040</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,21 +3249,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651850</v>
+        <v>651788</v>
       </c>
       <c r="R24" t="n">
-        <v>6626173</v>
+        <v>6626118</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3314,6 +3309,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670612</v>
+        <v>129670655</v>
       </c>
       <c r="B25" t="n">
-        <v>92040</v>
+        <v>100958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651783</v>
+        <v>651655</v>
       </c>
       <c r="R25" t="n">
-        <v>6626160</v>
+        <v>6626179</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670607</v>
+        <v>129670656</v>
       </c>
       <c r="B26" t="n">
-        <v>92040</v>
+        <v>100958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651794</v>
+        <v>651804</v>
       </c>
       <c r="R26" t="n">
-        <v>6626119</v>
+        <v>6626213</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>129670577</v>
       </c>
       <c r="B29" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>129670657</v>
       </c>
       <c r="B32" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>129670592</v>
       </c>
       <c r="B33" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670651</v>
+        <v>129670644</v>
       </c>
       <c r="B34" t="n">
-        <v>92237</v>
+        <v>4779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651804</v>
+        <v>651725</v>
       </c>
       <c r="R34" t="n">
-        <v>6626204</v>
+        <v>6626217</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,6 +4284,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4310,32 +4315,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670585</v>
+        <v>129670651</v>
       </c>
       <c r="B35" t="n">
-        <v>91587</v>
+        <v>92238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651912</v>
+        <v>651804</v>
       </c>
       <c r="R35" t="n">
-        <v>6626052</v>
+        <v>6626204</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4407,10 +4412,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670601</v>
+        <v>129670585</v>
       </c>
       <c r="B36" t="n">
-        <v>57732</v>
+        <v>91588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4418,21 +4423,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4447,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651723</v>
+        <v>651912</v>
       </c>
       <c r="R36" t="n">
-        <v>6626229</v>
+        <v>6626052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4478,11 +4483,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R37" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670610</v>
+        <v>129670599</v>
       </c>
       <c r="B39" t="n">
-        <v>92040</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651780</v>
+        <v>651890</v>
       </c>
       <c r="R39" t="n">
-        <v>6626169</v>
+        <v>6626039</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,6 +4779,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,32 +4810,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670599</v>
+        <v>129670647</v>
       </c>
       <c r="B40" t="n">
-        <v>57732</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651890</v>
+        <v>651851</v>
       </c>
       <c r="R40" t="n">
-        <v>6626039</v>
+        <v>6626154</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4880,7 +4885,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4912,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4978,11 +4983,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670654</v>
+        <v>129670649</v>
       </c>
       <c r="B42" t="n">
-        <v>92237</v>
+        <v>83037</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651893</v>
+        <v>651934</v>
       </c>
       <c r="R42" t="n">
-        <v>6626104</v>
+        <v>6626028</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670619</v>
+        <v>129670654</v>
       </c>
       <c r="B43" t="n">
-        <v>92040</v>
+        <v>92238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651882</v>
+        <v>651893</v>
       </c>
       <c r="R43" t="n">
-        <v>6626177</v>
+        <v>6626104</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670626</v>
+        <v>129670619</v>
       </c>
       <c r="B44" t="n">
-        <v>91885</v>
+        <v>92041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651935</v>
+        <v>651882</v>
       </c>
       <c r="R44" t="n">
-        <v>6626058</v>
+        <v>6626177</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670627</v>
+        <v>129670626</v>
       </c>
       <c r="B45" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651922</v>
+        <v>651935</v>
       </c>
       <c r="R45" t="n">
-        <v>6626059</v>
+        <v>6626058</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670649</v>
+        <v>129670627</v>
       </c>
       <c r="B46" t="n">
-        <v>83036</v>
+        <v>91886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651934</v>
+        <v>651922</v>
       </c>
       <c r="R46" t="n">
-        <v>6626028</v>
+        <v>6626059</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670587</v>
+        <v>129670579</v>
       </c>
       <c r="B49" t="n">
-        <v>92305</v>
+        <v>91588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651796</v>
+        <v>651794</v>
       </c>
       <c r="R49" t="n">
-        <v>6626068</v>
+        <v>6626119</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5785,32 +5785,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670590</v>
+        <v>129670621</v>
       </c>
       <c r="B50" t="n">
-        <v>91608</v>
+        <v>92041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651906</v>
+        <v>651904</v>
       </c>
       <c r="R50" t="n">
-        <v>6626033</v>
+        <v>6626101</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670637</v>
+        <v>129670628</v>
       </c>
       <c r="B51" t="n">
-        <v>98768</v>
+        <v>91886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651703</v>
+        <v>651867</v>
       </c>
       <c r="R51" t="n">
-        <v>6626171</v>
+        <v>6626099</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5953,11 +5953,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5984,32 +5979,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670579</v>
+        <v>129670650</v>
       </c>
       <c r="B52" t="n">
-        <v>91587</v>
+        <v>92238</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6019,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651794</v>
+        <v>651923</v>
       </c>
       <c r="R52" t="n">
-        <v>6626119</v>
+        <v>6626100</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6081,32 +6076,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670621</v>
+        <v>129670587</v>
       </c>
       <c r="B53" t="n">
-        <v>92040</v>
+        <v>92306</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651904</v>
+        <v>651796</v>
       </c>
       <c r="R53" t="n">
-        <v>6626101</v>
+        <v>6626068</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6178,10 +6173,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670628</v>
+        <v>129670590</v>
       </c>
       <c r="B54" t="n">
-        <v>91885</v>
+        <v>91609</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6189,21 +6184,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6213,10 +6208,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651867</v>
+        <v>651906</v>
       </c>
       <c r="R54" t="n">
-        <v>6626099</v>
+        <v>6626033</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6275,32 +6270,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670650</v>
+        <v>129670637</v>
       </c>
       <c r="B55" t="n">
-        <v>92237</v>
+        <v>98769</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651923</v>
+        <v>651703</v>
       </c>
       <c r="R55" t="n">
-        <v>6626100</v>
+        <v>6626171</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6346,6 +6341,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6857,32 +6857,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129670605</v>
+        <v>129670576</v>
       </c>
       <c r="B61" t="n">
-        <v>92040</v>
+        <v>91588</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651938</v>
+        <v>651928</v>
       </c>
       <c r="R61" t="n">
-        <v>6626032</v>
+        <v>6626010</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6954,32 +6954,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129670576</v>
+        <v>129670623</v>
       </c>
       <c r="B62" t="n">
-        <v>91587</v>
+        <v>92041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651928</v>
+        <v>651877</v>
       </c>
       <c r="R62" t="n">
-        <v>6626010</v>
+        <v>6626056</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7051,10 +7051,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129670623</v>
+        <v>129670605</v>
       </c>
       <c r="B63" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651877</v>
+        <v>651938</v>
       </c>
       <c r="R63" t="n">
-        <v>6626056</v>
+        <v>6626032</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B64" t="n">
-        <v>92040</v>
+        <v>91552</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7245,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B65" t="n">
-        <v>91551</v>
+        <v>92041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R65" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7549,7 +7549,7 @@
         <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>129670600</v>
       </c>
       <c r="B69" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7847,32 +7847,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670658</v>
+        <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>92240</v>
+        <v>91588</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651860</v>
+        <v>651813</v>
       </c>
       <c r="R71" t="n">
-        <v>6626084</v>
+        <v>6626139</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,6 +7918,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7944,10 +7949,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670574</v>
+        <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7979,10 +7984,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651813</v>
+        <v>651828</v>
       </c>
       <c r="R72" t="n">
-        <v>6626139</v>
+        <v>6626081</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8015,11 +8020,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8046,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670573</v>
+        <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>91587</v>
+        <v>92241</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651828</v>
+        <v>651860</v>
       </c>
       <c r="R73" t="n">
-        <v>6626081</v>
+        <v>6626084</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670636</v>
+        <v>129670598</v>
       </c>
       <c r="B75" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651666</v>
+        <v>651789</v>
       </c>
       <c r="R75" t="n">
-        <v>6626156</v>
+        <v>6626199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8345,7 +8345,7 @@
         <v>129670614</v>
       </c>
       <c r="B76" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>129670659</v>
       </c>
       <c r="B77" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>129670617</v>
       </c>
       <c r="B78" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>129670581</v>
       </c>
       <c r="B79" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>129670630</v>
       </c>
       <c r="B80" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670598</v>
+        <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651789</v>
+        <v>651666</v>
       </c>
       <c r="R81" t="n">
-        <v>6626199</v>
+        <v>6626156</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Flyg och landningsläte</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8932,7 +8932,7 @@
         <v>129670639</v>
       </c>
       <c r="B82" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>129670616</v>
       </c>
       <c r="B83" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670606</v>
+        <v>129670591</v>
       </c>
       <c r="B84" t="n">
-        <v>92040</v>
+        <v>91609</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651875</v>
+        <v>651709</v>
       </c>
       <c r="R84" t="n">
-        <v>6626072</v>
+        <v>6626216</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670591</v>
+        <v>129670646</v>
       </c>
       <c r="B85" t="n">
-        <v>91608</v>
+        <v>4779</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651709</v>
+        <v>651847</v>
       </c>
       <c r="R85" t="n">
-        <v>6626216</v>
+        <v>6626179</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9296,6 +9296,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9322,32 +9327,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670646</v>
+        <v>129670606</v>
       </c>
       <c r="B86" t="n">
-        <v>4779</v>
+        <v>92041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651847</v>
+        <v>651875</v>
       </c>
       <c r="R86" t="n">
-        <v>6626179</v>
+        <v>6626072</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,11 +9398,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>92040</v>
+        <v>98769</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B89" t="n">
-        <v>98768</v>
+        <v>92041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>105834</v>
+        <v>91588</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R90" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>91587</v>
+        <v>105835</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R91" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9909,27 +9909,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92006</v>
+        <v>92041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9939,10 +9944,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R92" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10001,32 +10006,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92040</v>
+        <v>92007</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R93" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10101,7 +10101,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10777,54 +10777,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717884</v>
+        <v>129717137</v>
       </c>
       <c r="B101" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R101" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10883,45 +10874,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717137</v>
+        <v>129717884</v>
       </c>
       <c r="B102" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R102" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10983,7 +10983,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11280,32 +11280,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129716641</v>
+        <v>129717100</v>
       </c>
       <c r="B106" t="n">
-        <v>92040</v>
+        <v>91588</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651940</v>
+        <v>651840</v>
       </c>
       <c r="R106" t="n">
-        <v>6626011</v>
+        <v>6626075</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11377,10 +11377,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129717132</v>
+        <v>129716641</v>
       </c>
       <c r="B107" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651809</v>
+        <v>651940</v>
       </c>
       <c r="R107" t="n">
-        <v>6626096</v>
+        <v>6626011</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11474,32 +11474,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129717100</v>
+        <v>129717132</v>
       </c>
       <c r="B108" t="n">
-        <v>91587</v>
+        <v>92041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11509,10 +11509,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651840</v>
+        <v>651809</v>
       </c>
       <c r="R108" t="n">
-        <v>6626075</v>
+        <v>6626096</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11574,7 +11574,7 @@
         <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670652</v>
+        <v>129670602</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651866</v>
+        <v>651892</v>
       </c>
       <c r="R14" t="n">
-        <v>6626192</v>
+        <v>6626058</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,6 +2334,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2360,32 +2365,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670575</v>
+        <v>129670652</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>92238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651902</v>
+        <v>651866</v>
       </c>
       <c r="R15" t="n">
-        <v>6626042</v>
+        <v>6626192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,7 +2462,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670584</v>
+        <v>129670575</v>
       </c>
       <c r="B16" t="n">
         <v>91588</v>
@@ -2492,10 +2497,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651906</v>
+        <v>651902</v>
       </c>
       <c r="R16" t="n">
-        <v>6626091</v>
+        <v>6626042</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2554,32 +2559,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670602</v>
+        <v>129670653</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>92238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651892</v>
+        <v>651890</v>
       </c>
       <c r="R17" t="n">
-        <v>6626058</v>
+        <v>6626144</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2625,11 +2630,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,32 +2656,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670653</v>
+        <v>129670584</v>
       </c>
       <c r="B18" t="n">
-        <v>92238</v>
+        <v>91588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651890</v>
+        <v>651906</v>
       </c>
       <c r="R18" t="n">
-        <v>6626144</v>
+        <v>6626091</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -3141,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670586</v>
+        <v>129670638</v>
       </c>
       <c r="B23" t="n">
-        <v>92306</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651896</v>
+        <v>651788</v>
       </c>
       <c r="R23" t="n">
-        <v>6626042</v>
+        <v>6626118</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3212,6 +3212,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,32 +3243,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670638</v>
+        <v>129670655</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>100958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651788</v>
+        <v>651655</v>
       </c>
       <c r="R24" t="n">
-        <v>6626118</v>
+        <v>6626179</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,11 +3314,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,7 +3340,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670655</v>
+        <v>129670656</v>
       </c>
       <c r="B25" t="n">
         <v>100958</v>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651655</v>
+        <v>651804</v>
       </c>
       <c r="R25" t="n">
-        <v>6626179</v>
+        <v>6626213</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670656</v>
+        <v>129670586</v>
       </c>
       <c r="B26" t="n">
-        <v>100958</v>
+        <v>92306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651804</v>
+        <v>651896</v>
       </c>
       <c r="R26" t="n">
-        <v>6626213</v>
+        <v>6626042</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B34" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R34" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670651</v>
+        <v>129670644</v>
       </c>
       <c r="B35" t="n">
-        <v>92238</v>
+        <v>4779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651804</v>
+        <v>651725</v>
       </c>
       <c r="R35" t="n">
-        <v>6626204</v>
+        <v>6626217</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,6 +4386,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,32 +4417,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670585</v>
+        <v>129670651</v>
       </c>
       <c r="B36" t="n">
-        <v>91588</v>
+        <v>92238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4452,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651912</v>
+        <v>651804</v>
       </c>
       <c r="R36" t="n">
-        <v>6626052</v>
+        <v>6626204</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670601</v>
+        <v>129670585</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>91588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651723</v>
+        <v>651912</v>
       </c>
       <c r="R37" t="n">
-        <v>6626229</v>
+        <v>6626052</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4580,11 +4585,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670599</v>
+        <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>92041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651890</v>
+        <v>651780</v>
       </c>
       <c r="R39" t="n">
-        <v>6626039</v>
+        <v>6626169</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,11 +4779,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4810,32 +4805,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670647</v>
+        <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4845,10 +4840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651851</v>
+        <v>651890</v>
       </c>
       <c r="R40" t="n">
-        <v>6626154</v>
+        <v>6626039</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4885,7 +4880,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B41" t="n">
-        <v>92041</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R41" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4983,6 +4978,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5494,7 +5494,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129670608</v>
+        <v>129670613</v>
       </c>
       <c r="B47" t="n">
         <v>92041</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651799</v>
+        <v>651827</v>
       </c>
       <c r="R47" t="n">
-        <v>6626199</v>
+        <v>6626081</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129670613</v>
+        <v>129670608</v>
       </c>
       <c r="B48" t="n">
         <v>92041</v>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651827</v>
+        <v>651799</v>
       </c>
       <c r="R48" t="n">
-        <v>6626081</v>
+        <v>6626199</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670579</v>
+        <v>129670637</v>
       </c>
       <c r="B49" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651794</v>
+        <v>651703</v>
       </c>
       <c r="R49" t="n">
-        <v>6626119</v>
+        <v>6626171</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5759,6 +5759,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5785,32 +5790,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670621</v>
+        <v>129670579</v>
       </c>
       <c r="B50" t="n">
-        <v>92041</v>
+        <v>91588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651904</v>
+        <v>651794</v>
       </c>
       <c r="R50" t="n">
-        <v>6626101</v>
+        <v>6626119</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5887,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670628</v>
+        <v>129670621</v>
       </c>
       <c r="B51" t="n">
-        <v>91886</v>
+        <v>92041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5922,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651867</v>
+        <v>651904</v>
       </c>
       <c r="R51" t="n">
-        <v>6626099</v>
+        <v>6626101</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5979,32 +5984,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670650</v>
+        <v>129670628</v>
       </c>
       <c r="B52" t="n">
-        <v>92238</v>
+        <v>91886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651923</v>
+        <v>651867</v>
       </c>
       <c r="R52" t="n">
-        <v>6626100</v>
+        <v>6626099</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,10 +6081,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670587</v>
+        <v>129670650</v>
       </c>
       <c r="B53" t="n">
-        <v>92306</v>
+        <v>92238</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6087,21 +6092,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651796</v>
+        <v>651923</v>
       </c>
       <c r="R53" t="n">
-        <v>6626068</v>
+        <v>6626100</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6173,32 +6178,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670590</v>
+        <v>129670587</v>
       </c>
       <c r="B54" t="n">
-        <v>91609</v>
+        <v>92306</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651906</v>
+        <v>651796</v>
       </c>
       <c r="R54" t="n">
-        <v>6626033</v>
+        <v>6626068</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6270,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670637</v>
+        <v>129670590</v>
       </c>
       <c r="B55" t="n">
-        <v>98769</v>
+        <v>91609</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651703</v>
+        <v>651906</v>
       </c>
       <c r="R55" t="n">
-        <v>6626171</v>
+        <v>6626033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6341,11 +6346,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6857,32 +6857,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129670576</v>
+        <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>91588</v>
+        <v>92041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651928</v>
+        <v>651938</v>
       </c>
       <c r="R61" t="n">
-        <v>6626010</v>
+        <v>6626032</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6954,32 +6954,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129670623</v>
+        <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>92041</v>
+        <v>91588</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651877</v>
+        <v>651928</v>
       </c>
       <c r="R62" t="n">
-        <v>6626056</v>
+        <v>6626010</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129670605</v>
+        <v>129670623</v>
       </c>
       <c r="B63" t="n">
         <v>92041</v>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651938</v>
+        <v>651877</v>
       </c>
       <c r="R63" t="n">
-        <v>6626032</v>
+        <v>6626056</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>91552</v>
+        <v>92041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R64" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7245,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>92041</v>
+        <v>91552</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R65" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B68" t="n">
-        <v>91588</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,6 +7617,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7643,10 +7648,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>91588</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7654,21 +7659,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R69" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7714,11 +7719,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670598</v>
+        <v>129670630</v>
       </c>
       <c r="B75" t="n">
-        <v>57733</v>
+        <v>91361</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651789</v>
+        <v>651671</v>
       </c>
       <c r="R75" t="n">
-        <v>6626199</v>
+        <v>6626205</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8311,11 +8311,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8342,10 +8337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670614</v>
+        <v>129670636</v>
       </c>
       <c r="B76" t="n">
-        <v>92041</v>
+        <v>98769</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8353,21 +8348,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651826</v>
+        <v>651666</v>
       </c>
       <c r="R76" t="n">
-        <v>6626121</v>
+        <v>6626156</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8413,6 +8408,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8439,10 +8439,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670659</v>
+        <v>129670614</v>
       </c>
       <c r="B77" t="n">
-        <v>92279</v>
+        <v>92041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8450,21 +8450,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651798</v>
+        <v>651826</v>
       </c>
       <c r="R77" t="n">
-        <v>6626111</v>
+        <v>6626121</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670617</v>
+        <v>129670659</v>
       </c>
       <c r="B78" t="n">
-        <v>92041</v>
+        <v>92279</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8547,21 +8547,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651843</v>
+        <v>651798</v>
       </c>
       <c r="R78" t="n">
-        <v>6626170</v>
+        <v>6626111</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8633,32 +8633,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B79" t="n">
-        <v>91588</v>
+        <v>92041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R79" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8730,32 +8730,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670630</v>
+        <v>129670581</v>
       </c>
       <c r="B80" t="n">
-        <v>91361</v>
+        <v>91588</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651671</v>
+        <v>651836</v>
       </c>
       <c r="R80" t="n">
-        <v>6626205</v>
+        <v>6626151</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670636</v>
+        <v>129670598</v>
       </c>
       <c r="B81" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651666</v>
+        <v>651789</v>
       </c>
       <c r="R81" t="n">
-        <v>6626156</v>
+        <v>6626199</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B88" t="n">
-        <v>98769</v>
+        <v>92041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B89" t="n">
-        <v>92041</v>
+        <v>98769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11280,32 +11280,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129717100</v>
+        <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>91588</v>
+        <v>92041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651840</v>
+        <v>651940</v>
       </c>
       <c r="R106" t="n">
-        <v>6626075</v>
+        <v>6626011</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11377,7 +11377,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129716641</v>
+        <v>129717132</v>
       </c>
       <c r="B107" t="n">
         <v>92041</v>
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651940</v>
+        <v>651809</v>
       </c>
       <c r="R107" t="n">
-        <v>6626011</v>
+        <v>6626096</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11474,32 +11474,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129717132</v>
+        <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>92041</v>
+        <v>91588</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11509,10 +11509,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651809</v>
+        <v>651840</v>
       </c>
       <c r="R108" t="n">
-        <v>6626096</v>
+        <v>6626075</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670602</v>
+        <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651892</v>
+        <v>651866</v>
       </c>
       <c r="R14" t="n">
-        <v>6626058</v>
+        <v>6626192</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,11 +2334,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,32 +2360,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>92238</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R15" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2462,32 +2457,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670575</v>
+        <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>91588</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2497,10 +2492,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651902</v>
+        <v>651890</v>
       </c>
       <c r="R16" t="n">
-        <v>6626042</v>
+        <v>6626144</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2559,32 +2554,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670653</v>
+        <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>92238</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651890</v>
+        <v>651906</v>
       </c>
       <c r="R17" t="n">
-        <v>6626144</v>
+        <v>6626091</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2656,10 +2651,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670584</v>
+        <v>129670602</v>
       </c>
       <c r="B18" t="n">
-        <v>91588</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,21 +2662,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2691,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651906</v>
+        <v>651892</v>
       </c>
       <c r="R18" t="n">
-        <v>6626091</v>
+        <v>6626058</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2727,6 +2722,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670611</v>
+        <v>129670655</v>
       </c>
       <c r="B19" t="n">
-        <v>92041</v>
+        <v>100963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651780</v>
+        <v>651655</v>
       </c>
       <c r="R19" t="n">
-        <v>6626166</v>
+        <v>6626179</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,32 +2850,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670618</v>
+        <v>129670656</v>
       </c>
       <c r="B20" t="n">
-        <v>92041</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651850</v>
+        <v>651804</v>
       </c>
       <c r="R20" t="n">
-        <v>6626173</v>
+        <v>6626213</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670612</v>
+        <v>129670611</v>
       </c>
       <c r="B21" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651783</v>
+        <v>651780</v>
       </c>
       <c r="R21" t="n">
-        <v>6626160</v>
+        <v>6626166</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670607</v>
+        <v>129670618</v>
       </c>
       <c r="B22" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651794</v>
+        <v>651850</v>
       </c>
       <c r="R22" t="n">
-        <v>6626119</v>
+        <v>6626173</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670638</v>
+        <v>129670612</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>92046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651788</v>
+        <v>651783</v>
       </c>
       <c r="R23" t="n">
-        <v>6626118</v>
+        <v>6626160</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3212,11 +3212,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,32 +3238,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670655</v>
+        <v>129670607</v>
       </c>
       <c r="B24" t="n">
-        <v>100958</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651655</v>
+        <v>651794</v>
       </c>
       <c r="R24" t="n">
-        <v>6626179</v>
+        <v>6626119</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3340,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670656</v>
+        <v>129670586</v>
       </c>
       <c r="B25" t="n">
-        <v>100958</v>
+        <v>92311</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,21 +3346,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651804</v>
+        <v>651896</v>
       </c>
       <c r="R25" t="n">
-        <v>6626213</v>
+        <v>6626042</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3432,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670586</v>
+        <v>129670638</v>
       </c>
       <c r="B26" t="n">
-        <v>92306</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651896</v>
+        <v>651788</v>
       </c>
       <c r="R26" t="n">
-        <v>6626042</v>
+        <v>6626118</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,6 +3503,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670577</v>
+        <v>129670582</v>
       </c>
       <c r="B29" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651934</v>
+        <v>651839</v>
       </c>
       <c r="R29" t="n">
-        <v>6626035</v>
+        <v>6626178</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670582</v>
+        <v>129670577</v>
       </c>
       <c r="B30" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651839</v>
+        <v>651934</v>
       </c>
       <c r="R30" t="n">
-        <v>6626178</v>
+        <v>6626035</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3925,7 +3925,7 @@
         <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670657</v>
+        <v>129670592</v>
       </c>
       <c r="B32" t="n">
-        <v>92241</v>
+        <v>91614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651836</v>
+        <v>651842</v>
       </c>
       <c r="R32" t="n">
-        <v>6626075</v>
+        <v>6626152</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670592</v>
+        <v>129670657</v>
       </c>
       <c r="B33" t="n">
-        <v>91609</v>
+        <v>92246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651842</v>
+        <v>651836</v>
       </c>
       <c r="R33" t="n">
-        <v>6626152</v>
+        <v>6626075</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4420,7 +4420,7 @@
         <v>129670651</v>
       </c>
       <c r="B36" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>129670585</v>
       </c>
       <c r="B37" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>129670649</v>
       </c>
       <c r="B42" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670654</v>
+        <v>129670626</v>
       </c>
       <c r="B43" t="n">
-        <v>92238</v>
+        <v>91891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651893</v>
+        <v>651935</v>
       </c>
       <c r="R43" t="n">
-        <v>6626104</v>
+        <v>6626058</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670619</v>
+        <v>129670627</v>
       </c>
       <c r="B44" t="n">
-        <v>92041</v>
+        <v>91891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651882</v>
+        <v>651922</v>
       </c>
       <c r="R44" t="n">
-        <v>6626177</v>
+        <v>6626059</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670626</v>
+        <v>129670654</v>
       </c>
       <c r="B45" t="n">
-        <v>91886</v>
+        <v>92243</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651935</v>
+        <v>651893</v>
       </c>
       <c r="R45" t="n">
-        <v>6626058</v>
+        <v>6626104</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670627</v>
+        <v>129670619</v>
       </c>
       <c r="B46" t="n">
-        <v>91886</v>
+        <v>92046</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651922</v>
+        <v>651882</v>
       </c>
       <c r="R46" t="n">
-        <v>6626059</v>
+        <v>6626177</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129670613</v>
+        <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651827</v>
+        <v>651799</v>
       </c>
       <c r="R47" t="n">
-        <v>6626081</v>
+        <v>6626199</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129670608</v>
+        <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651799</v>
+        <v>651827</v>
       </c>
       <c r="R48" t="n">
-        <v>6626199</v>
+        <v>6626081</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670637</v>
+        <v>129670579</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651703</v>
+        <v>651794</v>
       </c>
       <c r="R49" t="n">
-        <v>6626171</v>
+        <v>6626119</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5759,11 +5759,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5790,32 +5785,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670579</v>
+        <v>129670621</v>
       </c>
       <c r="B50" t="n">
-        <v>91588</v>
+        <v>92046</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651794</v>
+        <v>651904</v>
       </c>
       <c r="R50" t="n">
-        <v>6626119</v>
+        <v>6626101</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5887,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670621</v>
+        <v>129670650</v>
       </c>
       <c r="B51" t="n">
-        <v>92041</v>
+        <v>92243</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5922,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651904</v>
+        <v>651923</v>
       </c>
       <c r="R51" t="n">
-        <v>6626101</v>
+        <v>6626100</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5984,32 +5979,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670628</v>
+        <v>129670587</v>
       </c>
       <c r="B52" t="n">
-        <v>91886</v>
+        <v>92311</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6019,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651867</v>
+        <v>651796</v>
       </c>
       <c r="R52" t="n">
-        <v>6626099</v>
+        <v>6626068</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6081,32 +6076,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670650</v>
+        <v>129670637</v>
       </c>
       <c r="B53" t="n">
-        <v>92238</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651923</v>
+        <v>651703</v>
       </c>
       <c r="R53" t="n">
-        <v>6626100</v>
+        <v>6626171</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6152,6 +6147,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,32 +6178,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670587</v>
+        <v>129670628</v>
       </c>
       <c r="B54" t="n">
-        <v>92306</v>
+        <v>91891</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651796</v>
+        <v>651867</v>
       </c>
       <c r="R54" t="n">
-        <v>6626068</v>
+        <v>6626099</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6278,7 +6278,7 @@
         <v>129670590</v>
       </c>
       <c r="B55" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,32 +6663,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129670615</v>
+        <v>129670578</v>
       </c>
       <c r="B59" t="n">
-        <v>92041</v>
+        <v>91593</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651823</v>
+        <v>651796</v>
       </c>
       <c r="R59" t="n">
-        <v>6626169</v>
+        <v>6626108</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6760,32 +6760,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129670578</v>
+        <v>129670605</v>
       </c>
       <c r="B60" t="n">
-        <v>91588</v>
+        <v>92046</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651796</v>
+        <v>651938</v>
       </c>
       <c r="R60" t="n">
-        <v>6626108</v>
+        <v>6626032</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6857,32 +6857,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129670605</v>
+        <v>129670576</v>
       </c>
       <c r="B61" t="n">
-        <v>92041</v>
+        <v>91593</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651938</v>
+        <v>651928</v>
       </c>
       <c r="R61" t="n">
-        <v>6626032</v>
+        <v>6626010</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6954,32 +6954,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129670576</v>
+        <v>129670623</v>
       </c>
       <c r="B62" t="n">
-        <v>91588</v>
+        <v>92046</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651928</v>
+        <v>651877</v>
       </c>
       <c r="R62" t="n">
-        <v>6626010</v>
+        <v>6626056</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7051,10 +7051,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129670623</v>
+        <v>129670615</v>
       </c>
       <c r="B63" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651877</v>
+        <v>651823</v>
       </c>
       <c r="R63" t="n">
-        <v>6626056</v>
+        <v>6626169</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7151,7 +7151,7 @@
         <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,32 +7643,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670583</v>
+        <v>129670635</v>
       </c>
       <c r="B69" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651907</v>
+        <v>651924</v>
       </c>
       <c r="R69" t="n">
-        <v>6626130</v>
+        <v>6626060</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7719,6 +7714,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670635</v>
+        <v>129670600</v>
       </c>
       <c r="B70" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651924</v>
+        <v>651666</v>
       </c>
       <c r="R70" t="n">
-        <v>6626060</v>
+        <v>6626239</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7850,7 +7850,7 @@
         <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>129670630</v>
       </c>
       <c r="B75" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8337,10 +8337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670636</v>
+        <v>129670614</v>
       </c>
       <c r="B76" t="n">
-        <v>98769</v>
+        <v>92046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,21 +8348,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651666</v>
+        <v>651826</v>
       </c>
       <c r="R76" t="n">
-        <v>6626156</v>
+        <v>6626121</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8408,11 +8408,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8439,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670614</v>
+        <v>129670617</v>
       </c>
       <c r="B77" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8474,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651826</v>
+        <v>651843</v>
       </c>
       <c r="R77" t="n">
-        <v>6626121</v>
+        <v>6626170</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8536,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670659</v>
+        <v>129670581</v>
       </c>
       <c r="B78" t="n">
-        <v>92279</v>
+        <v>91593</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651798</v>
+        <v>651836</v>
       </c>
       <c r="R78" t="n">
-        <v>6626111</v>
+        <v>6626151</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8633,10 +8628,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670617</v>
+        <v>129670659</v>
       </c>
       <c r="B79" t="n">
-        <v>92041</v>
+        <v>92284</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8644,21 +8639,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8668,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651843</v>
+        <v>651798</v>
       </c>
       <c r="R79" t="n">
-        <v>6626170</v>
+        <v>6626111</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8730,10 +8725,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670581</v>
+        <v>129670598</v>
       </c>
       <c r="B80" t="n">
-        <v>91588</v>
+        <v>57733</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8741,21 +8736,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8760,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651836</v>
+        <v>651789</v>
       </c>
       <c r="R80" t="n">
-        <v>6626151</v>
+        <v>6626199</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8801,6 +8796,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670598</v>
+        <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651789</v>
+        <v>651666</v>
       </c>
       <c r="R81" t="n">
-        <v>6626199</v>
+        <v>6626156</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Flyg och landningsläte</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B82" t="n">
-        <v>98769</v>
+        <v>92046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R82" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,11 +9000,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9031,10 +9026,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>92041</v>
+        <v>98774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9042,21 +9037,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R83" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9102,6 +9097,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9131,7 +9131,7 @@
         <v>129670591</v>
       </c>
       <c r="B84" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>129670606</v>
       </c>
       <c r="B86" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>129718132</v>
       </c>
       <c r="B88" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>129718176</v>
       </c>
       <c r="B89" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9909,32 +9909,27 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B92" t="n">
-        <v>92041</v>
+        <v>92012</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9944,10 +9939,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R92" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10006,27 +10001,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B93" t="n">
-        <v>92007</v>
+        <v>92046</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R93" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10101,7 +10101,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10583,45 +10583,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129716946</v>
+        <v>129717884</v>
       </c>
       <c r="B99" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651888</v>
+        <v>651824</v>
       </c>
       <c r="R99" t="n">
-        <v>6626032</v>
+        <v>6626153</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10780,7 +10789,7 @@
         <v>129717137</v>
       </c>
       <c r="B101" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10874,54 +10883,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717884</v>
+        <v>129716946</v>
       </c>
       <c r="B102" t="n">
-        <v>98769</v>
+        <v>5177</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651824</v>
+        <v>651888</v>
       </c>
       <c r="R102" t="n">
-        <v>6626153</v>
+        <v>6626032</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10983,7 +10983,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11571,32 +11571,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129729579</v>
+        <v>129729569</v>
       </c>
       <c r="B109" t="n">
-        <v>92241</v>
+        <v>91614</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651841</v>
+        <v>651836</v>
       </c>
       <c r="R109" t="n">
         <v>6626143</v>
@@ -11650,7 +11650,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11669,32 +11668,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129729569</v>
+        <v>129729579</v>
       </c>
       <c r="B110" t="n">
-        <v>91609</v>
+        <v>92246</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11704,7 +11703,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651836</v>
+        <v>651841</v>
       </c>
       <c r="R110" t="n">
         <v>6626143</v>
@@ -11748,6 +11747,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670652</v>
+        <v>129670602</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651866</v>
+        <v>651892</v>
       </c>
       <c r="R14" t="n">
-        <v>6626192</v>
+        <v>6626058</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,6 +2334,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2360,32 +2365,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670575</v>
+        <v>129670652</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>92243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651902</v>
+        <v>651866</v>
       </c>
       <c r="R15" t="n">
-        <v>6626042</v>
+        <v>6626192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,32 +2462,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670653</v>
+        <v>129670575</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2492,10 +2497,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651890</v>
+        <v>651902</v>
       </c>
       <c r="R16" t="n">
-        <v>6626144</v>
+        <v>6626042</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2554,32 +2559,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670584</v>
+        <v>129670653</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>92243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651906</v>
+        <v>651890</v>
       </c>
       <c r="R17" t="n">
-        <v>6626091</v>
+        <v>6626144</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2651,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670602</v>
+        <v>129670584</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,21 +2667,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2686,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651892</v>
+        <v>651906</v>
       </c>
       <c r="R18" t="n">
-        <v>6626058</v>
+        <v>6626091</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2722,11 +2727,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670655</v>
+        <v>129670611</v>
       </c>
       <c r="B19" t="n">
-        <v>100963</v>
+        <v>92046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651655</v>
+        <v>651780</v>
       </c>
       <c r="R19" t="n">
-        <v>6626179</v>
+        <v>6626166</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,32 +2850,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670656</v>
+        <v>129670618</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>92046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651804</v>
+        <v>651850</v>
       </c>
       <c r="R20" t="n">
-        <v>6626213</v>
+        <v>6626173</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670611</v>
+        <v>129670612</v>
       </c>
       <c r="B21" t="n">
         <v>92046</v>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651780</v>
+        <v>651783</v>
       </c>
       <c r="R21" t="n">
-        <v>6626166</v>
+        <v>6626160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670618</v>
+        <v>129670607</v>
       </c>
       <c r="B22" t="n">
         <v>92046</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651850</v>
+        <v>651794</v>
       </c>
       <c r="R22" t="n">
-        <v>6626173</v>
+        <v>6626119</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670612</v>
+        <v>129670586</v>
       </c>
       <c r="B23" t="n">
-        <v>92046</v>
+        <v>92311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651783</v>
+        <v>651896</v>
       </c>
       <c r="R23" t="n">
-        <v>6626160</v>
+        <v>6626042</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,32 +3238,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670607</v>
+        <v>129670655</v>
       </c>
       <c r="B24" t="n">
-        <v>92046</v>
+        <v>100963</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651794</v>
+        <v>651655</v>
       </c>
       <c r="R24" t="n">
-        <v>6626119</v>
+        <v>6626179</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670586</v>
+        <v>129670656</v>
       </c>
       <c r="B25" t="n">
-        <v>92311</v>
+        <v>100963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651896</v>
+        <v>651804</v>
       </c>
       <c r="R25" t="n">
-        <v>6626042</v>
+        <v>6626213</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670582</v>
+        <v>129670577</v>
       </c>
       <c r="B29" t="n">
         <v>91593</v>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651839</v>
+        <v>651934</v>
       </c>
       <c r="R29" t="n">
-        <v>6626178</v>
+        <v>6626035</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670577</v>
+        <v>129670582</v>
       </c>
       <c r="B30" t="n">
         <v>91593</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651934</v>
+        <v>651839</v>
       </c>
       <c r="R30" t="n">
-        <v>6626035</v>
+        <v>6626178</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670592</v>
+        <v>129670657</v>
       </c>
       <c r="B32" t="n">
-        <v>91614</v>
+        <v>92246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651842</v>
+        <v>651836</v>
       </c>
       <c r="R32" t="n">
-        <v>6626152</v>
+        <v>6626075</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670657</v>
+        <v>129670592</v>
       </c>
       <c r="B33" t="n">
-        <v>92246</v>
+        <v>91614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651836</v>
+        <v>651842</v>
       </c>
       <c r="R33" t="n">
-        <v>6626075</v>
+        <v>6626152</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R34" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670644</v>
+        <v>129670651</v>
       </c>
       <c r="B35" t="n">
-        <v>4779</v>
+        <v>92243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651725</v>
+        <v>651804</v>
       </c>
       <c r="R35" t="n">
-        <v>6626217</v>
+        <v>6626204</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,11 +4386,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,32 +4412,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670651</v>
+        <v>129670585</v>
       </c>
       <c r="B36" t="n">
-        <v>92243</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4452,10 +4447,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651804</v>
+        <v>651912</v>
       </c>
       <c r="R36" t="n">
-        <v>6626204</v>
+        <v>6626052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4514,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670585</v>
+        <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4520,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651912</v>
+        <v>651723</v>
       </c>
       <c r="R37" t="n">
-        <v>6626052</v>
+        <v>6626229</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4585,6 +4580,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670649</v>
+        <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>83042</v>
+        <v>92243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651934</v>
+        <v>651893</v>
       </c>
       <c r="R42" t="n">
-        <v>6626028</v>
+        <v>6626104</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670626</v>
+        <v>129670619</v>
       </c>
       <c r="B43" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651935</v>
+        <v>651882</v>
       </c>
       <c r="R43" t="n">
-        <v>6626058</v>
+        <v>6626177</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670627</v>
+        <v>129670649</v>
       </c>
       <c r="B44" t="n">
-        <v>91891</v>
+        <v>83042</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5214,21 +5214,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651922</v>
+        <v>651934</v>
       </c>
       <c r="R44" t="n">
-        <v>6626059</v>
+        <v>6626028</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670654</v>
+        <v>129670626</v>
       </c>
       <c r="B45" t="n">
-        <v>92243</v>
+        <v>91891</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651893</v>
+        <v>651935</v>
       </c>
       <c r="R45" t="n">
-        <v>6626104</v>
+        <v>6626058</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670619</v>
+        <v>129670627</v>
       </c>
       <c r="B46" t="n">
-        <v>92046</v>
+        <v>91891</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651882</v>
+        <v>651922</v>
       </c>
       <c r="R46" t="n">
-        <v>6626177</v>
+        <v>6626059</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6076,32 +6076,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670637</v>
+        <v>129670590</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>91614</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651703</v>
+        <v>651906</v>
       </c>
       <c r="R53" t="n">
-        <v>6626171</v>
+        <v>6626033</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6147,11 +6147,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6275,32 +6270,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670590</v>
+        <v>129670637</v>
       </c>
       <c r="B55" t="n">
-        <v>91614</v>
+        <v>98774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651906</v>
+        <v>651703</v>
       </c>
       <c r="R55" t="n">
-        <v>6626033</v>
+        <v>6626171</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6346,6 +6341,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6663,32 +6663,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129670578</v>
+        <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651796</v>
+        <v>651823</v>
       </c>
       <c r="R59" t="n">
-        <v>6626108</v>
+        <v>6626169</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6760,32 +6760,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129670605</v>
+        <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651938</v>
+        <v>651796</v>
       </c>
       <c r="R60" t="n">
-        <v>6626032</v>
+        <v>6626108</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6857,32 +6857,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129670576</v>
+        <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651928</v>
+        <v>651938</v>
       </c>
       <c r="R61" t="n">
-        <v>6626010</v>
+        <v>6626032</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6954,32 +6954,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129670623</v>
+        <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651877</v>
+        <v>651928</v>
       </c>
       <c r="R62" t="n">
-        <v>6626056</v>
+        <v>6626010</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129670615</v>
+        <v>129670623</v>
       </c>
       <c r="B63" t="n">
         <v>92046</v>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651823</v>
+        <v>651877</v>
       </c>
       <c r="R63" t="n">
-        <v>6626169</v>
+        <v>6626056</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B64" t="n">
-        <v>92046</v>
+        <v>91557</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7245,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B65" t="n">
-        <v>91557</v>
+        <v>92046</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R65" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7546,32 +7546,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670635</v>
       </c>
       <c r="B68" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651924</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626060</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,6 +7617,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7643,32 +7648,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670635</v>
+        <v>129670583</v>
       </c>
       <c r="B69" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651924</v>
+        <v>651907</v>
       </c>
       <c r="R69" t="n">
-        <v>6626060</v>
+        <v>6626130</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7714,11 +7719,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7847,7 +7847,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670574</v>
+        <v>129670573</v>
       </c>
       <c r="B71" t="n">
         <v>91593</v>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651813</v>
+        <v>651828</v>
       </c>
       <c r="R71" t="n">
-        <v>6626139</v>
+        <v>6626081</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,11 +7918,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7949,32 +7944,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670573</v>
+        <v>129670658</v>
       </c>
       <c r="B72" t="n">
-        <v>91593</v>
+        <v>92246</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651828</v>
+        <v>651860</v>
       </c>
       <c r="R72" t="n">
-        <v>6626081</v>
+        <v>6626084</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8046,32 +8041,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670658</v>
+        <v>129670574</v>
       </c>
       <c r="B73" t="n">
-        <v>92246</v>
+        <v>91593</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8076,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651860</v>
+        <v>651813</v>
       </c>
       <c r="R73" t="n">
-        <v>6626084</v>
+        <v>6626139</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8117,6 +8112,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8434,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670617</v>
+        <v>129670659</v>
       </c>
       <c r="B77" t="n">
-        <v>92046</v>
+        <v>92284</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8445,21 +8445,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651843</v>
+        <v>651798</v>
       </c>
       <c r="R77" t="n">
-        <v>6626170</v>
+        <v>6626111</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8531,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B78" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R78" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8628,32 +8628,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670659</v>
+        <v>129670581</v>
       </c>
       <c r="B79" t="n">
-        <v>92284</v>
+        <v>91593</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651798</v>
+        <v>651836</v>
       </c>
       <c r="R79" t="n">
-        <v>6626111</v>
+        <v>6626151</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B90" t="n">
-        <v>91593</v>
+        <v>105840</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R90" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B91" t="n">
-        <v>105840</v>
+        <v>91593</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R91" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9909,27 +9909,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92012</v>
+        <v>92046</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9939,10 +9944,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R92" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10001,32 +10006,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92046</v>
+        <v>92012</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R93" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10583,54 +10583,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717884</v>
+        <v>129717137</v>
       </c>
       <c r="B99" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R99" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10689,10 +10680,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717145</v>
+        <v>129716946</v>
       </c>
       <c r="B100" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10700,21 +10691,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10724,10 +10715,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651809</v>
+        <v>651888</v>
       </c>
       <c r="R100" t="n">
-        <v>6626096</v>
+        <v>6626032</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10786,32 +10777,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717137</v>
+        <v>129717145</v>
       </c>
       <c r="B101" t="n">
-        <v>91593</v>
+        <v>5197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10883,45 +10874,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129716946</v>
+        <v>129717884</v>
       </c>
       <c r="B102" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651888</v>
+        <v>651824</v>
       </c>
       <c r="R102" t="n">
-        <v>6626032</v>
+        <v>6626153</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11571,32 +11571,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129729569</v>
+        <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>91614</v>
+        <v>92246</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651836</v>
+        <v>651841</v>
       </c>
       <c r="R109" t="n">
         <v>6626143</v>
@@ -11650,6 +11650,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11668,32 +11669,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129729579</v>
+        <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>92246</v>
+        <v>91614</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11703,7 +11704,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651841</v>
+        <v>651836</v>
       </c>
       <c r="R110" t="n">
         <v>6626143</v>
@@ -11747,7 +11748,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670602</v>
+        <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651892</v>
+        <v>651866</v>
       </c>
       <c r="R14" t="n">
-        <v>6626058</v>
+        <v>6626192</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,11 +2334,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,32 +2360,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>92243</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R15" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2462,32 +2457,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670575</v>
+        <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2497,10 +2492,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651902</v>
+        <v>651890</v>
       </c>
       <c r="R16" t="n">
-        <v>6626042</v>
+        <v>6626144</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2559,32 +2554,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670653</v>
+        <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>92243</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651890</v>
+        <v>651906</v>
       </c>
       <c r="R17" t="n">
-        <v>6626144</v>
+        <v>6626091</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2656,10 +2651,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670584</v>
+        <v>129670602</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,21 +2662,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2691,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651906</v>
+        <v>651892</v>
       </c>
       <c r="R18" t="n">
-        <v>6626091</v>
+        <v>6626058</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2727,6 +2722,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670611</v>
+        <v>129670586</v>
       </c>
       <c r="B19" t="n">
-        <v>92046</v>
+        <v>92311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651780</v>
+        <v>651896</v>
       </c>
       <c r="R19" t="n">
-        <v>6626166</v>
+        <v>6626042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670618</v>
+        <v>129670611</v>
       </c>
       <c r="B20" t="n">
         <v>92046</v>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651850</v>
+        <v>651780</v>
       </c>
       <c r="R20" t="n">
-        <v>6626173</v>
+        <v>6626166</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670612</v>
+        <v>129670618</v>
       </c>
       <c r="B21" t="n">
         <v>92046</v>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651783</v>
+        <v>651850</v>
       </c>
       <c r="R21" t="n">
-        <v>6626160</v>
+        <v>6626173</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670607</v>
+        <v>129670612</v>
       </c>
       <c r="B22" t="n">
         <v>92046</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651794</v>
+        <v>651783</v>
       </c>
       <c r="R22" t="n">
-        <v>6626119</v>
+        <v>6626160</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670586</v>
+        <v>129670607</v>
       </c>
       <c r="B23" t="n">
-        <v>92311</v>
+        <v>92046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651896</v>
+        <v>651794</v>
       </c>
       <c r="R23" t="n">
-        <v>6626042</v>
+        <v>6626119</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,32 +3238,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670655</v>
+        <v>129670638</v>
       </c>
       <c r="B24" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651655</v>
+        <v>651788</v>
       </c>
       <c r="R24" t="n">
-        <v>6626179</v>
+        <v>6626118</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,6 +3309,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,7 +3340,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670656</v>
+        <v>129670655</v>
       </c>
       <c r="B25" t="n">
         <v>100963</v>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651804</v>
+        <v>651655</v>
       </c>
       <c r="R25" t="n">
-        <v>6626213</v>
+        <v>6626179</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3432,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670638</v>
+        <v>129670656</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651788</v>
+        <v>651804</v>
       </c>
       <c r="R26" t="n">
-        <v>6626118</v>
+        <v>6626213</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3503,11 +3508,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4213,10 +4213,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670644</v>
+        <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>4779</v>
+        <v>92243</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651725</v>
+        <v>651804</v>
       </c>
       <c r="R34" t="n">
-        <v>6626217</v>
+        <v>6626204</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,11 +4284,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,32 +4310,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670651</v>
+        <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>92243</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4345,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651804</v>
+        <v>651912</v>
       </c>
       <c r="R35" t="n">
-        <v>6626204</v>
+        <v>6626052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4412,10 +4407,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670585</v>
+        <v>129670601</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,21 +4418,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651912</v>
+        <v>651723</v>
       </c>
       <c r="R36" t="n">
-        <v>6626052</v>
+        <v>6626229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4483,6 +4478,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R37" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670654</v>
+        <v>129670626</v>
       </c>
       <c r="B42" t="n">
-        <v>92243</v>
+        <v>91891</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651893</v>
+        <v>651935</v>
       </c>
       <c r="R42" t="n">
-        <v>6626104</v>
+        <v>6626058</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670619</v>
+        <v>129670627</v>
       </c>
       <c r="B43" t="n">
-        <v>92046</v>
+        <v>91891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651882</v>
+        <v>651922</v>
       </c>
       <c r="R43" t="n">
-        <v>6626177</v>
+        <v>6626059</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670626</v>
+        <v>129670654</v>
       </c>
       <c r="B45" t="n">
-        <v>91891</v>
+        <v>92243</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651935</v>
+        <v>651893</v>
       </c>
       <c r="R45" t="n">
-        <v>6626058</v>
+        <v>6626104</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670627</v>
+        <v>129670619</v>
       </c>
       <c r="B46" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651922</v>
+        <v>651882</v>
       </c>
       <c r="R46" t="n">
-        <v>6626059</v>
+        <v>6626177</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670579</v>
+        <v>129670587</v>
       </c>
       <c r="B49" t="n">
-        <v>91593</v>
+        <v>92311</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651794</v>
+        <v>651796</v>
       </c>
       <c r="R49" t="n">
-        <v>6626119</v>
+        <v>6626068</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5785,32 +5785,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670621</v>
+        <v>129670590</v>
       </c>
       <c r="B50" t="n">
-        <v>92046</v>
+        <v>91614</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651904</v>
+        <v>651906</v>
       </c>
       <c r="R50" t="n">
-        <v>6626101</v>
+        <v>6626033</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670650</v>
+        <v>129670637</v>
       </c>
       <c r="B51" t="n">
-        <v>92243</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651923</v>
+        <v>651703</v>
       </c>
       <c r="R51" t="n">
-        <v>6626100</v>
+        <v>6626171</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5953,6 +5953,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5979,32 +5984,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670587</v>
+        <v>129670628</v>
       </c>
       <c r="B52" t="n">
-        <v>92311</v>
+        <v>91891</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651796</v>
+        <v>651867</v>
       </c>
       <c r="R52" t="n">
-        <v>6626068</v>
+        <v>6626099</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,10 +6081,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670590</v>
+        <v>129670579</v>
       </c>
       <c r="B53" t="n">
-        <v>91614</v>
+        <v>91593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6087,21 +6092,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651906</v>
+        <v>651794</v>
       </c>
       <c r="R53" t="n">
-        <v>6626033</v>
+        <v>6626119</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6173,32 +6178,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670628</v>
+        <v>129670621</v>
       </c>
       <c r="B54" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651867</v>
+        <v>651904</v>
       </c>
       <c r="R54" t="n">
-        <v>6626099</v>
+        <v>6626101</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6270,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670637</v>
+        <v>129670650</v>
       </c>
       <c r="B55" t="n">
-        <v>98774</v>
+        <v>92243</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651703</v>
+        <v>651923</v>
       </c>
       <c r="R55" t="n">
-        <v>6626171</v>
+        <v>6626100</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6341,11 +6346,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7148,10 +7148,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670572</v>
+        <v>129670645</v>
       </c>
       <c r="B64" t="n">
-        <v>91557</v>
+        <v>4779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7159,21 +7159,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651860</v>
+        <v>651662</v>
       </c>
       <c r="R64" t="n">
-        <v>6626196</v>
+        <v>6626158</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,6 +7219,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7342,10 +7347,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670645</v>
+        <v>129670572</v>
       </c>
       <c r="B66" t="n">
-        <v>4779</v>
+        <v>91557</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7353,21 +7358,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7377,10 +7382,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651662</v>
+        <v>651860</v>
       </c>
       <c r="R66" t="n">
-        <v>6626158</v>
+        <v>6626196</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7413,11 +7418,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7546,32 +7546,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670635</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651924</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626060</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,10 +7643,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B69" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7659,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R69" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7719,6 +7714,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670600</v>
+        <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651666</v>
+        <v>651924</v>
       </c>
       <c r="R70" t="n">
-        <v>6626239</v>
+        <v>6626060</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7847,7 +7847,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670573</v>
+        <v>129670574</v>
       </c>
       <c r="B71" t="n">
         <v>91593</v>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651828</v>
+        <v>651813</v>
       </c>
       <c r="R71" t="n">
-        <v>6626081</v>
+        <v>6626139</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,6 +7918,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7944,32 +7949,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670658</v>
+        <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>92246</v>
+        <v>91593</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7979,10 +7984,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651860</v>
+        <v>651828</v>
       </c>
       <c r="R72" t="n">
-        <v>6626084</v>
+        <v>6626081</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8041,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670574</v>
+        <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>91593</v>
+        <v>92246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8076,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651813</v>
+        <v>651860</v>
       </c>
       <c r="R73" t="n">
-        <v>6626139</v>
+        <v>6626084</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8112,11 +8117,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670630</v>
+        <v>129670659</v>
       </c>
       <c r="B75" t="n">
-        <v>91366</v>
+        <v>92284</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3215</v>
+        <v>898</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651671</v>
+        <v>651798</v>
       </c>
       <c r="R75" t="n">
-        <v>6626205</v>
+        <v>6626111</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8337,32 +8337,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670614</v>
+        <v>129670630</v>
       </c>
       <c r="B76" t="n">
-        <v>92046</v>
+        <v>91366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651826</v>
+        <v>651671</v>
       </c>
       <c r="R76" t="n">
-        <v>6626121</v>
+        <v>6626205</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8434,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670659</v>
+        <v>129670636</v>
       </c>
       <c r="B77" t="n">
-        <v>92284</v>
+        <v>98774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8445,21 +8445,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651798</v>
+        <v>651666</v>
       </c>
       <c r="R77" t="n">
-        <v>6626111</v>
+        <v>6626156</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8505,6 +8505,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8531,7 +8536,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670617</v>
+        <v>129670614</v>
       </c>
       <c r="B78" t="n">
         <v>92046</v>
@@ -8566,10 +8571,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651843</v>
+        <v>651826</v>
       </c>
       <c r="R78" t="n">
-        <v>6626170</v>
+        <v>6626121</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8628,32 +8633,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B79" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8668,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R79" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8725,10 +8730,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670598</v>
+        <v>129670581</v>
       </c>
       <c r="B80" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8736,21 +8741,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8760,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651789</v>
+        <v>651836</v>
       </c>
       <c r="R80" t="n">
-        <v>6626199</v>
+        <v>6626151</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8796,11 +8801,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670636</v>
+        <v>129670598</v>
       </c>
       <c r="B81" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651666</v>
+        <v>651789</v>
       </c>
       <c r="R81" t="n">
-        <v>6626156</v>
+        <v>6626199</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670646</v>
+        <v>129670606</v>
       </c>
       <c r="B85" t="n">
-        <v>4779</v>
+        <v>92046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651847</v>
+        <v>651875</v>
       </c>
       <c r="R85" t="n">
-        <v>6626179</v>
+        <v>6626072</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9296,11 +9296,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9327,32 +9322,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670606</v>
+        <v>129670646</v>
       </c>
       <c r="B86" t="n">
-        <v>92046</v>
+        <v>4779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651875</v>
+        <v>651847</v>
       </c>
       <c r="R86" t="n">
-        <v>6626072</v>
+        <v>6626179</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9398,6 +9393,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>105840</v>
+        <v>91593</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R90" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>91593</v>
+        <v>105840</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R91" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10583,32 +10583,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717137</v>
+        <v>129716946</v>
       </c>
       <c r="B99" t="n">
-        <v>91593</v>
+        <v>5177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10618,10 +10618,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651809</v>
+        <v>651888</v>
       </c>
       <c r="R99" t="n">
-        <v>6626096</v>
+        <v>6626032</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716946</v>
+        <v>129717145</v>
       </c>
       <c r="B100" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10691,21 +10691,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651888</v>
+        <v>651809</v>
       </c>
       <c r="R100" t="n">
-        <v>6626032</v>
+        <v>6626096</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10777,45 +10777,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B101" t="n">
-        <v>5197</v>
+        <v>98774</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R101" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10874,54 +10883,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717884</v>
+        <v>129717137</v>
       </c>
       <c r="B102" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R102" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670611</v>
+        <v>129670638</v>
       </c>
       <c r="B20" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651780</v>
+        <v>651788</v>
       </c>
       <c r="R20" t="n">
-        <v>6626166</v>
+        <v>6626118</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2921,6 +2921,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,32 +2952,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670618</v>
+        <v>129670655</v>
       </c>
       <c r="B21" t="n">
-        <v>92046</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651850</v>
+        <v>651655</v>
       </c>
       <c r="R21" t="n">
-        <v>6626173</v>
+        <v>6626179</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,32 +3049,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670612</v>
+        <v>129670656</v>
       </c>
       <c r="B22" t="n">
-        <v>92046</v>
+        <v>100963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651783</v>
+        <v>651804</v>
       </c>
       <c r="R22" t="n">
-        <v>6626160</v>
+        <v>6626213</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,7 +3146,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670607</v>
+        <v>129670611</v>
       </c>
       <c r="B23" t="n">
         <v>92046</v>
@@ -3176,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651794</v>
+        <v>651780</v>
       </c>
       <c r="R23" t="n">
-        <v>6626119</v>
+        <v>6626166</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670638</v>
+        <v>129670618</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,21 +3254,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651788</v>
+        <v>651850</v>
       </c>
       <c r="R24" t="n">
-        <v>6626118</v>
+        <v>6626173</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,11 +3314,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670655</v>
+        <v>129670612</v>
       </c>
       <c r="B25" t="n">
-        <v>100963</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651655</v>
+        <v>651783</v>
       </c>
       <c r="R25" t="n">
-        <v>6626179</v>
+        <v>6626160</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670656</v>
+        <v>129670607</v>
       </c>
       <c r="B26" t="n">
-        <v>100963</v>
+        <v>92046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651804</v>
+        <v>651794</v>
       </c>
       <c r="R26" t="n">
-        <v>6626213</v>
+        <v>6626119</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3631,32 +3631,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670620</v>
+        <v>129670592</v>
       </c>
       <c r="B28" t="n">
-        <v>92046</v>
+        <v>91614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651894</v>
+        <v>651842</v>
       </c>
       <c r="R28" t="n">
-        <v>6626133</v>
+        <v>6626152</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670577</v>
+        <v>129670657</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>92246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651934</v>
+        <v>651836</v>
       </c>
       <c r="R29" t="n">
-        <v>6626035</v>
+        <v>6626075</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670582</v>
+        <v>129670620</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651839</v>
+        <v>651894</v>
       </c>
       <c r="R30" t="n">
-        <v>6626178</v>
+        <v>6626133</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,32 +3922,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670625</v>
+        <v>129670577</v>
       </c>
       <c r="B31" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651793</v>
+        <v>651934</v>
       </c>
       <c r="R31" t="n">
-        <v>6626135</v>
+        <v>6626035</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670657</v>
+        <v>129670582</v>
       </c>
       <c r="B32" t="n">
-        <v>92246</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651836</v>
+        <v>651839</v>
       </c>
       <c r="R32" t="n">
-        <v>6626075</v>
+        <v>6626178</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670592</v>
+        <v>129670625</v>
       </c>
       <c r="B33" t="n">
-        <v>91614</v>
+        <v>92046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651842</v>
+        <v>651793</v>
       </c>
       <c r="R33" t="n">
-        <v>6626152</v>
+        <v>6626135</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4407,32 +4407,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R36" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R37" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670626</v>
+        <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>91891</v>
+        <v>92243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651935</v>
+        <v>651893</v>
       </c>
       <c r="R42" t="n">
-        <v>6626058</v>
+        <v>6626104</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670627</v>
+        <v>129670619</v>
       </c>
       <c r="B43" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651922</v>
+        <v>651882</v>
       </c>
       <c r="R43" t="n">
-        <v>6626059</v>
+        <v>6626177</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670654</v>
+        <v>129670626</v>
       </c>
       <c r="B45" t="n">
-        <v>92243</v>
+        <v>91891</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651893</v>
+        <v>651935</v>
       </c>
       <c r="R45" t="n">
-        <v>6626104</v>
+        <v>6626058</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670619</v>
+        <v>129670627</v>
       </c>
       <c r="B46" t="n">
-        <v>92046</v>
+        <v>91891</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651882</v>
+        <v>651922</v>
       </c>
       <c r="R46" t="n">
-        <v>6626177</v>
+        <v>6626059</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670587</v>
+        <v>129670637</v>
       </c>
       <c r="B49" t="n">
-        <v>92311</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651796</v>
+        <v>651703</v>
       </c>
       <c r="R49" t="n">
-        <v>6626068</v>
+        <v>6626171</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5759,6 +5759,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5785,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670590</v>
+        <v>129670579</v>
       </c>
       <c r="B50" t="n">
-        <v>91614</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5796,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651906</v>
+        <v>651794</v>
       </c>
       <c r="R50" t="n">
-        <v>6626033</v>
+        <v>6626119</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,10 +5887,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670637</v>
+        <v>129670621</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>92046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5893,21 +5898,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5922,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651703</v>
+        <v>651904</v>
       </c>
       <c r="R51" t="n">
-        <v>6626171</v>
+        <v>6626101</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5953,11 +5958,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5984,32 +5984,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670628</v>
+        <v>129670650</v>
       </c>
       <c r="B52" t="n">
-        <v>91891</v>
+        <v>92243</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6019,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651867</v>
+        <v>651923</v>
       </c>
       <c r="R52" t="n">
-        <v>6626099</v>
+        <v>6626100</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6081,32 +6081,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670579</v>
+        <v>129670587</v>
       </c>
       <c r="B53" t="n">
-        <v>91593</v>
+        <v>92311</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651794</v>
+        <v>651796</v>
       </c>
       <c r="R53" t="n">
-        <v>6626119</v>
+        <v>6626068</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6178,32 +6178,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670621</v>
+        <v>129670628</v>
       </c>
       <c r="B54" t="n">
-        <v>92046</v>
+        <v>91891</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651904</v>
+        <v>651867</v>
       </c>
       <c r="R54" t="n">
-        <v>6626101</v>
+        <v>6626099</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6275,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670650</v>
+        <v>129670590</v>
       </c>
       <c r="B55" t="n">
-        <v>92243</v>
+        <v>91614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1339</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651923</v>
+        <v>651906</v>
       </c>
       <c r="R55" t="n">
-        <v>6626100</v>
+        <v>6626033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670645</v>
+        <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>4779</v>
+        <v>92046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651662</v>
+        <v>651791</v>
       </c>
       <c r="R64" t="n">
-        <v>6626158</v>
+        <v>6626110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,11 +7219,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7250,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>92046</v>
+        <v>91557</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R65" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7347,10 +7342,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670572</v>
+        <v>129670645</v>
       </c>
       <c r="B66" t="n">
-        <v>91557</v>
+        <v>4779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7358,21 +7353,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7377,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651860</v>
+        <v>651662</v>
       </c>
       <c r="R66" t="n">
-        <v>6626196</v>
+        <v>6626158</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7418,6 +7413,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8240,10 +8240,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670659</v>
+        <v>129670614</v>
       </c>
       <c r="B75" t="n">
-        <v>92284</v>
+        <v>92046</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,21 +8251,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651798</v>
+        <v>651826</v>
       </c>
       <c r="R75" t="n">
-        <v>6626111</v>
+        <v>6626121</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8337,32 +8337,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670630</v>
+        <v>129670659</v>
       </c>
       <c r="B76" t="n">
-        <v>91366</v>
+        <v>92284</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3215</v>
+        <v>898</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651671</v>
+        <v>651798</v>
       </c>
       <c r="R76" t="n">
-        <v>6626205</v>
+        <v>6626111</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8434,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670636</v>
+        <v>129670617</v>
       </c>
       <c r="B77" t="n">
-        <v>98774</v>
+        <v>92046</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8445,21 +8445,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651666</v>
+        <v>651843</v>
       </c>
       <c r="R77" t="n">
-        <v>6626156</v>
+        <v>6626170</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8505,11 +8505,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8536,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670614</v>
+        <v>129670581</v>
       </c>
       <c r="B78" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651826</v>
+        <v>651836</v>
       </c>
       <c r="R78" t="n">
-        <v>6626121</v>
+        <v>6626151</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8633,32 +8628,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670617</v>
+        <v>129670598</v>
       </c>
       <c r="B79" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8668,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651843</v>
+        <v>651789</v>
       </c>
       <c r="R79" t="n">
-        <v>6626170</v>
+        <v>6626199</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8704,6 +8699,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8730,32 +8730,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670581</v>
+        <v>129670630</v>
       </c>
       <c r="B80" t="n">
-        <v>91593</v>
+        <v>91366</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651836</v>
+        <v>651671</v>
       </c>
       <c r="R80" t="n">
-        <v>6626151</v>
+        <v>6626205</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670598</v>
+        <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651789</v>
+        <v>651666</v>
       </c>
       <c r="R81" t="n">
-        <v>6626199</v>
+        <v>6626156</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Flyg och landningsläte</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670591</v>
+        <v>129670606</v>
       </c>
       <c r="B84" t="n">
-        <v>91614</v>
+        <v>92046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651709</v>
+        <v>651875</v>
       </c>
       <c r="R84" t="n">
-        <v>6626216</v>
+        <v>6626072</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670606</v>
+        <v>129670591</v>
       </c>
       <c r="B85" t="n">
-        <v>92046</v>
+        <v>91614</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651875</v>
+        <v>651709</v>
       </c>
       <c r="R85" t="n">
-        <v>6626072</v>
+        <v>6626216</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B89" t="n">
-        <v>98774</v>
+        <v>92046</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10583,45 +10583,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129716946</v>
+        <v>129717884</v>
       </c>
       <c r="B99" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651888</v>
+        <v>651824</v>
       </c>
       <c r="R99" t="n">
-        <v>6626032</v>
+        <v>6626153</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10680,32 +10689,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717145</v>
+        <v>129717137</v>
       </c>
       <c r="B100" t="n">
-        <v>5197</v>
+        <v>91593</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10777,54 +10786,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717884</v>
+        <v>129716946</v>
       </c>
       <c r="B101" t="n">
-        <v>98774</v>
+        <v>5177</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651824</v>
+        <v>651888</v>
       </c>
       <c r="R101" t="n">
-        <v>6626153</v>
+        <v>6626032</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10883,32 +10883,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717137</v>
+        <v>129717145</v>
       </c>
       <c r="B102" t="n">
-        <v>91593</v>
+        <v>5197</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12348,32 +12348,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729575</v>
+        <v>129729570</v>
       </c>
       <c r="B117" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651890</v>
+        <v>651833</v>
       </c>
       <c r="R117" t="n">
-        <v>6626043</v>
+        <v>6626152</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,32 +12445,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729570</v>
+        <v>129729575</v>
       </c>
       <c r="B118" t="n">
-        <v>92046</v>
+        <v>91891</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651833</v>
+        <v>651890</v>
       </c>
       <c r="R118" t="n">
-        <v>6626152</v>
+        <v>6626043</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670652</v>
+        <v>129670602</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651866</v>
+        <v>651892</v>
       </c>
       <c r="R14" t="n">
-        <v>6626192</v>
+        <v>6626058</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,6 +2334,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2360,32 +2365,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670575</v>
+        <v>129670652</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>92247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651902</v>
+        <v>651866</v>
       </c>
       <c r="R15" t="n">
-        <v>6626042</v>
+        <v>6626192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,32 +2462,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670653</v>
+        <v>129670575</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>91597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2492,10 +2497,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651890</v>
+        <v>651902</v>
       </c>
       <c r="R16" t="n">
-        <v>6626144</v>
+        <v>6626042</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2554,32 +2559,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670584</v>
+        <v>129670653</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>92247</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651906</v>
+        <v>651890</v>
       </c>
       <c r="R17" t="n">
-        <v>6626091</v>
+        <v>6626144</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2651,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670602</v>
+        <v>129670584</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,21 +2667,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2686,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651892</v>
+        <v>651906</v>
       </c>
       <c r="R18" t="n">
-        <v>6626058</v>
+        <v>6626091</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2722,11 +2727,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670586</v>
+        <v>129670638</v>
       </c>
       <c r="B19" t="n">
-        <v>92311</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651896</v>
+        <v>651788</v>
       </c>
       <c r="R19" t="n">
-        <v>6626042</v>
+        <v>6626118</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,6 +2824,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,32 +2855,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670638</v>
+        <v>129670655</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>100967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651788</v>
+        <v>651655</v>
       </c>
       <c r="R20" t="n">
-        <v>6626118</v>
+        <v>6626179</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2921,11 +2926,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670655</v>
+        <v>129670656</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651655</v>
+        <v>651804</v>
       </c>
       <c r="R21" t="n">
-        <v>6626179</v>
+        <v>6626213</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670656</v>
+        <v>129670586</v>
       </c>
       <c r="B22" t="n">
-        <v>100963</v>
+        <v>92315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651804</v>
+        <v>651896</v>
       </c>
       <c r="R22" t="n">
-        <v>6626213</v>
+        <v>6626042</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3149,7 +3149,7 @@
         <v>129670611</v>
       </c>
       <c r="B23" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>129670618</v>
       </c>
       <c r="B24" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>129670612</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>129670607</v>
       </c>
       <c r="B26" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,32 +3631,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670592</v>
+        <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>91614</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651842</v>
+        <v>651894</v>
       </c>
       <c r="R28" t="n">
-        <v>6626152</v>
+        <v>6626133</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670657</v>
+        <v>129670577</v>
       </c>
       <c r="B29" t="n">
-        <v>92246</v>
+        <v>91597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651836</v>
+        <v>651934</v>
       </c>
       <c r="R29" t="n">
-        <v>6626075</v>
+        <v>6626035</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670620</v>
+        <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>92046</v>
+        <v>91597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651894</v>
+        <v>651839</v>
       </c>
       <c r="R30" t="n">
-        <v>6626133</v>
+        <v>6626178</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,32 +3922,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670577</v>
+        <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>92050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651934</v>
+        <v>651793</v>
       </c>
       <c r="R31" t="n">
-        <v>6626035</v>
+        <v>6626135</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670582</v>
+        <v>129670592</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>91618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,21 +4030,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651839</v>
+        <v>651842</v>
       </c>
       <c r="R32" t="n">
-        <v>6626178</v>
+        <v>6626152</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670625</v>
+        <v>129670657</v>
       </c>
       <c r="B33" t="n">
-        <v>92046</v>
+        <v>92250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651793</v>
+        <v>651836</v>
       </c>
       <c r="R33" t="n">
-        <v>6626135</v>
+        <v>6626075</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4216,7 +4216,7 @@
         <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4407,32 +4407,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B36" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R36" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R37" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670610</v>
+        <v>129670599</v>
       </c>
       <c r="B39" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651780</v>
+        <v>651890</v>
       </c>
       <c r="R39" t="n">
-        <v>6626169</v>
+        <v>6626039</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,6 +4779,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,32 +4810,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670599</v>
+        <v>129670647</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651890</v>
+        <v>651851</v>
       </c>
       <c r="R40" t="n">
-        <v>6626039</v>
+        <v>6626154</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4880,7 +4885,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4912,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4978,11 +4983,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,7 +5012,7 @@
         <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>129670619</v>
       </c>
       <c r="B43" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670649</v>
+        <v>129670626</v>
       </c>
       <c r="B44" t="n">
-        <v>83042</v>
+        <v>91895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5214,21 +5214,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651934</v>
+        <v>651935</v>
       </c>
       <c r="R44" t="n">
-        <v>6626028</v>
+        <v>6626058</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670626</v>
+        <v>129670627</v>
       </c>
       <c r="B45" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651935</v>
+        <v>651922</v>
       </c>
       <c r="R45" t="n">
-        <v>6626058</v>
+        <v>6626059</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670627</v>
+        <v>129670649</v>
       </c>
       <c r="B46" t="n">
-        <v>91891</v>
+        <v>83042</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651922</v>
+        <v>651934</v>
       </c>
       <c r="R46" t="n">
-        <v>6626059</v>
+        <v>6626028</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670637</v>
+        <v>129670587</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>92315</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651703</v>
+        <v>651796</v>
       </c>
       <c r="R49" t="n">
-        <v>6626171</v>
+        <v>6626068</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5759,11 +5759,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5793,7 +5788,7 @@
         <v>129670579</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5890,7 +5885,7 @@
         <v>129670621</v>
       </c>
       <c r="B51" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,32 +5979,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670650</v>
+        <v>129670628</v>
       </c>
       <c r="B52" t="n">
-        <v>92243</v>
+        <v>91895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6019,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651923</v>
+        <v>651867</v>
       </c>
       <c r="R52" t="n">
-        <v>6626100</v>
+        <v>6626099</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6081,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670587</v>
+        <v>129670650</v>
       </c>
       <c r="B53" t="n">
-        <v>92311</v>
+        <v>92247</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6092,21 +6087,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651796</v>
+        <v>651923</v>
       </c>
       <c r="R53" t="n">
-        <v>6626068</v>
+        <v>6626100</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6178,10 +6173,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670628</v>
+        <v>129670590</v>
       </c>
       <c r="B54" t="n">
-        <v>91891</v>
+        <v>91618</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6189,21 +6184,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6213,10 +6208,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651867</v>
+        <v>651906</v>
       </c>
       <c r="R54" t="n">
-        <v>6626099</v>
+        <v>6626033</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6275,32 +6270,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670590</v>
+        <v>129670637</v>
       </c>
       <c r="B55" t="n">
-        <v>91614</v>
+        <v>98778</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651906</v>
+        <v>651703</v>
       </c>
       <c r="R55" t="n">
-        <v>6626033</v>
+        <v>6626171</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6346,6 +6341,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B64" t="n">
-        <v>92046</v>
+        <v>91561</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7245,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B65" t="n">
-        <v>91557</v>
+        <v>92050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R65" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B68" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,6 +7617,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7643,10 +7648,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>91597</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7654,21 +7659,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R69" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7714,11 +7719,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7748,7 +7748,7 @@
         <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670614</v>
+        <v>129670630</v>
       </c>
       <c r="B75" t="n">
-        <v>92046</v>
+        <v>91370</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651826</v>
+        <v>651671</v>
       </c>
       <c r="R75" t="n">
-        <v>6626121</v>
+        <v>6626205</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8337,10 +8337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670659</v>
+        <v>129670614</v>
       </c>
       <c r="B76" t="n">
-        <v>92284</v>
+        <v>92050</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,21 +8348,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651798</v>
+        <v>651826</v>
       </c>
       <c r="R76" t="n">
-        <v>6626111</v>
+        <v>6626121</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8434,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670617</v>
+        <v>129670659</v>
       </c>
       <c r="B77" t="n">
-        <v>92046</v>
+        <v>92288</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8445,21 +8445,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651843</v>
+        <v>651798</v>
       </c>
       <c r="R77" t="n">
-        <v>6626170</v>
+        <v>6626111</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8531,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B78" t="n">
-        <v>91593</v>
+        <v>92050</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R78" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8628,10 +8628,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670598</v>
+        <v>129670581</v>
       </c>
       <c r="B79" t="n">
-        <v>57733</v>
+        <v>91597</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8639,21 +8639,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651789</v>
+        <v>651836</v>
       </c>
       <c r="R79" t="n">
-        <v>6626199</v>
+        <v>6626151</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8699,11 +8699,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8730,32 +8725,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670630</v>
+        <v>129670598</v>
       </c>
       <c r="B80" t="n">
-        <v>91366</v>
+        <v>57733</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8760,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651671</v>
+        <v>651789</v>
       </c>
       <c r="R80" t="n">
-        <v>6626205</v>
+        <v>6626199</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8801,6 +8796,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8830,7 +8830,7 @@
         <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B82" t="n">
-        <v>92046</v>
+        <v>98778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R82" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,6 +9000,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9026,10 +9031,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B83" t="n">
-        <v>98774</v>
+        <v>92050</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9037,21 +9042,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9061,10 +9066,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R83" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9097,11 +9102,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670606</v>
+        <v>129670646</v>
       </c>
       <c r="B84" t="n">
-        <v>92046</v>
+        <v>4779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651875</v>
+        <v>651847</v>
       </c>
       <c r="R84" t="n">
-        <v>6626072</v>
+        <v>6626179</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9199,6 +9199,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9225,32 +9230,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670591</v>
+        <v>129670606</v>
       </c>
       <c r="B85" t="n">
-        <v>91614</v>
+        <v>92050</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9265,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651709</v>
+        <v>651875</v>
       </c>
       <c r="R85" t="n">
-        <v>6626216</v>
+        <v>6626072</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9322,32 +9327,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670646</v>
+        <v>129670591</v>
       </c>
       <c r="B86" t="n">
-        <v>4779</v>
+        <v>91618</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651847</v>
+        <v>651709</v>
       </c>
       <c r="R86" t="n">
-        <v>6626179</v>
+        <v>6626216</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,11 +9398,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9524,7 +9524,7 @@
         <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>129718132</v>
       </c>
       <c r="B89" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B90" t="n">
-        <v>91593</v>
+        <v>105844</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R90" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B91" t="n">
-        <v>105840</v>
+        <v>91597</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R91" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9912,7 +9912,7 @@
         <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92012</v>
+        <v>92016</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10583,54 +10583,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717884</v>
+        <v>129717145</v>
       </c>
       <c r="B99" t="n">
-        <v>98774</v>
+        <v>5197</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R99" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10689,45 +10680,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717137</v>
+        <v>129717884</v>
       </c>
       <c r="B100" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R100" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10883,32 +10883,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717145</v>
+        <v>129717137</v>
       </c>
       <c r="B102" t="n">
-        <v>5197</v>
+        <v>91597</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10983,7 +10983,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12348,32 +12348,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729570</v>
+        <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>92046</v>
+        <v>91895</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651833</v>
+        <v>651890</v>
       </c>
       <c r="R117" t="n">
-        <v>6626152</v>
+        <v>6626043</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,32 +12445,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729575</v>
+        <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>91891</v>
+        <v>92050</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651890</v>
+        <v>651833</v>
       </c>
       <c r="R118" t="n">
-        <v>6626043</v>
+        <v>6626152</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12545,7 +12545,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670602</v>
+        <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>92249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651892</v>
+        <v>651866</v>
       </c>
       <c r="R14" t="n">
-        <v>6626058</v>
+        <v>6626192</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2334,11 +2334,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,32 +2360,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>92247</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R15" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2462,32 +2457,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670575</v>
+        <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>91597</v>
+        <v>92249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2497,10 +2492,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651902</v>
+        <v>651890</v>
       </c>
       <c r="R16" t="n">
-        <v>6626042</v>
+        <v>6626144</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2559,32 +2554,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670653</v>
+        <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>92247</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651890</v>
+        <v>651906</v>
       </c>
       <c r="R17" t="n">
-        <v>6626144</v>
+        <v>6626091</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2656,10 +2651,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670584</v>
+        <v>129670602</v>
       </c>
       <c r="B18" t="n">
-        <v>91597</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,21 +2662,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2691,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651906</v>
+        <v>651892</v>
       </c>
       <c r="R18" t="n">
-        <v>6626091</v>
+        <v>6626058</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2727,6 +2722,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2756,7 +2756,7 @@
         <v>129670638</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129670655</v>
       </c>
       <c r="B20" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129670656</v>
       </c>
       <c r="B21" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,32 +3049,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670586</v>
+        <v>129670611</v>
       </c>
       <c r="B22" t="n">
-        <v>92315</v>
+        <v>92052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651896</v>
+        <v>651780</v>
       </c>
       <c r="R22" t="n">
-        <v>6626042</v>
+        <v>6626166</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670611</v>
+        <v>129670618</v>
       </c>
       <c r="B23" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651780</v>
+        <v>651850</v>
       </c>
       <c r="R23" t="n">
-        <v>6626166</v>
+        <v>6626173</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670618</v>
+        <v>129670612</v>
       </c>
       <c r="B24" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651850</v>
+        <v>651783</v>
       </c>
       <c r="R24" t="n">
-        <v>6626173</v>
+        <v>6626160</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670612</v>
+        <v>129670607</v>
       </c>
       <c r="B25" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651783</v>
+        <v>651794</v>
       </c>
       <c r="R25" t="n">
-        <v>6626160</v>
+        <v>6626119</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670607</v>
+        <v>129670586</v>
       </c>
       <c r="B26" t="n">
-        <v>92050</v>
+        <v>92317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651794</v>
+        <v>651896</v>
       </c>
       <c r="R26" t="n">
-        <v>6626119</v>
+        <v>6626042</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,32 +3631,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670620</v>
+        <v>129670592</v>
       </c>
       <c r="B28" t="n">
-        <v>92050</v>
+        <v>91620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651894</v>
+        <v>651842</v>
       </c>
       <c r="R28" t="n">
-        <v>6626133</v>
+        <v>6626152</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670577</v>
+        <v>129670657</v>
       </c>
       <c r="B29" t="n">
-        <v>91597</v>
+        <v>92252</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651934</v>
+        <v>651836</v>
       </c>
       <c r="R29" t="n">
-        <v>6626035</v>
+        <v>6626075</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670582</v>
+        <v>129670620</v>
       </c>
       <c r="B30" t="n">
-        <v>91597</v>
+        <v>92052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651839</v>
+        <v>651894</v>
       </c>
       <c r="R30" t="n">
-        <v>6626178</v>
+        <v>6626133</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,32 +3922,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670625</v>
+        <v>129670577</v>
       </c>
       <c r="B31" t="n">
-        <v>92050</v>
+        <v>91599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651793</v>
+        <v>651934</v>
       </c>
       <c r="R31" t="n">
-        <v>6626135</v>
+        <v>6626035</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670592</v>
+        <v>129670582</v>
       </c>
       <c r="B32" t="n">
-        <v>91618</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,21 +4030,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651842</v>
+        <v>651839</v>
       </c>
       <c r="R32" t="n">
-        <v>6626152</v>
+        <v>6626178</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670657</v>
+        <v>129670625</v>
       </c>
       <c r="B33" t="n">
-        <v>92250</v>
+        <v>92052</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651836</v>
+        <v>651793</v>
       </c>
       <c r="R33" t="n">
-        <v>6626075</v>
+        <v>6626135</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4216,7 +4216,7 @@
         <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670654</v>
+        <v>129670649</v>
       </c>
       <c r="B42" t="n">
-        <v>92247</v>
+        <v>83044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651893</v>
+        <v>651934</v>
       </c>
       <c r="R42" t="n">
-        <v>6626104</v>
+        <v>6626028</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670619</v>
+        <v>129670626</v>
       </c>
       <c r="B43" t="n">
-        <v>92050</v>
+        <v>91897</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651882</v>
+        <v>651935</v>
       </c>
       <c r="R43" t="n">
-        <v>6626177</v>
+        <v>6626058</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670626</v>
+        <v>129670627</v>
       </c>
       <c r="B44" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651935</v>
+        <v>651922</v>
       </c>
       <c r="R44" t="n">
-        <v>6626058</v>
+        <v>6626059</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670627</v>
+        <v>129670654</v>
       </c>
       <c r="B45" t="n">
-        <v>91895</v>
+        <v>92249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651922</v>
+        <v>651893</v>
       </c>
       <c r="R45" t="n">
-        <v>6626059</v>
+        <v>6626104</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670649</v>
+        <v>129670619</v>
       </c>
       <c r="B46" t="n">
-        <v>83042</v>
+        <v>92052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651934</v>
+        <v>651882</v>
       </c>
       <c r="R46" t="n">
-        <v>6626028</v>
+        <v>6626177</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5688,32 +5688,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670587</v>
+        <v>129670628</v>
       </c>
       <c r="B49" t="n">
-        <v>92315</v>
+        <v>91897</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651796</v>
+        <v>651867</v>
       </c>
       <c r="R49" t="n">
-        <v>6626068</v>
+        <v>6626099</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5788,7 +5788,7 @@
         <v>129670579</v>
       </c>
       <c r="B50" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129670621</v>
       </c>
       <c r="B51" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5979,32 +5979,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670628</v>
+        <v>129670650</v>
       </c>
       <c r="B52" t="n">
-        <v>91895</v>
+        <v>92249</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651867</v>
+        <v>651923</v>
       </c>
       <c r="R52" t="n">
-        <v>6626099</v>
+        <v>6626100</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670650</v>
+        <v>129670587</v>
       </c>
       <c r="B53" t="n">
-        <v>92247</v>
+        <v>92317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1339</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651923</v>
+        <v>651796</v>
       </c>
       <c r="R53" t="n">
-        <v>6626100</v>
+        <v>6626068</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6173,32 +6173,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670590</v>
+        <v>129670637</v>
       </c>
       <c r="B54" t="n">
-        <v>91618</v>
+        <v>98780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651906</v>
+        <v>651703</v>
       </c>
       <c r="R54" t="n">
-        <v>6626033</v>
+        <v>6626171</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6244,6 +6244,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6270,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670637</v>
+        <v>129670590</v>
       </c>
       <c r="B55" t="n">
-        <v>98778</v>
+        <v>91620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651703</v>
+        <v>651906</v>
       </c>
       <c r="R55" t="n">
-        <v>6626171</v>
+        <v>6626033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6341,11 +6346,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>91561</v>
+        <v>92052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R64" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7245,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670624</v>
+        <v>129670645</v>
       </c>
       <c r="B65" t="n">
-        <v>92050</v>
+        <v>4779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651791</v>
+        <v>651662</v>
       </c>
       <c r="R65" t="n">
-        <v>6626110</v>
+        <v>6626158</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7316,6 +7316,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7342,10 +7347,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670645</v>
+        <v>129670572</v>
       </c>
       <c r="B66" t="n">
-        <v>4779</v>
+        <v>91563</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7353,21 +7358,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7377,10 +7382,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651662</v>
+        <v>651860</v>
       </c>
       <c r="R66" t="n">
-        <v>6626158</v>
+        <v>6626196</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7413,11 +7418,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,32 +7643,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670583</v>
+        <v>129670635</v>
       </c>
       <c r="B69" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651907</v>
+        <v>651924</v>
       </c>
       <c r="R69" t="n">
-        <v>6626130</v>
+        <v>6626060</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7719,6 +7714,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670635</v>
+        <v>129670600</v>
       </c>
       <c r="B70" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651924</v>
+        <v>651666</v>
       </c>
       <c r="R70" t="n">
-        <v>6626060</v>
+        <v>6626239</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7847,32 +7847,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670574</v>
+        <v>129670658</v>
       </c>
       <c r="B71" t="n">
-        <v>91597</v>
+        <v>92252</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651813</v>
+        <v>651860</v>
       </c>
       <c r="R71" t="n">
-        <v>6626139</v>
+        <v>6626084</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,11 +7918,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7949,10 +7944,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670573</v>
+        <v>129670574</v>
       </c>
       <c r="B72" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651828</v>
+        <v>651813</v>
       </c>
       <c r="R72" t="n">
-        <v>6626081</v>
+        <v>6626139</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8020,6 +8015,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8046,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670658</v>
+        <v>129670573</v>
       </c>
       <c r="B73" t="n">
-        <v>92250</v>
+        <v>91599</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651860</v>
+        <v>651828</v>
       </c>
       <c r="R73" t="n">
-        <v>6626084</v>
+        <v>6626081</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670630</v>
+        <v>129670636</v>
       </c>
       <c r="B75" t="n">
-        <v>91370</v>
+        <v>98780</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651671</v>
+        <v>651666</v>
       </c>
       <c r="R75" t="n">
-        <v>6626205</v>
+        <v>6626156</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8311,6 +8311,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8337,32 +8342,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670614</v>
+        <v>129670598</v>
       </c>
       <c r="B76" t="n">
-        <v>92050</v>
+        <v>57733</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651826</v>
+        <v>651789</v>
       </c>
       <c r="R76" t="n">
-        <v>6626121</v>
+        <v>6626199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8408,6 +8413,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8434,10 +8444,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670659</v>
+        <v>129670614</v>
       </c>
       <c r="B77" t="n">
-        <v>92288</v>
+        <v>92052</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8445,21 +8455,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8479,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651798</v>
+        <v>651826</v>
       </c>
       <c r="R77" t="n">
-        <v>6626111</v>
+        <v>6626121</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8531,10 +8541,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670617</v>
+        <v>129670659</v>
       </c>
       <c r="B78" t="n">
-        <v>92050</v>
+        <v>92290</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8542,21 +8552,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8566,10 +8576,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651843</v>
+        <v>651798</v>
       </c>
       <c r="R78" t="n">
-        <v>6626170</v>
+        <v>6626111</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8628,32 +8638,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B79" t="n">
-        <v>91597</v>
+        <v>92052</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8673,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R79" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8725,10 +8735,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670598</v>
+        <v>129670581</v>
       </c>
       <c r="B80" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8736,21 +8746,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8760,10 +8770,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651789</v>
+        <v>651836</v>
       </c>
       <c r="R80" t="n">
-        <v>6626199</v>
+        <v>6626151</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8796,11 +8806,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8827,32 +8832,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670636</v>
+        <v>129670630</v>
       </c>
       <c r="B81" t="n">
-        <v>98778</v>
+        <v>91372</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651666</v>
+        <v>651671</v>
       </c>
       <c r="R81" t="n">
-        <v>6626156</v>
+        <v>6626205</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8898,11 +8903,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B82" t="n">
-        <v>98778</v>
+        <v>92052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R82" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,11 +9000,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9031,10 +9026,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>92050</v>
+        <v>98780</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9042,21 +9037,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R83" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9102,6 +9097,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670646</v>
+        <v>129670591</v>
       </c>
       <c r="B84" t="n">
-        <v>4779</v>
+        <v>91620</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651847</v>
+        <v>651709</v>
       </c>
       <c r="R84" t="n">
-        <v>6626179</v>
+        <v>6626216</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9199,11 +9199,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9233,7 +9228,7 @@
         <v>129670606</v>
       </c>
       <c r="B85" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9327,32 +9322,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670591</v>
+        <v>129670646</v>
       </c>
       <c r="B86" t="n">
-        <v>91618</v>
+        <v>4779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651709</v>
+        <v>651847</v>
       </c>
       <c r="R86" t="n">
-        <v>6626216</v>
+        <v>6626179</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9398,6 +9393,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B88" t="n">
-        <v>98778</v>
+        <v>92052</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B89" t="n">
-        <v>92050</v>
+        <v>98780</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>105844</v>
+        <v>91599</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R90" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>91597</v>
+        <v>105846</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R91" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9912,7 +9912,7 @@
         <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92016</v>
+        <v>92018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10583,45 +10583,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B99" t="n">
-        <v>5197</v>
+        <v>98780</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R99" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10680,54 +10689,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717884</v>
+        <v>129717137</v>
       </c>
       <c r="B100" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R100" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10883,32 +10883,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717137</v>
+        <v>129717145</v>
       </c>
       <c r="B102" t="n">
-        <v>91597</v>
+        <v>5197</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10983,7 +10983,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -4810,32 +4810,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>92052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R40" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4881,11 +4881,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B41" t="n">
-        <v>92052</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R41" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4983,6 +4978,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -7847,32 +7847,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670658</v>
+        <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>92252</v>
+        <v>91599</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651860</v>
+        <v>651813</v>
       </c>
       <c r="R71" t="n">
-        <v>6626084</v>
+        <v>6626139</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,6 +7918,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7944,7 +7949,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670574</v>
+        <v>129670573</v>
       </c>
       <c r="B72" t="n">
         <v>91599</v>
@@ -7979,10 +7984,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651813</v>
+        <v>651828</v>
       </c>
       <c r="R72" t="n">
-        <v>6626139</v>
+        <v>6626081</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8015,11 +8020,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8046,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670573</v>
+        <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>91599</v>
+        <v>92252</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651828</v>
+        <v>651860</v>
       </c>
       <c r="R73" t="n">
-        <v>6626081</v>
+        <v>6626084</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>92052</v>
+        <v>98780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B89" t="n">
-        <v>98780</v>
+        <v>92052</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -4810,32 +4810,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B40" t="n">
-        <v>92052</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R40" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4881,6 +4881,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4912,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4978,11 +4983,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670649</v>
+        <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>83044</v>
+        <v>92249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651934</v>
+        <v>651893</v>
       </c>
       <c r="R42" t="n">
-        <v>6626028</v>
+        <v>6626104</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670626</v>
+        <v>129670619</v>
       </c>
       <c r="B43" t="n">
-        <v>91897</v>
+        <v>92052</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651935</v>
+        <v>651882</v>
       </c>
       <c r="R43" t="n">
-        <v>6626058</v>
+        <v>6626177</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670627</v>
+        <v>129670649</v>
       </c>
       <c r="B44" t="n">
-        <v>91897</v>
+        <v>83044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5214,21 +5214,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651922</v>
+        <v>651934</v>
       </c>
       <c r="R44" t="n">
-        <v>6626059</v>
+        <v>6626028</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670654</v>
+        <v>129670626</v>
       </c>
       <c r="B45" t="n">
-        <v>92249</v>
+        <v>91897</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651893</v>
+        <v>651935</v>
       </c>
       <c r="R45" t="n">
-        <v>6626104</v>
+        <v>6626058</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670619</v>
+        <v>129670627</v>
       </c>
       <c r="B46" t="n">
-        <v>92052</v>
+        <v>91897</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651882</v>
+        <v>651922</v>
       </c>
       <c r="R46" t="n">
-        <v>6626177</v>
+        <v>6626059</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670636</v>
+        <v>129670598</v>
       </c>
       <c r="B75" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651666</v>
+        <v>651789</v>
       </c>
       <c r="R75" t="n">
-        <v>6626156</v>
+        <v>6626199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8342,32 +8342,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670598</v>
+        <v>129670636</v>
       </c>
       <c r="B76" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651789</v>
+        <v>651666</v>
       </c>
       <c r="R76" t="n">
-        <v>6626199</v>
+        <v>6626156</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Flyg och landningsläte</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2753,10 +2753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670638</v>
+        <v>129670611</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>92052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,21 +2764,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651788</v>
+        <v>651780</v>
       </c>
       <c r="R19" t="n">
-        <v>6626118</v>
+        <v>6626166</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,11 +2824,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,32 +2850,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670655</v>
+        <v>129670618</v>
       </c>
       <c r="B20" t="n">
-        <v>100969</v>
+        <v>92052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651655</v>
+        <v>651850</v>
       </c>
       <c r="R20" t="n">
-        <v>6626179</v>
+        <v>6626173</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2952,32 +2947,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670656</v>
+        <v>129670612</v>
       </c>
       <c r="B21" t="n">
-        <v>100969</v>
+        <v>92052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651804</v>
+        <v>651783</v>
       </c>
       <c r="R21" t="n">
-        <v>6626213</v>
+        <v>6626160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3049,7 +3044,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670611</v>
+        <v>129670607</v>
       </c>
       <c r="B22" t="n">
         <v>92052</v>
@@ -3084,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651780</v>
+        <v>651794</v>
       </c>
       <c r="R22" t="n">
-        <v>6626166</v>
+        <v>6626119</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3146,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670618</v>
+        <v>129670586</v>
       </c>
       <c r="B23" t="n">
-        <v>92052</v>
+        <v>92317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651850</v>
+        <v>651896</v>
       </c>
       <c r="R23" t="n">
-        <v>6626173</v>
+        <v>6626042</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3243,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670612</v>
+        <v>129670638</v>
       </c>
       <c r="B24" t="n">
-        <v>92052</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,21 +3249,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651783</v>
+        <v>651788</v>
       </c>
       <c r="R24" t="n">
-        <v>6626160</v>
+        <v>6626118</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3314,6 +3309,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670607</v>
+        <v>129670655</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>100969</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651794</v>
+        <v>651655</v>
       </c>
       <c r="R25" t="n">
-        <v>6626119</v>
+        <v>6626179</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670586</v>
+        <v>129670656</v>
       </c>
       <c r="B26" t="n">
-        <v>92317</v>
+        <v>100969</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651896</v>
+        <v>651804</v>
       </c>
       <c r="R26" t="n">
-        <v>6626042</v>
+        <v>6626213</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670651</v>
+        <v>129670601</v>
       </c>
       <c r="B34" t="n">
-        <v>92249</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651804</v>
+        <v>651723</v>
       </c>
       <c r="R34" t="n">
-        <v>6626204</v>
+        <v>6626229</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,6 +4284,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4310,32 +4315,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670585</v>
+        <v>129670644</v>
       </c>
       <c r="B35" t="n">
-        <v>91599</v>
+        <v>4779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651912</v>
+        <v>651725</v>
       </c>
       <c r="R35" t="n">
-        <v>6626052</v>
+        <v>6626217</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4381,6 +4386,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4407,32 +4417,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670601</v>
+        <v>129670651</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>92249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4452,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651723</v>
+        <v>651804</v>
       </c>
       <c r="R36" t="n">
-        <v>6626229</v>
+        <v>6626204</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4478,11 +4488,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4514,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670644</v>
+        <v>129670585</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>91599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651725</v>
+        <v>651912</v>
       </c>
       <c r="R37" t="n">
-        <v>6626217</v>
+        <v>6626052</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4580,11 +4585,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B68" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,6 +7617,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7643,32 +7648,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670635</v>
+        <v>129670583</v>
       </c>
       <c r="B69" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651924</v>
+        <v>651907</v>
       </c>
       <c r="R69" t="n">
-        <v>6626060</v>
+        <v>6626130</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7714,11 +7719,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670600</v>
+        <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651666</v>
+        <v>651924</v>
       </c>
       <c r="R70" t="n">
-        <v>6626239</v>
+        <v>6626060</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670611</v>
+        <v>129670586</v>
       </c>
       <c r="B19" t="n">
-        <v>92052</v>
+        <v>92317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651780</v>
+        <v>651896</v>
       </c>
       <c r="R19" t="n">
-        <v>6626166</v>
+        <v>6626042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670618</v>
+        <v>129670638</v>
       </c>
       <c r="B20" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651850</v>
+        <v>651788</v>
       </c>
       <c r="R20" t="n">
-        <v>6626173</v>
+        <v>6626118</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2921,6 +2921,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,32 +2952,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670612</v>
+        <v>129670655</v>
       </c>
       <c r="B21" t="n">
-        <v>92052</v>
+        <v>100979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651783</v>
+        <v>651655</v>
       </c>
       <c r="R21" t="n">
-        <v>6626160</v>
+        <v>6626179</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,32 +3049,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670607</v>
+        <v>129670656</v>
       </c>
       <c r="B22" t="n">
-        <v>92052</v>
+        <v>100979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651794</v>
+        <v>651804</v>
       </c>
       <c r="R22" t="n">
-        <v>6626119</v>
+        <v>6626213</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,32 +3146,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670586</v>
+        <v>129670611</v>
       </c>
       <c r="B23" t="n">
-        <v>92317</v>
+        <v>92052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651896</v>
+        <v>651780</v>
       </c>
       <c r="R23" t="n">
-        <v>6626042</v>
+        <v>6626166</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670638</v>
+        <v>129670618</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>92052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,21 +3254,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651788</v>
+        <v>651850</v>
       </c>
       <c r="R24" t="n">
-        <v>6626118</v>
+        <v>6626173</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,11 +3314,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670655</v>
+        <v>129670612</v>
       </c>
       <c r="B25" t="n">
-        <v>100969</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651655</v>
+        <v>651783</v>
       </c>
       <c r="R25" t="n">
-        <v>6626179</v>
+        <v>6626160</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670656</v>
+        <v>129670607</v>
       </c>
       <c r="B26" t="n">
-        <v>100969</v>
+        <v>92052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651804</v>
+        <v>651794</v>
       </c>
       <c r="R26" t="n">
-        <v>6626213</v>
+        <v>6626119</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670592</v>
+        <v>129670582</v>
       </c>
       <c r="B28" t="n">
-        <v>91620</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3642,21 +3642,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651842</v>
+        <v>651839</v>
       </c>
       <c r="R28" t="n">
-        <v>6626152</v>
+        <v>6626178</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670657</v>
+        <v>129670620</v>
       </c>
       <c r="B29" t="n">
-        <v>92252</v>
+        <v>92052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6031</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651836</v>
+        <v>651894</v>
       </c>
       <c r="R29" t="n">
-        <v>6626075</v>
+        <v>6626133</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670620</v>
+        <v>129670577</v>
       </c>
       <c r="B30" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651894</v>
+        <v>651934</v>
       </c>
       <c r="R30" t="n">
-        <v>6626133</v>
+        <v>6626035</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,32 +3922,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670577</v>
+        <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651934</v>
+        <v>651793</v>
       </c>
       <c r="R31" t="n">
-        <v>6626035</v>
+        <v>6626135</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670582</v>
+        <v>129670657</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>92252</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651839</v>
+        <v>651836</v>
       </c>
       <c r="R32" t="n">
-        <v>6626178</v>
+        <v>6626075</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670625</v>
+        <v>129670592</v>
       </c>
       <c r="B33" t="n">
-        <v>92052</v>
+        <v>91620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651793</v>
+        <v>651842</v>
       </c>
       <c r="R33" t="n">
-        <v>6626135</v>
+        <v>6626152</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R34" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670644</v>
+        <v>129670651</v>
       </c>
       <c r="B35" t="n">
-        <v>4779</v>
+        <v>92249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651725</v>
+        <v>651804</v>
       </c>
       <c r="R35" t="n">
-        <v>6626217</v>
+        <v>6626204</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,11 +4386,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,32 +4412,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670651</v>
+        <v>129670585</v>
       </c>
       <c r="B36" t="n">
-        <v>92249</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4452,10 +4447,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651804</v>
+        <v>651912</v>
       </c>
       <c r="R36" t="n">
-        <v>6626204</v>
+        <v>6626052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4514,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670585</v>
+        <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4520,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651912</v>
+        <v>651723</v>
       </c>
       <c r="R37" t="n">
-        <v>6626052</v>
+        <v>6626229</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4585,6 +4580,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670599</v>
+        <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651890</v>
+        <v>651780</v>
       </c>
       <c r="R39" t="n">
-        <v>6626039</v>
+        <v>6626169</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,11 +4779,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4810,32 +4805,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670647</v>
+        <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4845,10 +4840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651851</v>
+        <v>651890</v>
       </c>
       <c r="R40" t="n">
-        <v>6626154</v>
+        <v>6626039</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4885,7 +4880,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B41" t="n">
-        <v>92052</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R41" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4983,6 +4978,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5688,10 +5688,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670628</v>
+        <v>129670579</v>
       </c>
       <c r="B49" t="n">
-        <v>91897</v>
+        <v>91599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,21 +5699,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651867</v>
+        <v>651794</v>
       </c>
       <c r="R49" t="n">
-        <v>6626099</v>
+        <v>6626119</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5785,32 +5785,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670579</v>
+        <v>129670621</v>
       </c>
       <c r="B50" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651794</v>
+        <v>651904</v>
       </c>
       <c r="R50" t="n">
-        <v>6626119</v>
+        <v>6626101</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670621</v>
+        <v>129670650</v>
       </c>
       <c r="B51" t="n">
-        <v>92052</v>
+        <v>92249</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651904</v>
+        <v>651923</v>
       </c>
       <c r="R51" t="n">
-        <v>6626101</v>
+        <v>6626100</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670650</v>
+        <v>129670587</v>
       </c>
       <c r="B52" t="n">
-        <v>92249</v>
+        <v>92317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651923</v>
+        <v>651796</v>
       </c>
       <c r="R52" t="n">
-        <v>6626100</v>
+        <v>6626068</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,32 +6076,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670587</v>
+        <v>129670628</v>
       </c>
       <c r="B53" t="n">
-        <v>92317</v>
+        <v>91897</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651796</v>
+        <v>651867</v>
       </c>
       <c r="R53" t="n">
-        <v>6626068</v>
+        <v>6626099</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6173,32 +6173,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670637</v>
+        <v>129670590</v>
       </c>
       <c r="B54" t="n">
-        <v>98780</v>
+        <v>91620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651703</v>
+        <v>651906</v>
       </c>
       <c r="R54" t="n">
-        <v>6626171</v>
+        <v>6626033</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6244,11 +6244,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6275,32 +6270,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670590</v>
+        <v>129670637</v>
       </c>
       <c r="B55" t="n">
-        <v>91620</v>
+        <v>98790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651906</v>
+        <v>651703</v>
       </c>
       <c r="R55" t="n">
-        <v>6626033</v>
+        <v>6626171</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6346,6 +6341,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129670645</v>
       </c>
       <c r="B64" t="n">
-        <v>92052</v>
+        <v>4779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651662</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626158</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,6 +7219,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7245,10 +7250,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670645</v>
+        <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>4779</v>
+        <v>91563</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7256,21 +7261,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7285,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651662</v>
+        <v>651860</v>
       </c>
       <c r="R65" t="n">
-        <v>6626158</v>
+        <v>6626196</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7316,11 +7321,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7347,32 +7347,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B66" t="n">
-        <v>91563</v>
+        <v>92052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R66" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,10 +7643,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B69" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7659,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R69" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7719,6 +7714,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7748,7 +7748,7 @@
         <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670574</v>
+        <v>129670573</v>
       </c>
       <c r="B71" t="n">
         <v>91599</v>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651813</v>
+        <v>651828</v>
       </c>
       <c r="R71" t="n">
-        <v>6626139</v>
+        <v>6626081</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,11 +7918,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7949,32 +7944,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670573</v>
+        <v>129670658</v>
       </c>
       <c r="B72" t="n">
-        <v>91599</v>
+        <v>92252</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651828</v>
+        <v>651860</v>
       </c>
       <c r="R72" t="n">
-        <v>6626081</v>
+        <v>6626084</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8046,32 +8041,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670658</v>
+        <v>129670574</v>
       </c>
       <c r="B73" t="n">
-        <v>92252</v>
+        <v>91599</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +8076,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651860</v>
+        <v>651813</v>
       </c>
       <c r="R73" t="n">
-        <v>6626084</v>
+        <v>6626139</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8117,6 +8112,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>129670636</v>
       </c>
       <c r="B76" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670614</v>
+        <v>129670659</v>
       </c>
       <c r="B77" t="n">
-        <v>92052</v>
+        <v>92290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8455,21 +8455,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651826</v>
+        <v>651798</v>
       </c>
       <c r="R77" t="n">
-        <v>6626121</v>
+        <v>6626111</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670659</v>
+        <v>129670614</v>
       </c>
       <c r="B78" t="n">
-        <v>92290</v>
+        <v>92052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651798</v>
+        <v>651826</v>
       </c>
       <c r="R78" t="n">
-        <v>6626111</v>
+        <v>6626121</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9029,7 +9029,7 @@
         <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670591</v>
+        <v>129670646</v>
       </c>
       <c r="B84" t="n">
-        <v>91620</v>
+        <v>4779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651709</v>
+        <v>651847</v>
       </c>
       <c r="R84" t="n">
-        <v>6626216</v>
+        <v>6626179</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9199,6 +9199,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9322,32 +9327,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670646</v>
+        <v>129670591</v>
       </c>
       <c r="B86" t="n">
-        <v>4779</v>
+        <v>91620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651847</v>
+        <v>651709</v>
       </c>
       <c r="R86" t="n">
-        <v>6626179</v>
+        <v>6626216</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,11 +9398,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9524,7 +9524,7 @@
         <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B90" t="n">
-        <v>91599</v>
+        <v>105856</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R90" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B91" t="n">
-        <v>105846</v>
+        <v>91599</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R91" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9909,32 +9909,27 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B92" t="n">
-        <v>92052</v>
+        <v>92018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9944,10 +9939,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R92" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10006,27 +10001,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B93" t="n">
-        <v>92018</v>
+        <v>92052</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R93" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10583,54 +10583,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717884</v>
+        <v>129717137</v>
       </c>
       <c r="B99" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R99" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10689,32 +10680,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717137</v>
+        <v>129716946</v>
       </c>
       <c r="B100" t="n">
-        <v>91599</v>
+        <v>5177</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10724,10 +10715,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651809</v>
+        <v>651888</v>
       </c>
       <c r="R100" t="n">
-        <v>6626096</v>
+        <v>6626032</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10786,10 +10777,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129716946</v>
+        <v>129717145</v>
       </c>
       <c r="B101" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10797,21 +10788,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10821,10 +10812,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651888</v>
+        <v>651809</v>
       </c>
       <c r="R101" t="n">
-        <v>6626032</v>
+        <v>6626096</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10883,45 +10874,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B102" t="n">
-        <v>5197</v>
+        <v>98790</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R102" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10983,7 +10983,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670586</v>
+        <v>129670611</v>
       </c>
       <c r="B19" t="n">
-        <v>92317</v>
+        <v>92052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651896</v>
+        <v>651780</v>
       </c>
       <c r="R19" t="n">
-        <v>6626042</v>
+        <v>6626166</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670638</v>
+        <v>129670618</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>92052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651788</v>
+        <v>651850</v>
       </c>
       <c r="R20" t="n">
-        <v>6626118</v>
+        <v>6626173</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2921,11 +2921,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2952,32 +2947,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670655</v>
+        <v>129670612</v>
       </c>
       <c r="B21" t="n">
-        <v>100979</v>
+        <v>92052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651655</v>
+        <v>651783</v>
       </c>
       <c r="R21" t="n">
-        <v>6626179</v>
+        <v>6626160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3049,32 +3044,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670656</v>
+        <v>129670607</v>
       </c>
       <c r="B22" t="n">
-        <v>100979</v>
+        <v>92052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3084,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651804</v>
+        <v>651794</v>
       </c>
       <c r="R22" t="n">
-        <v>6626213</v>
+        <v>6626119</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3146,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670611</v>
+        <v>129670586</v>
       </c>
       <c r="B23" t="n">
-        <v>92052</v>
+        <v>92317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651780</v>
+        <v>651896</v>
       </c>
       <c r="R23" t="n">
-        <v>6626166</v>
+        <v>6626042</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3243,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670618</v>
+        <v>129670638</v>
       </c>
       <c r="B24" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,21 +3249,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651850</v>
+        <v>651788</v>
       </c>
       <c r="R24" t="n">
-        <v>6626173</v>
+        <v>6626118</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3314,6 +3309,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670612</v>
+        <v>129670655</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>100979</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651783</v>
+        <v>651655</v>
       </c>
       <c r="R25" t="n">
-        <v>6626160</v>
+        <v>6626179</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670607</v>
+        <v>129670656</v>
       </c>
       <c r="B26" t="n">
-        <v>92052</v>
+        <v>100979</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651794</v>
+        <v>651804</v>
       </c>
       <c r="R26" t="n">
-        <v>6626119</v>
+        <v>6626213</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -7944,32 +7944,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670658</v>
+        <v>129670574</v>
       </c>
       <c r="B72" t="n">
-        <v>92252</v>
+        <v>91599</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651860</v>
+        <v>651813</v>
       </c>
       <c r="R72" t="n">
-        <v>6626084</v>
+        <v>6626139</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8015,6 +8015,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8041,32 +8046,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670574</v>
+        <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>91599</v>
+        <v>92252</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8076,10 +8081,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651813</v>
+        <v>651860</v>
       </c>
       <c r="R73" t="n">
-        <v>6626139</v>
+        <v>6626084</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8112,11 +8117,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B82" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R82" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,6 +9000,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9026,10 +9031,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B83" t="n">
-        <v>98790</v>
+        <v>92052</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9037,21 +9042,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9061,10 +9066,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R83" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9097,11 +9102,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9909,27 +9909,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92018</v>
+        <v>92052</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9939,10 +9944,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R92" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10001,32 +10006,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92052</v>
+        <v>92018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R93" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716946</v>
+        <v>129717145</v>
       </c>
       <c r="B100" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10691,21 +10691,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651888</v>
+        <v>651809</v>
       </c>
       <c r="R100" t="n">
-        <v>6626032</v>
+        <v>6626096</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10777,45 +10777,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B101" t="n">
-        <v>5197</v>
+        <v>98790</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R101" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10874,54 +10883,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717884</v>
+        <v>129716946</v>
       </c>
       <c r="B102" t="n">
-        <v>98790</v>
+        <v>5177</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651824</v>
+        <v>651888</v>
       </c>
       <c r="R102" t="n">
-        <v>6626153</v>
+        <v>6626032</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129716641</v>
+        <v>129717132</v>
       </c>
       <c r="B106" t="n">
         <v>92052</v>
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651940</v>
+        <v>651809</v>
       </c>
       <c r="R106" t="n">
-        <v>6626011</v>
+        <v>6626096</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11377,32 +11377,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129717132</v>
+        <v>129717100</v>
       </c>
       <c r="B107" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651809</v>
+        <v>651840</v>
       </c>
       <c r="R107" t="n">
-        <v>6626096</v>
+        <v>6626075</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11474,32 +11474,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129717100</v>
+        <v>129716641</v>
       </c>
       <c r="B108" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11509,10 +11509,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651840</v>
+        <v>651940</v>
       </c>
       <c r="R108" t="n">
-        <v>6626075</v>
+        <v>6626011</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -4213,10 +4213,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670644</v>
+        <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>4779</v>
+        <v>92249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651725</v>
+        <v>651804</v>
       </c>
       <c r="R34" t="n">
-        <v>6626217</v>
+        <v>6626204</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,11 +4284,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,32 +4310,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670651</v>
+        <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>92249</v>
+        <v>91599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4345,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651804</v>
+        <v>651912</v>
       </c>
       <c r="R35" t="n">
-        <v>6626204</v>
+        <v>6626052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4412,32 +4407,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670585</v>
+        <v>129670644</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>4779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651912</v>
+        <v>651725</v>
       </c>
       <c r="R36" t="n">
-        <v>6626052</v>
+        <v>6626217</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4483,6 +4478,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B82" t="n">
-        <v>98790</v>
+        <v>92052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R82" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,11 +9000,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9031,10 +9026,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9042,21 +9037,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R83" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9102,6 +9097,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670646</v>
+        <v>129670606</v>
       </c>
       <c r="B84" t="n">
-        <v>4779</v>
+        <v>92052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651847</v>
+        <v>651875</v>
       </c>
       <c r="R84" t="n">
-        <v>6626179</v>
+        <v>6626072</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9199,11 +9199,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9230,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670606</v>
+        <v>129670591</v>
       </c>
       <c r="B85" t="n">
-        <v>92052</v>
+        <v>91620</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9265,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651875</v>
+        <v>651709</v>
       </c>
       <c r="R85" t="n">
-        <v>6626072</v>
+        <v>6626216</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9327,32 +9322,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670591</v>
+        <v>129670646</v>
       </c>
       <c r="B86" t="n">
-        <v>91620</v>
+        <v>4779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651709</v>
+        <v>651847</v>
       </c>
       <c r="R86" t="n">
-        <v>6626216</v>
+        <v>6626179</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9398,6 +9393,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B88" t="n">
-        <v>98790</v>
+        <v>92052</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B89" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129717132</v>
+        <v>129716641</v>
       </c>
       <c r="B106" t="n">
         <v>92052</v>
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651809</v>
+        <v>651940</v>
       </c>
       <c r="R106" t="n">
-        <v>6626096</v>
+        <v>6626011</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11377,32 +11377,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129717100</v>
+        <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651840</v>
+        <v>651809</v>
       </c>
       <c r="R107" t="n">
-        <v>6626075</v>
+        <v>6626096</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11474,32 +11474,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129716641</v>
+        <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11509,10 +11509,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651940</v>
+        <v>651840</v>
       </c>
       <c r="R108" t="n">
-        <v>6626011</v>
+        <v>6626075</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11574,7 +11574,7 @@
         <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129670602</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129670611</v>
       </c>
       <c r="B19" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>129670618</v>
       </c>
       <c r="B20" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>129670612</v>
       </c>
       <c r="B21" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>129670607</v>
       </c>
       <c r="B22" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>129670586</v>
       </c>
       <c r="B23" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3238,32 +3238,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670638</v>
+        <v>129670655</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>100983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651788</v>
+        <v>651655</v>
       </c>
       <c r="R24" t="n">
-        <v>6626118</v>
+        <v>6626179</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,11 +3309,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670655</v>
+        <v>129670656</v>
       </c>
       <c r="B25" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651655</v>
+        <v>651804</v>
       </c>
       <c r="R25" t="n">
-        <v>6626179</v>
+        <v>6626213</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3432,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670656</v>
+        <v>129670638</v>
       </c>
       <c r="B26" t="n">
-        <v>100979</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651804</v>
+        <v>651788</v>
       </c>
       <c r="R26" t="n">
-        <v>6626213</v>
+        <v>6626118</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,6 +3503,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,32 +3631,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670582</v>
+        <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>92055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651839</v>
+        <v>651894</v>
       </c>
       <c r="R28" t="n">
-        <v>6626178</v>
+        <v>6626133</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670620</v>
+        <v>129670577</v>
       </c>
       <c r="B29" t="n">
-        <v>92052</v>
+        <v>91602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651894</v>
+        <v>651934</v>
       </c>
       <c r="R29" t="n">
-        <v>6626133</v>
+        <v>6626035</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670577</v>
+        <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651934</v>
+        <v>651839</v>
       </c>
       <c r="R30" t="n">
-        <v>6626035</v>
+        <v>6626178</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3925,7 +3925,7 @@
         <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670657</v>
+        <v>129670592</v>
       </c>
       <c r="B32" t="n">
-        <v>92252</v>
+        <v>91623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651836</v>
+        <v>651842</v>
       </c>
       <c r="R32" t="n">
-        <v>6626075</v>
+        <v>6626152</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670592</v>
+        <v>129670657</v>
       </c>
       <c r="B33" t="n">
-        <v>91620</v>
+        <v>92255</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651842</v>
+        <v>651836</v>
       </c>
       <c r="R33" t="n">
-        <v>6626152</v>
+        <v>6626075</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4216,7 +4216,7 @@
         <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4407,32 +4407,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B36" t="n">
-        <v>4779</v>
+        <v>57734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R36" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R37" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670619</v>
+        <v>129670649</v>
       </c>
       <c r="B43" t="n">
-        <v>92052</v>
+        <v>83047</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651882</v>
+        <v>651934</v>
       </c>
       <c r="R43" t="n">
-        <v>6626177</v>
+        <v>6626028</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670649</v>
+        <v>129670619</v>
       </c>
       <c r="B44" t="n">
-        <v>83044</v>
+        <v>92055</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651934</v>
+        <v>651882</v>
       </c>
       <c r="R44" t="n">
-        <v>6626028</v>
+        <v>6626177</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>129670626</v>
       </c>
       <c r="B45" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>129670627</v>
       </c>
       <c r="B46" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>129670579</v>
       </c>
       <c r="B49" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129670621</v>
       </c>
       <c r="B50" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670650</v>
+        <v>129670628</v>
       </c>
       <c r="B51" t="n">
-        <v>92249</v>
+        <v>91900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651923</v>
+        <v>651867</v>
       </c>
       <c r="R51" t="n">
-        <v>6626100</v>
+        <v>6626099</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670587</v>
+        <v>129670650</v>
       </c>
       <c r="B52" t="n">
-        <v>92317</v>
+        <v>92252</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651796</v>
+        <v>651923</v>
       </c>
       <c r="R52" t="n">
-        <v>6626068</v>
+        <v>6626100</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,32 +6076,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670628</v>
+        <v>129670587</v>
       </c>
       <c r="B53" t="n">
-        <v>91897</v>
+        <v>92320</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651867</v>
+        <v>651796</v>
       </c>
       <c r="R53" t="n">
-        <v>6626099</v>
+        <v>6626068</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6176,7 +6176,7 @@
         <v>129670590</v>
       </c>
       <c r="B54" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>129670637</v>
       </c>
       <c r="B55" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670645</v>
+        <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>4779</v>
+        <v>92055</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651662</v>
+        <v>651791</v>
       </c>
       <c r="R64" t="n">
-        <v>6626158</v>
+        <v>6626110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,11 +7219,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7250,10 +7245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670572</v>
+        <v>129670645</v>
       </c>
       <c r="B65" t="n">
-        <v>91563</v>
+        <v>4779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7261,21 +7256,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651860</v>
+        <v>651662</v>
       </c>
       <c r="R65" t="n">
-        <v>6626196</v>
+        <v>6626158</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7321,6 +7316,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7347,32 +7347,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B66" t="n">
-        <v>92052</v>
+        <v>91566</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R66" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B68" t="n">
-        <v>91599</v>
+        <v>57734</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,6 +7617,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7643,32 +7648,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670600</v>
+        <v>129670635</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651666</v>
+        <v>651924</v>
       </c>
       <c r="R69" t="n">
-        <v>6626239</v>
+        <v>6626060</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7718,7 +7723,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7750,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670635</v>
+        <v>129670583</v>
       </c>
       <c r="B70" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7785,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651924</v>
+        <v>651907</v>
       </c>
       <c r="R70" t="n">
-        <v>6626060</v>
+        <v>6626130</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7816,11 +7821,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7847,10 +7847,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670573</v>
+        <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651828</v>
+        <v>651813</v>
       </c>
       <c r="R71" t="n">
-        <v>6626081</v>
+        <v>6626139</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7918,6 +7918,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7944,10 +7949,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670574</v>
+        <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7979,10 +7984,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651813</v>
+        <v>651828</v>
       </c>
       <c r="R72" t="n">
-        <v>6626139</v>
+        <v>6626081</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8015,11 +8020,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8049,7 +8049,7 @@
         <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670598</v>
+        <v>129670614</v>
       </c>
       <c r="B75" t="n">
-        <v>57733</v>
+        <v>92055</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651789</v>
+        <v>651826</v>
       </c>
       <c r="R75" t="n">
-        <v>6626199</v>
+        <v>6626121</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8311,11 +8311,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8342,10 +8337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670636</v>
+        <v>129670659</v>
       </c>
       <c r="B76" t="n">
-        <v>98790</v>
+        <v>92293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8353,21 +8348,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651666</v>
+        <v>651798</v>
       </c>
       <c r="R76" t="n">
-        <v>6626156</v>
+        <v>6626111</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8413,11 +8408,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8444,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670659</v>
+        <v>129670617</v>
       </c>
       <c r="B77" t="n">
-        <v>92290</v>
+        <v>92055</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8455,21 +8445,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8479,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651798</v>
+        <v>651843</v>
       </c>
       <c r="R77" t="n">
-        <v>6626111</v>
+        <v>6626170</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8541,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670614</v>
+        <v>129670581</v>
       </c>
       <c r="B78" t="n">
-        <v>92052</v>
+        <v>91602</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8576,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651826</v>
+        <v>651836</v>
       </c>
       <c r="R78" t="n">
-        <v>6626121</v>
+        <v>6626151</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8638,32 +8628,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670617</v>
+        <v>129670630</v>
       </c>
       <c r="B79" t="n">
-        <v>92052</v>
+        <v>91375</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8673,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651843</v>
+        <v>651671</v>
       </c>
       <c r="R79" t="n">
-        <v>6626170</v>
+        <v>6626205</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8735,10 +8725,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670581</v>
+        <v>129670598</v>
       </c>
       <c r="B80" t="n">
-        <v>91599</v>
+        <v>57734</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8746,21 +8736,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8770,10 +8760,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651836</v>
+        <v>651789</v>
       </c>
       <c r="R80" t="n">
-        <v>6626151</v>
+        <v>6626199</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8806,6 +8796,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8832,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670630</v>
+        <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>91372</v>
+        <v>98794</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651671</v>
+        <v>651666</v>
       </c>
       <c r="R81" t="n">
-        <v>6626205</v>
+        <v>6626156</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8903,6 +8898,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8932,7 +8932,7 @@
         <v>129670616</v>
       </c>
       <c r="B82" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>129670606</v>
       </c>
       <c r="B84" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>129670591</v>
       </c>
       <c r="B85" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>92052</v>
+        <v>98794</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B89" t="n">
-        <v>98790</v>
+        <v>92055</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>105856</v>
+        <v>91602</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R90" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>91599</v>
+        <v>105860</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R91" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9912,7 +9912,7 @@
         <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92018</v>
+        <v>92021</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10018,6 +10018,11 @@
       </c>
       <c r="E93" t="n">
         <v>6040186</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -10101,7 +10106,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10295,7 +10300,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10489,7 +10494,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10586,7 +10591,7 @@
         <v>129717137</v>
       </c>
       <c r="B99" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10680,10 +10685,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717145</v>
+        <v>129716946</v>
       </c>
       <c r="B100" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10691,21 +10696,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10715,10 +10720,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651809</v>
+        <v>651888</v>
       </c>
       <c r="R100" t="n">
-        <v>6626096</v>
+        <v>6626032</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10777,54 +10782,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717884</v>
+        <v>129717145</v>
       </c>
       <c r="B101" t="n">
-        <v>98790</v>
+        <v>5197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R101" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10883,45 +10879,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129716946</v>
+        <v>129717884</v>
       </c>
       <c r="B102" t="n">
-        <v>5177</v>
+        <v>98794</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651888</v>
+        <v>651824</v>
       </c>
       <c r="R102" t="n">
-        <v>6626032</v>
+        <v>6626153</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10983,7 +10988,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11089,7 +11094,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,7 +11191,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11280,32 +11285,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129716641</v>
+        <v>129717100</v>
       </c>
       <c r="B106" t="n">
-        <v>92052</v>
+        <v>91602</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11315,10 +11320,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651940</v>
+        <v>651840</v>
       </c>
       <c r="R106" t="n">
-        <v>6626011</v>
+        <v>6626075</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11377,10 +11382,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129717132</v>
+        <v>129716641</v>
       </c>
       <c r="B107" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11412,10 +11417,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651809</v>
+        <v>651940</v>
       </c>
       <c r="R107" t="n">
-        <v>6626096</v>
+        <v>6626011</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11474,32 +11479,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129717100</v>
+        <v>129717132</v>
       </c>
       <c r="B108" t="n">
-        <v>91599</v>
+        <v>92055</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11509,10 +11514,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651840</v>
+        <v>651809</v>
       </c>
       <c r="R108" t="n">
-        <v>6626075</v>
+        <v>6626096</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12348,32 +12353,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729575</v>
+        <v>129729570</v>
       </c>
       <c r="B117" t="n">
-        <v>91900</v>
+        <v>92055</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12383,10 +12388,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651890</v>
+        <v>651833</v>
       </c>
       <c r="R117" t="n">
-        <v>6626043</v>
+        <v>6626152</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,32 +12450,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729570</v>
+        <v>129729575</v>
       </c>
       <c r="B118" t="n">
-        <v>92055</v>
+        <v>91900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12480,10 +12485,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651833</v>
+        <v>651890</v>
       </c>
       <c r="R118" t="n">
-        <v>6626152</v>
+        <v>6626043</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -4407,32 +4407,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B36" t="n">
-        <v>57734</v>
+        <v>4779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R36" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>57734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R37" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670610</v>
+        <v>129670599</v>
       </c>
       <c r="B39" t="n">
-        <v>92055</v>
+        <v>57734</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651780</v>
+        <v>651890</v>
       </c>
       <c r="R39" t="n">
-        <v>6626169</v>
+        <v>6626039</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,6 +4779,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,32 +4810,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670599</v>
+        <v>129670647</v>
       </c>
       <c r="B40" t="n">
-        <v>57734</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651890</v>
+        <v>651851</v>
       </c>
       <c r="R40" t="n">
-        <v>6626039</v>
+        <v>6626154</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4880,7 +4885,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4912,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92055</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4978,11 +4983,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -10588,32 +10588,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717137</v>
+        <v>129716946</v>
       </c>
       <c r="B99" t="n">
-        <v>91602</v>
+        <v>5177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651809</v>
+        <v>651888</v>
       </c>
       <c r="R99" t="n">
-        <v>6626096</v>
+        <v>6626032</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10685,32 +10685,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716946</v>
+        <v>129717137</v>
       </c>
       <c r="B100" t="n">
-        <v>5177</v>
+        <v>91602</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10720,10 +10720,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651888</v>
+        <v>651809</v>
       </c>
       <c r="R100" t="n">
-        <v>6626032</v>
+        <v>6626096</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10782,45 +10782,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B101" t="n">
-        <v>5197</v>
+        <v>98794</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R101" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10879,54 +10888,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717884</v>
+        <v>129717145</v>
       </c>
       <c r="B102" t="n">
-        <v>98794</v>
+        <v>5197</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R102" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11285,32 +11285,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129717100</v>
+        <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>91602</v>
+        <v>92055</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651840</v>
+        <v>651940</v>
       </c>
       <c r="R106" t="n">
-        <v>6626075</v>
+        <v>6626011</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11382,7 +11382,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129716641</v>
+        <v>129717132</v>
       </c>
       <c r="B107" t="n">
         <v>92055</v>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651940</v>
+        <v>651809</v>
       </c>
       <c r="R107" t="n">
-        <v>6626011</v>
+        <v>6626096</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11479,32 +11479,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129717132</v>
+        <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>92055</v>
+        <v>91602</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11514,10 +11514,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651809</v>
+        <v>651840</v>
       </c>
       <c r="R108" t="n">
-        <v>6626096</v>
+        <v>6626075</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B14" t="n">
-        <v>92252</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R14" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2360,32 +2360,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670575</v>
+        <v>129670652</v>
       </c>
       <c r="B15" t="n">
-        <v>91602</v>
+        <v>92255</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651902</v>
+        <v>651866</v>
       </c>
       <c r="R15" t="n">
-        <v>6626042</v>
+        <v>6626192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2460,7 +2460,7 @@
         <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129670602</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670611</v>
+        <v>129670586</v>
       </c>
       <c r="B19" t="n">
-        <v>92055</v>
+        <v>92323</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651780</v>
+        <v>651896</v>
       </c>
       <c r="R19" t="n">
-        <v>6626166</v>
+        <v>6626042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670618</v>
+        <v>129670611</v>
       </c>
       <c r="B20" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651850</v>
+        <v>651780</v>
       </c>
       <c r="R20" t="n">
-        <v>6626173</v>
+        <v>6626166</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670612</v>
+        <v>129670618</v>
       </c>
       <c r="B21" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651783</v>
+        <v>651850</v>
       </c>
       <c r="R21" t="n">
-        <v>6626160</v>
+        <v>6626173</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670607</v>
+        <v>129670612</v>
       </c>
       <c r="B22" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651794</v>
+        <v>651783</v>
       </c>
       <c r="R22" t="n">
-        <v>6626119</v>
+        <v>6626160</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670586</v>
+        <v>129670607</v>
       </c>
       <c r="B23" t="n">
-        <v>92320</v>
+        <v>92058</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651896</v>
+        <v>651794</v>
       </c>
       <c r="R23" t="n">
-        <v>6626042</v>
+        <v>6626119</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,32 +3238,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670655</v>
+        <v>129670638</v>
       </c>
       <c r="B24" t="n">
-        <v>100983</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651655</v>
+        <v>651788</v>
       </c>
       <c r="R24" t="n">
-        <v>6626179</v>
+        <v>6626118</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,6 +3309,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,10 +3340,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670656</v>
+        <v>129670655</v>
       </c>
       <c r="B25" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651804</v>
+        <v>651655</v>
       </c>
       <c r="R25" t="n">
-        <v>6626213</v>
+        <v>6626179</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3432,32 +3437,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670638</v>
+        <v>129670656</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>100986</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651788</v>
+        <v>651804</v>
       </c>
       <c r="R26" t="n">
-        <v>6626118</v>
+        <v>6626213</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3503,11 +3508,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670577</v>
+        <v>129670582</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651934</v>
+        <v>651839</v>
       </c>
       <c r="R29" t="n">
-        <v>6626035</v>
+        <v>6626178</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670582</v>
+        <v>129670625</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>92058</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651839</v>
+        <v>651793</v>
       </c>
       <c r="R30" t="n">
-        <v>6626178</v>
+        <v>6626135</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,32 +3922,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670625</v>
+        <v>129670592</v>
       </c>
       <c r="B31" t="n">
-        <v>92055</v>
+        <v>91626</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651793</v>
+        <v>651842</v>
       </c>
       <c r="R31" t="n">
-        <v>6626135</v>
+        <v>6626152</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670592</v>
+        <v>129670657</v>
       </c>
       <c r="B32" t="n">
-        <v>91623</v>
+        <v>92258</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651842</v>
+        <v>651836</v>
       </c>
       <c r="R32" t="n">
-        <v>6626152</v>
+        <v>6626075</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670657</v>
+        <v>129670577</v>
       </c>
       <c r="B33" t="n">
-        <v>92255</v>
+        <v>91605</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651836</v>
+        <v>651934</v>
       </c>
       <c r="R33" t="n">
-        <v>6626075</v>
+        <v>6626035</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670651</v>
+        <v>129670644</v>
       </c>
       <c r="B34" t="n">
-        <v>92252</v>
+        <v>4779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651804</v>
+        <v>651725</v>
       </c>
       <c r="R34" t="n">
-        <v>6626204</v>
+        <v>6626217</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,6 +4284,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4310,32 +4315,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670585</v>
+        <v>129670651</v>
       </c>
       <c r="B35" t="n">
-        <v>91602</v>
+        <v>92255</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651912</v>
+        <v>651804</v>
       </c>
       <c r="R35" t="n">
-        <v>6626052</v>
+        <v>6626204</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4407,32 +4412,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670644</v>
+        <v>129670585</v>
       </c>
       <c r="B36" t="n">
-        <v>4779</v>
+        <v>91605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4447,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651725</v>
+        <v>651912</v>
       </c>
       <c r="R36" t="n">
-        <v>6626217</v>
+        <v>6626052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4478,11 +4483,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4512,7 +4512,7 @@
         <v>129670601</v>
       </c>
       <c r="B37" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670599</v>
+        <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>57734</v>
+        <v>92058</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651890</v>
+        <v>651780</v>
       </c>
       <c r="R39" t="n">
-        <v>6626039</v>
+        <v>6626169</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,11 +4779,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4912,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670610</v>
+        <v>129670599</v>
       </c>
       <c r="B41" t="n">
-        <v>92055</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651780</v>
+        <v>651890</v>
       </c>
       <c r="R41" t="n">
-        <v>6626169</v>
+        <v>6626039</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4983,6 +4978,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670654</v>
+        <v>129670649</v>
       </c>
       <c r="B42" t="n">
-        <v>92252</v>
+        <v>83050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651893</v>
+        <v>651934</v>
       </c>
       <c r="R42" t="n">
-        <v>6626104</v>
+        <v>6626028</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670649</v>
+        <v>129670626</v>
       </c>
       <c r="B43" t="n">
-        <v>83047</v>
+        <v>91903</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651934</v>
+        <v>651935</v>
       </c>
       <c r="R43" t="n">
-        <v>6626028</v>
+        <v>6626058</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670619</v>
+        <v>129670627</v>
       </c>
       <c r="B44" t="n">
-        <v>92055</v>
+        <v>91903</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651882</v>
+        <v>651922</v>
       </c>
       <c r="R44" t="n">
-        <v>6626177</v>
+        <v>6626059</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670626</v>
+        <v>129670654</v>
       </c>
       <c r="B45" t="n">
-        <v>91900</v>
+        <v>92255</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651935</v>
+        <v>651893</v>
       </c>
       <c r="R45" t="n">
-        <v>6626058</v>
+        <v>6626104</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670627</v>
+        <v>129670619</v>
       </c>
       <c r="B46" t="n">
-        <v>91900</v>
+        <v>92058</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651922</v>
+        <v>651882</v>
       </c>
       <c r="R46" t="n">
-        <v>6626059</v>
+        <v>6626177</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>129670579</v>
       </c>
       <c r="B49" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5785,32 +5785,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670621</v>
+        <v>129670628</v>
       </c>
       <c r="B50" t="n">
-        <v>92055</v>
+        <v>91903</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651904</v>
+        <v>651867</v>
       </c>
       <c r="R50" t="n">
-        <v>6626101</v>
+        <v>6626099</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670628</v>
+        <v>129670587</v>
       </c>
       <c r="B51" t="n">
-        <v>91900</v>
+        <v>92323</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651867</v>
+        <v>651796</v>
       </c>
       <c r="R51" t="n">
-        <v>6626099</v>
+        <v>6626068</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5979,32 +5979,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670650</v>
+        <v>129670621</v>
       </c>
       <c r="B52" t="n">
-        <v>92252</v>
+        <v>92058</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651923</v>
+        <v>651904</v>
       </c>
       <c r="R52" t="n">
-        <v>6626100</v>
+        <v>6626101</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670587</v>
+        <v>129670650</v>
       </c>
       <c r="B53" t="n">
-        <v>92320</v>
+        <v>92255</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651796</v>
+        <v>651923</v>
       </c>
       <c r="R53" t="n">
-        <v>6626068</v>
+        <v>6626100</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6176,7 +6176,7 @@
         <v>129670590</v>
       </c>
       <c r="B54" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>129670637</v>
       </c>
       <c r="B55" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129670645</v>
       </c>
       <c r="B64" t="n">
-        <v>92055</v>
+        <v>4779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651662</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626158</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,6 +7219,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7245,10 +7250,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670645</v>
+        <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>4779</v>
+        <v>91569</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7256,21 +7261,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7285,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651662</v>
+        <v>651860</v>
       </c>
       <c r="R65" t="n">
-        <v>6626158</v>
+        <v>6626196</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7316,11 +7321,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7347,32 +7347,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B66" t="n">
-        <v>91566</v>
+        <v>92058</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R66" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>57734</v>
+        <v>91605</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,32 +7643,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670635</v>
+        <v>129670600</v>
       </c>
       <c r="B69" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651924</v>
+        <v>651666</v>
       </c>
       <c r="R69" t="n">
-        <v>6626060</v>
+        <v>6626239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7723,7 +7718,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7750,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670583</v>
+        <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>91602</v>
+        <v>98797</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7785,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651907</v>
+        <v>651924</v>
       </c>
       <c r="R70" t="n">
-        <v>6626130</v>
+        <v>6626060</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7821,6 +7816,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7850,7 +7850,7 @@
         <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,10 +8240,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670614</v>
+        <v>129670659</v>
       </c>
       <c r="B75" t="n">
-        <v>92055</v>
+        <v>92296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,21 +8251,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651826</v>
+        <v>651798</v>
       </c>
       <c r="R75" t="n">
-        <v>6626121</v>
+        <v>6626111</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8337,32 +8337,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670659</v>
+        <v>129670581</v>
       </c>
       <c r="B76" t="n">
-        <v>92293</v>
+        <v>91605</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651798</v>
+        <v>651836</v>
       </c>
       <c r="R76" t="n">
-        <v>6626111</v>
+        <v>6626151</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8434,32 +8434,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670617</v>
+        <v>129670630</v>
       </c>
       <c r="B77" t="n">
-        <v>92055</v>
+        <v>91378</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651843</v>
+        <v>651671</v>
       </c>
       <c r="R77" t="n">
-        <v>6626170</v>
+        <v>6626205</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8531,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670581</v>
+        <v>129670614</v>
       </c>
       <c r="B78" t="n">
-        <v>91602</v>
+        <v>92058</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651836</v>
+        <v>651826</v>
       </c>
       <c r="R78" t="n">
-        <v>6626151</v>
+        <v>6626121</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8628,32 +8628,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670630</v>
+        <v>129670617</v>
       </c>
       <c r="B79" t="n">
-        <v>91375</v>
+        <v>92058</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3215</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651671</v>
+        <v>651843</v>
       </c>
       <c r="R79" t="n">
-        <v>6626205</v>
+        <v>6626170</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8728,7 +8728,7 @@
         <v>129670598</v>
       </c>
       <c r="B80" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B82" t="n">
-        <v>92055</v>
+        <v>98797</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R82" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,6 +9000,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9026,10 +9031,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B83" t="n">
-        <v>98794</v>
+        <v>92058</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9037,21 +9042,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9061,10 +9066,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R83" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9097,11 +9102,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9131,7 +9131,7 @@
         <v>129670606</v>
       </c>
       <c r="B84" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>129670591</v>
       </c>
       <c r="B85" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B88" t="n">
-        <v>98794</v>
+        <v>92058</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B89" t="n">
-        <v>92055</v>
+        <v>98797</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9718,7 +9718,7 @@
         <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10588,10 +10588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129716946</v>
+        <v>129717145</v>
       </c>
       <c r="B99" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10599,21 +10599,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651888</v>
+        <v>651809</v>
       </c>
       <c r="R99" t="n">
-        <v>6626032</v>
+        <v>6626096</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10688,7 +10688,7 @@
         <v>129717137</v>
       </c>
       <c r="B100" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10782,54 +10782,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717884</v>
+        <v>129716946</v>
       </c>
       <c r="B101" t="n">
-        <v>98794</v>
+        <v>5177</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651824</v>
+        <v>651888</v>
       </c>
       <c r="R101" t="n">
-        <v>6626153</v>
+        <v>6626032</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10888,45 +10879,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B102" t="n">
-        <v>5197</v>
+        <v>98797</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R102" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10988,7 +10988,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12353,32 +12353,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729570</v>
+        <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>92055</v>
+        <v>91903</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651833</v>
+        <v>651890</v>
       </c>
       <c r="R117" t="n">
-        <v>6626152</v>
+        <v>6626043</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12450,32 +12450,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729575</v>
+        <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>91900</v>
+        <v>92058</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651890</v>
+        <v>651833</v>
       </c>
       <c r="R118" t="n">
-        <v>6626043</v>
+        <v>6626152</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12550,7 +12550,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670644</v>
+        <v>129670601</v>
       </c>
       <c r="B34" t="n">
-        <v>4779</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651725</v>
+        <v>651723</v>
       </c>
       <c r="R34" t="n">
-        <v>6626217</v>
+        <v>6626229</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,32 +4315,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670651</v>
+        <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>92255</v>
+        <v>91605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651804</v>
+        <v>651912</v>
       </c>
       <c r="R35" t="n">
-        <v>6626204</v>
+        <v>6626052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4412,32 +4412,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670585</v>
+        <v>129670651</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
+        <v>92255</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651912</v>
+        <v>651804</v>
       </c>
       <c r="R36" t="n">
-        <v>6626052</v>
+        <v>6626204</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670601</v>
+        <v>129670644</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651723</v>
+        <v>651725</v>
       </c>
       <c r="R37" t="n">
-        <v>6626229</v>
+        <v>6626217</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,32 +4805,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670647</v>
+        <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651851</v>
+        <v>651890</v>
       </c>
       <c r="R40" t="n">
-        <v>6626154</v>
+        <v>6626039</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670599</v>
+        <v>129670647</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651890</v>
+        <v>651851</v>
       </c>
       <c r="R41" t="n">
-        <v>6626039</v>
+        <v>6626154</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -7148,10 +7148,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670645</v>
+        <v>129670572</v>
       </c>
       <c r="B64" t="n">
-        <v>4779</v>
+        <v>91569</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7159,21 +7159,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651662</v>
+        <v>651860</v>
       </c>
       <c r="R64" t="n">
-        <v>6626158</v>
+        <v>6626196</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7219,11 +7219,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7250,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B65" t="n">
-        <v>91569</v>
+        <v>92058</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R65" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7347,32 +7342,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670624</v>
+        <v>129670645</v>
       </c>
       <c r="B66" t="n">
-        <v>92058</v>
+        <v>4779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7382,10 +7377,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651791</v>
+        <v>651662</v>
       </c>
       <c r="R66" t="n">
-        <v>6626110</v>
+        <v>6626158</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7418,6 +7413,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7546,32 +7546,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670635</v>
       </c>
       <c r="B68" t="n">
-        <v>91605</v>
+        <v>98797</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651924</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626060</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,6 +7617,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7643,10 +7648,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670600</v>
+        <v>129670583</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7654,21 +7659,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651666</v>
+        <v>651907</v>
       </c>
       <c r="R69" t="n">
-        <v>6626239</v>
+        <v>6626130</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7714,11 +7719,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670635</v>
+        <v>129670600</v>
       </c>
       <c r="B70" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651924</v>
+        <v>651666</v>
       </c>
       <c r="R70" t="n">
-        <v>6626060</v>
+        <v>6626239</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670659</v>
+        <v>129670598</v>
       </c>
       <c r="B75" t="n">
-        <v>92296</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651798</v>
+        <v>651789</v>
       </c>
       <c r="R75" t="n">
-        <v>6626111</v>
+        <v>6626199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8311,6 +8311,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8337,32 +8342,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670581</v>
+        <v>129670659</v>
       </c>
       <c r="B76" t="n">
-        <v>91605</v>
+        <v>92296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651836</v>
+        <v>651798</v>
       </c>
       <c r="R76" t="n">
-        <v>6626151</v>
+        <v>6626111</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8434,32 +8439,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670630</v>
+        <v>129670581</v>
       </c>
       <c r="B77" t="n">
-        <v>91378</v>
+        <v>91605</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651671</v>
+        <v>651836</v>
       </c>
       <c r="R77" t="n">
-        <v>6626205</v>
+        <v>6626151</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8725,32 +8730,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670598</v>
+        <v>129670630</v>
       </c>
       <c r="B80" t="n">
-        <v>57737</v>
+        <v>91378</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8760,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651789</v>
+        <v>651671</v>
       </c>
       <c r="R80" t="n">
-        <v>6626199</v>
+        <v>6626205</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8796,11 +8801,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12353,32 +12353,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729575</v>
+        <v>129729570</v>
       </c>
       <c r="B117" t="n">
-        <v>91903</v>
+        <v>92058</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651890</v>
+        <v>651833</v>
       </c>
       <c r="R117" t="n">
-        <v>6626043</v>
+        <v>6626152</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12450,32 +12450,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729570</v>
+        <v>129729575</v>
       </c>
       <c r="B118" t="n">
-        <v>92058</v>
+        <v>91903</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651833</v>
+        <v>651890</v>
       </c>
       <c r="R118" t="n">
-        <v>6626152</v>
+        <v>6626043</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -3631,32 +3631,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670620</v>
+        <v>129670577</v>
       </c>
       <c r="B28" t="n">
-        <v>92058</v>
+        <v>91605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651894</v>
+        <v>651934</v>
       </c>
       <c r="R28" t="n">
-        <v>6626133</v>
+        <v>6626035</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670582</v>
+        <v>129670620</v>
       </c>
       <c r="B29" t="n">
-        <v>91605</v>
+        <v>92058</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651839</v>
+        <v>651894</v>
       </c>
       <c r="R29" t="n">
-        <v>6626178</v>
+        <v>6626133</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670625</v>
+        <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>92058</v>
+        <v>91605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651793</v>
+        <v>651839</v>
       </c>
       <c r="R30" t="n">
-        <v>6626135</v>
+        <v>6626178</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,32 +3922,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670592</v>
+        <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>91626</v>
+        <v>92058</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651842</v>
+        <v>651793</v>
       </c>
       <c r="R31" t="n">
-        <v>6626152</v>
+        <v>6626135</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670657</v>
+        <v>129670592</v>
       </c>
       <c r="B32" t="n">
-        <v>92258</v>
+        <v>91626</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651836</v>
+        <v>651842</v>
       </c>
       <c r="R32" t="n">
-        <v>6626075</v>
+        <v>6626152</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670577</v>
+        <v>129670657</v>
       </c>
       <c r="B33" t="n">
-        <v>91605</v>
+        <v>92258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651934</v>
+        <v>651836</v>
       </c>
       <c r="R33" t="n">
-        <v>6626035</v>
+        <v>6626075</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4315,32 +4315,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670585</v>
+        <v>129670644</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
+        <v>4779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651912</v>
+        <v>651725</v>
       </c>
       <c r="R35" t="n">
-        <v>6626052</v>
+        <v>6626217</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,6 +4386,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,32 +4417,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670651</v>
+        <v>129670585</v>
       </c>
       <c r="B36" t="n">
-        <v>92255</v>
+        <v>91605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,10 +4452,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651804</v>
+        <v>651912</v>
       </c>
       <c r="R36" t="n">
-        <v>6626204</v>
+        <v>6626052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670644</v>
+        <v>129670651</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>92255</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651725</v>
+        <v>651804</v>
       </c>
       <c r="R37" t="n">
-        <v>6626217</v>
+        <v>6626204</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4580,11 +4585,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7546,32 +7546,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670635</v>
+        <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>98797</v>
+        <v>91605</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651924</v>
+        <v>651907</v>
       </c>
       <c r="R68" t="n">
-        <v>6626060</v>
+        <v>6626130</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,11 +7617,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7648,10 +7643,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670583</v>
+        <v>129670600</v>
       </c>
       <c r="B69" t="n">
-        <v>91605</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7659,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7683,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651907</v>
+        <v>651666</v>
       </c>
       <c r="R69" t="n">
-        <v>6626130</v>
+        <v>6626239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7719,6 +7714,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,32 +7745,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670600</v>
+        <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651666</v>
+        <v>651924</v>
       </c>
       <c r="R70" t="n">
-        <v>6626239</v>
+        <v>6626060</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2263,32 +2263,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670575</v>
+        <v>129670652</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>92256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651902</v>
+        <v>651866</v>
       </c>
       <c r="R14" t="n">
-        <v>6626042</v>
+        <v>6626192</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2360,32 +2360,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B15" t="n">
-        <v>92255</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R15" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2460,7 +2460,7 @@
         <v>129670653</v>
       </c>
       <c r="B16" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>129670584</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670586</v>
+        <v>129670638</v>
       </c>
       <c r="B19" t="n">
-        <v>92323</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651896</v>
+        <v>651788</v>
       </c>
       <c r="R19" t="n">
-        <v>6626042</v>
+        <v>6626118</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,6 +2824,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,32 +2855,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670611</v>
+        <v>129670655</v>
       </c>
       <c r="B20" t="n">
-        <v>92058</v>
+        <v>100987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651780</v>
+        <v>651655</v>
       </c>
       <c r="R20" t="n">
-        <v>6626166</v>
+        <v>6626179</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,32 +2952,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670618</v>
+        <v>129670656</v>
       </c>
       <c r="B21" t="n">
-        <v>92058</v>
+        <v>100987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651850</v>
+        <v>651804</v>
       </c>
       <c r="R21" t="n">
-        <v>6626173</v>
+        <v>6626213</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670612</v>
+        <v>129670611</v>
       </c>
       <c r="B22" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651783</v>
+        <v>651780</v>
       </c>
       <c r="R22" t="n">
-        <v>6626160</v>
+        <v>6626166</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,10 +3146,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670607</v>
+        <v>129670618</v>
       </c>
       <c r="B23" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651794</v>
+        <v>651850</v>
       </c>
       <c r="R23" t="n">
-        <v>6626119</v>
+        <v>6626173</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670638</v>
+        <v>129670612</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>92059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,21 +3254,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651788</v>
+        <v>651783</v>
       </c>
       <c r="R24" t="n">
-        <v>6626118</v>
+        <v>6626160</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,11 +3314,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670655</v>
+        <v>129670607</v>
       </c>
       <c r="B25" t="n">
-        <v>100986</v>
+        <v>92059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651655</v>
+        <v>651794</v>
       </c>
       <c r="R25" t="n">
-        <v>6626179</v>
+        <v>6626119</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670656</v>
+        <v>129670586</v>
       </c>
       <c r="B26" t="n">
-        <v>100986</v>
+        <v>92324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651804</v>
+        <v>651896</v>
       </c>
       <c r="R26" t="n">
-        <v>6626213</v>
+        <v>6626042</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3537,7 +3537,7 @@
         <v>129670588</v>
       </c>
       <c r="B27" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,32 +3631,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670577</v>
+        <v>129670620</v>
       </c>
       <c r="B28" t="n">
-        <v>91605</v>
+        <v>92059</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651934</v>
+        <v>651894</v>
       </c>
       <c r="R28" t="n">
-        <v>6626035</v>
+        <v>6626133</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670620</v>
+        <v>129670577</v>
       </c>
       <c r="B29" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651894</v>
+        <v>651934</v>
       </c>
       <c r="R29" t="n">
-        <v>6626133</v>
+        <v>6626035</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3828,7 +3828,7 @@
         <v>129670582</v>
       </c>
       <c r="B30" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129670625</v>
       </c>
       <c r="B31" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>129670592</v>
       </c>
       <c r="B32" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>129670657</v>
       </c>
       <c r="B33" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4213,32 +4213,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670601</v>
+        <v>129670651</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>92256</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651723</v>
+        <v>651804</v>
       </c>
       <c r="R34" t="n">
-        <v>6626229</v>
+        <v>6626204</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4284,11 +4284,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4315,32 +4310,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670644</v>
+        <v>129670585</v>
       </c>
       <c r="B35" t="n">
-        <v>4779</v>
+        <v>91606</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4350,10 +4345,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651725</v>
+        <v>651912</v>
       </c>
       <c r="R35" t="n">
-        <v>6626217</v>
+        <v>6626052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4386,11 +4381,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,10 +4407,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670585</v>
+        <v>129670601</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,21 +4418,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4452,10 +4442,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651912</v>
+        <v>651723</v>
       </c>
       <c r="R36" t="n">
-        <v>6626052</v>
+        <v>6626229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4488,6 +4478,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4514,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670651</v>
+        <v>129670644</v>
       </c>
       <c r="B37" t="n">
-        <v>92255</v>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4520,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4544,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651804</v>
+        <v>651725</v>
       </c>
       <c r="R37" t="n">
-        <v>6626204</v>
+        <v>6626217</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4585,6 +4580,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129670640</v>
       </c>
       <c r="B38" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670610</v>
+        <v>129670647</v>
       </c>
       <c r="B39" t="n">
-        <v>92058</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651780</v>
+        <v>651851</v>
       </c>
       <c r="R39" t="n">
-        <v>6626169</v>
+        <v>6626154</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,6 +4779,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,32 +4810,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670599</v>
+        <v>129670610</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>92059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651890</v>
+        <v>651780</v>
       </c>
       <c r="R40" t="n">
-        <v>6626039</v>
+        <v>6626169</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4876,11 +4881,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670599</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651890</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626039</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5009,32 +5009,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670649</v>
+        <v>129670654</v>
       </c>
       <c r="B42" t="n">
-        <v>83050</v>
+        <v>92256</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651934</v>
+        <v>651893</v>
       </c>
       <c r="R42" t="n">
-        <v>6626028</v>
+        <v>6626104</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,32 +5106,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670626</v>
+        <v>129670619</v>
       </c>
       <c r="B43" t="n">
-        <v>91903</v>
+        <v>92059</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651935</v>
+        <v>651882</v>
       </c>
       <c r="R43" t="n">
-        <v>6626058</v>
+        <v>6626177</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670627</v>
+        <v>129670626</v>
       </c>
       <c r="B44" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651922</v>
+        <v>651935</v>
       </c>
       <c r="R44" t="n">
-        <v>6626059</v>
+        <v>6626058</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670654</v>
+        <v>129670627</v>
       </c>
       <c r="B45" t="n">
-        <v>92255</v>
+        <v>91904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651893</v>
+        <v>651922</v>
       </c>
       <c r="R45" t="n">
-        <v>6626104</v>
+        <v>6626059</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670619</v>
+        <v>129670649</v>
       </c>
       <c r="B46" t="n">
-        <v>92058</v>
+        <v>83051</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651882</v>
+        <v>651934</v>
       </c>
       <c r="R46" t="n">
-        <v>6626177</v>
+        <v>6626028</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5497,7 +5497,7 @@
         <v>129670608</v>
       </c>
       <c r="B47" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>129670613</v>
       </c>
       <c r="B48" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670579</v>
+        <v>129670590</v>
       </c>
       <c r="B49" t="n">
-        <v>91605</v>
+        <v>91627</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,21 +5699,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651794</v>
+        <v>651906</v>
       </c>
       <c r="R49" t="n">
-        <v>6626119</v>
+        <v>6626033</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5785,32 +5785,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670628</v>
+        <v>129670587</v>
       </c>
       <c r="B50" t="n">
-        <v>91903</v>
+        <v>92324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651867</v>
+        <v>651796</v>
       </c>
       <c r="R50" t="n">
-        <v>6626099</v>
+        <v>6626068</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5882,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670587</v>
+        <v>129670637</v>
       </c>
       <c r="B51" t="n">
-        <v>92323</v>
+        <v>98798</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651796</v>
+        <v>651703</v>
       </c>
       <c r="R51" t="n">
-        <v>6626068</v>
+        <v>6626171</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5953,6 +5953,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5979,32 +5984,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670621</v>
+        <v>129670579</v>
       </c>
       <c r="B52" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651904</v>
+        <v>651794</v>
       </c>
       <c r="R52" t="n">
-        <v>6626101</v>
+        <v>6626119</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6076,32 +6081,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670650</v>
+        <v>129670621</v>
       </c>
       <c r="B53" t="n">
-        <v>92255</v>
+        <v>92059</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651923</v>
+        <v>651904</v>
       </c>
       <c r="R53" t="n">
-        <v>6626100</v>
+        <v>6626101</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6173,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670590</v>
+        <v>129670628</v>
       </c>
       <c r="B54" t="n">
-        <v>91626</v>
+        <v>91904</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6184,21 +6189,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651906</v>
+        <v>651867</v>
       </c>
       <c r="R54" t="n">
-        <v>6626033</v>
+        <v>6626099</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6270,32 +6275,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670637</v>
+        <v>129670650</v>
       </c>
       <c r="B55" t="n">
-        <v>98797</v>
+        <v>92256</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651703</v>
+        <v>651923</v>
       </c>
       <c r="R55" t="n">
-        <v>6626171</v>
+        <v>6626100</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6341,11 +6346,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,7 +6375,7 @@
         <v>129670609</v>
       </c>
       <c r="B56" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129670622</v>
       </c>
       <c r="B57" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>129670580</v>
       </c>
       <c r="B58" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129670615</v>
       </c>
       <c r="B59" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129670578</v>
       </c>
       <c r="B60" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>129670605</v>
       </c>
       <c r="B61" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>129670576</v>
       </c>
       <c r="B62" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129670623</v>
       </c>
       <c r="B63" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7148,32 +7148,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670572</v>
+        <v>129670624</v>
       </c>
       <c r="B64" t="n">
-        <v>91569</v>
+        <v>92059</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651860</v>
+        <v>651791</v>
       </c>
       <c r="R64" t="n">
-        <v>6626196</v>
+        <v>6626110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7245,32 +7245,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670624</v>
+        <v>129670572</v>
       </c>
       <c r="B65" t="n">
-        <v>92058</v>
+        <v>91570</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651791</v>
+        <v>651860</v>
       </c>
       <c r="R65" t="n">
-        <v>6626110</v>
+        <v>6626196</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7549,7 +7549,7 @@
         <v>129670583</v>
       </c>
       <c r="B68" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>129670635</v>
       </c>
       <c r="B70" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>129670574</v>
       </c>
       <c r="B71" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>129670573</v>
       </c>
       <c r="B72" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>129670658</v>
       </c>
       <c r="B73" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129670629</v>
       </c>
       <c r="B74" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670598</v>
+        <v>129670614</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>92059</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651789</v>
+        <v>651826</v>
       </c>
       <c r="R75" t="n">
-        <v>6626199</v>
+        <v>6626121</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8311,11 +8311,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8345,7 +8340,7 @@
         <v>129670659</v>
       </c>
       <c r="B76" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8439,32 +8434,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670581</v>
+        <v>129670617</v>
       </c>
       <c r="B77" t="n">
-        <v>91605</v>
+        <v>92059</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8474,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651836</v>
+        <v>651843</v>
       </c>
       <c r="R77" t="n">
-        <v>6626151</v>
+        <v>6626170</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8536,32 +8531,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670614</v>
+        <v>129670581</v>
       </c>
       <c r="B78" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651826</v>
+        <v>651836</v>
       </c>
       <c r="R78" t="n">
-        <v>6626121</v>
+        <v>6626151</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8633,10 +8628,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670617</v>
+        <v>129670636</v>
       </c>
       <c r="B79" t="n">
-        <v>92058</v>
+        <v>98798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8644,21 +8639,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8668,10 +8663,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651843</v>
+        <v>651666</v>
       </c>
       <c r="R79" t="n">
-        <v>6626170</v>
+        <v>6626156</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8704,6 +8699,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8733,7 +8733,7 @@
         <v>129670630</v>
       </c>
       <c r="B80" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670636</v>
+        <v>129670598</v>
       </c>
       <c r="B81" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651666</v>
+        <v>651789</v>
       </c>
       <c r="R81" t="n">
-        <v>6626156</v>
+        <v>6626199</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670639</v>
+        <v>129670616</v>
       </c>
       <c r="B82" t="n">
-        <v>98797</v>
+        <v>92059</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651700</v>
+        <v>651831</v>
       </c>
       <c r="R82" t="n">
-        <v>6626184</v>
+        <v>6626150</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9000,11 +9000,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9031,10 +9026,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670616</v>
+        <v>129670639</v>
       </c>
       <c r="B83" t="n">
-        <v>92058</v>
+        <v>98798</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9042,21 +9037,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651831</v>
+        <v>651700</v>
       </c>
       <c r="R83" t="n">
-        <v>6626150</v>
+        <v>6626184</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9102,6 +9097,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9131,7 +9131,7 @@
         <v>129670606</v>
       </c>
       <c r="B84" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670591</v>
+        <v>129670646</v>
       </c>
       <c r="B85" t="n">
-        <v>91626</v>
+        <v>4779</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651709</v>
+        <v>651847</v>
       </c>
       <c r="R85" t="n">
-        <v>6626216</v>
+        <v>6626179</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9296,6 +9296,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9322,32 +9327,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670646</v>
+        <v>129670591</v>
       </c>
       <c r="B86" t="n">
-        <v>4779</v>
+        <v>91627</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651847</v>
+        <v>651709</v>
       </c>
       <c r="R86" t="n">
-        <v>6626179</v>
+        <v>6626216</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,11 +9398,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9524,7 +9524,7 @@
         <v>129718132</v>
       </c>
       <c r="B88" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>129718176</v>
       </c>
       <c r="B89" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B90" t="n">
-        <v>91605</v>
+        <v>105864</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R90" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B91" t="n">
-        <v>105863</v>
+        <v>91606</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R91" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9909,32 +9909,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B92" t="n">
-        <v>92058</v>
+        <v>92025</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
+        <v>6040186</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R92" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10006,32 +10006,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B93" t="n">
-        <v>92024</v>
+        <v>92059</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6040186</v>
+        <v>1209</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10041,10 +10041,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R93" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10106,7 +10106,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10588,10 +10588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717145</v>
+        <v>129716946</v>
       </c>
       <c r="B99" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10599,21 +10599,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651809</v>
+        <v>651888</v>
       </c>
       <c r="R99" t="n">
-        <v>6626096</v>
+        <v>6626032</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10685,45 +10685,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717137</v>
+        <v>129717884</v>
       </c>
       <c r="B100" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R100" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10782,32 +10791,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129716946</v>
+        <v>129717137</v>
       </c>
       <c r="B101" t="n">
-        <v>5177</v>
+        <v>91606</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10817,10 +10826,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651888</v>
+        <v>651809</v>
       </c>
       <c r="R101" t="n">
-        <v>6626032</v>
+        <v>6626096</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10879,54 +10888,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717884</v>
+        <v>129717145</v>
       </c>
       <c r="B102" t="n">
-        <v>98797</v>
+        <v>5197</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R102" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10988,7 +10988,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11576,32 +11576,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129729579</v>
+        <v>129729569</v>
       </c>
       <c r="B109" t="n">
-        <v>92258</v>
+        <v>91627</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651841</v>
+        <v>651836</v>
       </c>
       <c r="R109" t="n">
         <v>6626143</v>
@@ -11655,7 +11655,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11674,32 +11673,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129729569</v>
+        <v>129729579</v>
       </c>
       <c r="B110" t="n">
-        <v>91626</v>
+        <v>92259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11709,7 +11708,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651836</v>
+        <v>651841</v>
       </c>
       <c r="R110" t="n">
         <v>6626143</v>
@@ -11753,6 +11752,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12353,32 +12353,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729570</v>
+        <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>92058</v>
+        <v>91904</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651833</v>
+        <v>651890</v>
       </c>
       <c r="R117" t="n">
-        <v>6626152</v>
+        <v>6626043</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12450,32 +12450,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729575</v>
+        <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>91903</v>
+        <v>92059</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651890</v>
+        <v>651833</v>
       </c>
       <c r="R118" t="n">
-        <v>6626043</v>
+        <v>6626152</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12550,7 +12550,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -8240,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670614</v>
+        <v>129670630</v>
       </c>
       <c r="B75" t="n">
-        <v>92059</v>
+        <v>91379</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651826</v>
+        <v>651671</v>
       </c>
       <c r="R75" t="n">
-        <v>6626121</v>
+        <v>6626205</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8337,32 +8337,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670659</v>
+        <v>129670598</v>
       </c>
       <c r="B76" t="n">
-        <v>92297</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651798</v>
+        <v>651789</v>
       </c>
       <c r="R76" t="n">
-        <v>6626111</v>
+        <v>6626199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8408,6 +8408,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8434,7 +8439,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670617</v>
+        <v>129670614</v>
       </c>
       <c r="B77" t="n">
         <v>92059</v>
@@ -8469,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651843</v>
+        <v>651826</v>
       </c>
       <c r="R77" t="n">
-        <v>6626170</v>
+        <v>6626121</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8531,32 +8536,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670581</v>
+        <v>129670659</v>
       </c>
       <c r="B78" t="n">
-        <v>91606</v>
+        <v>92297</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8566,10 +8571,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651836</v>
+        <v>651798</v>
       </c>
       <c r="R78" t="n">
-        <v>6626151</v>
+        <v>6626111</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8628,10 +8633,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670636</v>
+        <v>129670617</v>
       </c>
       <c r="B79" t="n">
-        <v>98798</v>
+        <v>92059</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8639,21 +8644,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8668,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651666</v>
+        <v>651843</v>
       </c>
       <c r="R79" t="n">
-        <v>6626156</v>
+        <v>6626170</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8699,11 +8704,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8730,32 +8730,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670630</v>
+        <v>129670581</v>
       </c>
       <c r="B80" t="n">
-        <v>91379</v>
+        <v>91606</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651671</v>
+        <v>651836</v>
       </c>
       <c r="R80" t="n">
-        <v>6626205</v>
+        <v>6626151</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8827,32 +8827,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670598</v>
+        <v>129670636</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651789</v>
+        <v>651666</v>
       </c>
       <c r="R81" t="n">
-        <v>6626199</v>
+        <v>6626156</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Flyg och landningsläte</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -2753,10 +2753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670638</v>
+        <v>129670611</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>92059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,21 +2764,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651788</v>
+        <v>651780</v>
       </c>
       <c r="R19" t="n">
-        <v>6626118</v>
+        <v>6626166</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,11 +2824,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,32 +2850,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670655</v>
+        <v>129670618</v>
       </c>
       <c r="B20" t="n">
-        <v>100987</v>
+        <v>92059</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651655</v>
+        <v>651850</v>
       </c>
       <c r="R20" t="n">
-        <v>6626179</v>
+        <v>6626173</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2952,32 +2947,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670656</v>
+        <v>129670612</v>
       </c>
       <c r="B21" t="n">
-        <v>100987</v>
+        <v>92059</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651804</v>
+        <v>651783</v>
       </c>
       <c r="R21" t="n">
-        <v>6626213</v>
+        <v>6626160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3049,7 +3044,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670611</v>
+        <v>129670607</v>
       </c>
       <c r="B22" t="n">
         <v>92059</v>
@@ -3084,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651780</v>
+        <v>651794</v>
       </c>
       <c r="R22" t="n">
-        <v>6626166</v>
+        <v>6626119</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3146,32 +3141,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670618</v>
+        <v>129670586</v>
       </c>
       <c r="B23" t="n">
-        <v>92059</v>
+        <v>92324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651850</v>
+        <v>651896</v>
       </c>
       <c r="R23" t="n">
-        <v>6626173</v>
+        <v>6626042</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3243,32 +3238,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670612</v>
+        <v>129670655</v>
       </c>
       <c r="B24" t="n">
-        <v>92059</v>
+        <v>100987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651783</v>
+        <v>651655</v>
       </c>
       <c r="R24" t="n">
-        <v>6626160</v>
+        <v>6626179</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3340,32 +3335,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670607</v>
+        <v>129670656</v>
       </c>
       <c r="B25" t="n">
-        <v>92059</v>
+        <v>100987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651794</v>
+        <v>651804</v>
       </c>
       <c r="R25" t="n">
-        <v>6626119</v>
+        <v>6626213</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,32 +3432,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670586</v>
+        <v>129670638</v>
       </c>
       <c r="B26" t="n">
-        <v>92324</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651896</v>
+        <v>651788</v>
       </c>
       <c r="R26" t="n">
-        <v>6626042</v>
+        <v>6626118</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,6 +3503,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4708,32 +4708,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>92059</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R39" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4779,11 +4779,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4810,32 +4805,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670610</v>
+        <v>129670599</v>
       </c>
       <c r="B40" t="n">
-        <v>92059</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4845,10 +4840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651780</v>
+        <v>651890</v>
       </c>
       <c r="R40" t="n">
-        <v>6626169</v>
+        <v>6626039</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4881,6 +4876,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670599</v>
+        <v>129670647</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651890</v>
+        <v>651851</v>
       </c>
       <c r="R41" t="n">
-        <v>6626039</v>
+        <v>6626154</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -9521,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718132</v>
+        <v>129718176</v>
       </c>
       <c r="B88" t="n">
-        <v>92059</v>
+        <v>98815</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718176</v>
+        <v>129718132</v>
       </c>
       <c r="B89" t="n">
-        <v>98798</v>
+        <v>92076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9715,32 +9715,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129718056</v>
+        <v>129716221</v>
       </c>
       <c r="B90" t="n">
-        <v>105864</v>
+        <v>91623</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651824</v>
+        <v>651948</v>
       </c>
       <c r="R90" t="n">
-        <v>6626153</v>
+        <v>6626068</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9812,32 +9812,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129716221</v>
+        <v>129718056</v>
       </c>
       <c r="B91" t="n">
-        <v>91606</v>
+        <v>105881</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651948</v>
+        <v>651824</v>
       </c>
       <c r="R91" t="n">
-        <v>6626068</v>
+        <v>6626153</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9909,32 +9909,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717174</v>
+        <v>129717108</v>
       </c>
       <c r="B92" t="n">
-        <v>92025</v>
+        <v>92076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6040186</v>
+        <v>1209</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651792</v>
+        <v>651840</v>
       </c>
       <c r="R92" t="n">
-        <v>6626129</v>
+        <v>6626075</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10006,32 +10006,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717108</v>
+        <v>129717174</v>
       </c>
       <c r="B93" t="n">
-        <v>92059</v>
+        <v>92042</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>6040186</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10041,10 +10041,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651840</v>
+        <v>651792</v>
       </c>
       <c r="R93" t="n">
-        <v>6626075</v>
+        <v>6626129</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10106,7 +10106,7 @@
         <v>129716933</v>
       </c>
       <c r="B94" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>129716926</v>
       </c>
       <c r="B96" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>129716724</v>
       </c>
       <c r="B98" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10685,54 +10685,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717884</v>
+        <v>129717137</v>
       </c>
       <c r="B100" t="n">
-        <v>98798</v>
+        <v>91623</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651824</v>
+        <v>651809</v>
       </c>
       <c r="R100" t="n">
-        <v>6626153</v>
+        <v>6626096</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10791,32 +10782,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129717137</v>
+        <v>129717145</v>
       </c>
       <c r="B101" t="n">
-        <v>91606</v>
+        <v>5197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10888,45 +10879,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717145</v>
+        <v>129717884</v>
       </c>
       <c r="B102" t="n">
-        <v>5197</v>
+        <v>98815</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651809</v>
+        <v>651824</v>
       </c>
       <c r="R102" t="n">
-        <v>6626096</v>
+        <v>6626153</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10988,7 +10988,7 @@
         <v>129717904</v>
       </c>
       <c r="B103" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>129716568</v>
       </c>
       <c r="B104" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>129717005</v>
       </c>
       <c r="B105" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>129716641</v>
       </c>
       <c r="B106" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>129717132</v>
       </c>
       <c r="B107" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>129717100</v>
       </c>
       <c r="B108" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11576,32 +11576,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129729569</v>
+        <v>129729579</v>
       </c>
       <c r="B109" t="n">
-        <v>91627</v>
+        <v>92276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651836</v>
+        <v>651841</v>
       </c>
       <c r="R109" t="n">
         <v>6626143</v>
@@ -11655,6 +11655,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11673,32 +11674,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129729579</v>
+        <v>129729569</v>
       </c>
       <c r="B110" t="n">
-        <v>92259</v>
+        <v>91644</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11708,7 +11709,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651841</v>
+        <v>651836</v>
       </c>
       <c r="R110" t="n">
         <v>6626143</v>
@@ -11752,7 +11753,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>129729573</v>
       </c>
       <c r="B111" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>129729567</v>
       </c>
       <c r="B112" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>129729577</v>
       </c>
       <c r="B113" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>129729576</v>
       </c>
       <c r="B114" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>129729563</v>
       </c>
       <c r="B115" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>129729565</v>
       </c>
       <c r="B116" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>129729575</v>
       </c>
       <c r="B117" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>129729570</v>
       </c>
       <c r="B118" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>129729571</v>
       </c>
       <c r="B119" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>129729566</v>
       </c>
       <c r="B120" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>129729564</v>
       </c>
       <c r="B121" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>129729568</v>
       </c>
       <c r="B122" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60791717</v>
+        <v>88956906</v>
       </c>
       <c r="B2" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2058</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Lunsen, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651782.7986559763</v>
+        <v>651891</v>
       </c>
       <c r="R2" t="n">
-        <v>6626159.878078155</v>
+        <v>6626046</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-08-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex. under äldre gran i mossrik skog.</t>
+          <t>2020-11-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,82 +768,88 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60791718</v>
+        <v>129670649</v>
       </c>
       <c r="B3" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2058</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651661.8851508767</v>
+        <v>651934</v>
       </c>
       <c r="R3" t="n">
-        <v>6626162.521750844</v>
+        <v>6626028</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,27 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-08-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca. 30 ex. under äldre gran i mossrik skog.</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,83 +889,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69524489</v>
+        <v>129670626</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651791.5858935614</v>
+        <v>651935</v>
       </c>
       <c r="R4" t="n">
-        <v>6626179.915575871</v>
+        <v>6626058</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,27 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-08-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex.</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,36 +986,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72088660</v>
+        <v>129670627</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,46 +1013,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651802.2003113041</v>
+        <v>651922</v>
       </c>
       <c r="R5" t="n">
-        <v>6626155.118136751</v>
+        <v>6626059</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,27 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 ex. på äldre, levande tall, omkr. 117 cm.</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,46 +1083,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Äldre, levande tall. # Tall</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72088659</v>
+        <v>129670628</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,46 +1110,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651696.4864701636</v>
+        <v>651867</v>
       </c>
       <c r="R6" t="n">
-        <v>6626218.931773982</v>
+        <v>6626099</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,27 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 ex. på äldre, levande tall, omkr. 136 cm.</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,46 +1180,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Äldre, levande tall. # Tall</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72088661</v>
+        <v>129716753</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,46 +1207,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651672.2320515192</v>
+        <v>651937</v>
       </c>
       <c r="R7" t="n">
-        <v>6626144.272844349</v>
+        <v>6626030</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1429,27 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2002-11-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2002-11-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 ex. på levande tall, omkr. 142 cm.</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,89 +1277,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Levande tall. # Tall</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75811332</v>
+        <v>129716933</v>
       </c>
       <c r="B8" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651829.2828604176</v>
+        <v>651888</v>
       </c>
       <c r="R8" t="n">
-        <v>6626135.533247456</v>
+        <v>6626032</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1566,27 +1358,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 132 cm.</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1597,85 +1374,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75905513</v>
+        <v>129729575</v>
       </c>
       <c r="B9" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651828.4168627197</v>
+        <v>651890</v>
       </c>
       <c r="R9" t="n">
-        <v>6626045.172531778</v>
+        <v>6626043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,27 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 dm2 på gren på levande tall, omkr. 113 cm.</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1733,81 +1471,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Gren på levande tall. # Tall</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76009482</v>
+        <v>129729576</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651782.4019002792</v>
+        <v>651923</v>
       </c>
       <c r="R10" t="n">
-        <v>6626119.998194215</v>
+        <v>6626013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1834,27 +1552,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter.</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,27 +1572,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76009484</v>
+        <v>129670659</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,37 +1595,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651781.7894026903</v>
+        <v>651798</v>
       </c>
       <c r="R11" t="n">
-        <v>6626159.836950662</v>
+        <v>6626111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1951,27 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Några bladrosetter.</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1986,65 +1669,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>76009483</v>
+        <v>129670573</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651802.0889981296</v>
+        <v>651828</v>
       </c>
       <c r="R12" t="n">
-        <v>6626170.251635929</v>
+        <v>6626081</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2068,27 +1746,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Några bladrosetter.</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,76 +1766,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88956906</v>
+        <v>129670574</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björklunda, Lunsen, Knivsta, Upl</t>
+          <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651890.5700202603</v>
+        <v>651813</v>
       </c>
       <c r="R13" t="n">
-        <v>6626045.688011552</v>
+        <v>6626139</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2196,22 +1843,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2222,73 +1864,48 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Lindell</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Lindell</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670652</v>
+        <v>129670575</v>
       </c>
       <c r="B14" t="n">
-        <v>92256</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2298,10 +1915,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651866</v>
+        <v>651902</v>
       </c>
       <c r="R14" t="n">
-        <v>6626192</v>
+        <v>6626042</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2360,10 +1977,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670575</v>
+        <v>129670576</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651902</v>
+        <v>651928</v>
       </c>
       <c r="R15" t="n">
-        <v>6626042</v>
+        <v>6626010</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,32 +2074,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670653</v>
+        <v>129670577</v>
       </c>
       <c r="B16" t="n">
-        <v>92256</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2492,10 +2109,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651890</v>
+        <v>651934</v>
       </c>
       <c r="R16" t="n">
-        <v>6626144</v>
+        <v>6626035</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2554,10 +2171,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129670584</v>
+        <v>129670578</v>
       </c>
       <c r="B17" t="n">
-        <v>91606</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651906</v>
+        <v>651796</v>
       </c>
       <c r="R17" t="n">
-        <v>6626091</v>
+        <v>6626108</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2651,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129670602</v>
+        <v>129670579</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,21 +2279,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2686,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651892</v>
+        <v>651794</v>
       </c>
       <c r="R18" t="n">
-        <v>6626058</v>
+        <v>6626119</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2722,11 +2339,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,32 +2365,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129670611</v>
+        <v>129670580</v>
       </c>
       <c r="B19" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2788,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651780</v>
+        <v>651826</v>
       </c>
       <c r="R19" t="n">
-        <v>6626166</v>
+        <v>6626121</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2850,32 +2462,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129670618</v>
+        <v>129670581</v>
       </c>
       <c r="B20" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651850</v>
+        <v>651836</v>
       </c>
       <c r="R20" t="n">
-        <v>6626173</v>
+        <v>6626151</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2947,32 +2559,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129670612</v>
+        <v>129670582</v>
       </c>
       <c r="B21" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2594,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651783</v>
+        <v>651839</v>
       </c>
       <c r="R21" t="n">
-        <v>6626160</v>
+        <v>6626178</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3044,32 +2656,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129670607</v>
+        <v>129670583</v>
       </c>
       <c r="B22" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3079,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651794</v>
+        <v>651907</v>
       </c>
       <c r="R22" t="n">
-        <v>6626119</v>
+        <v>6626130</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3141,32 +2753,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129670586</v>
+        <v>129670584</v>
       </c>
       <c r="B23" t="n">
-        <v>92324</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651896</v>
+        <v>651906</v>
       </c>
       <c r="R23" t="n">
-        <v>6626042</v>
+        <v>6626091</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3238,32 +2850,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129670655</v>
+        <v>129670585</v>
       </c>
       <c r="B24" t="n">
-        <v>100987</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651655</v>
+        <v>651912</v>
       </c>
       <c r="R24" t="n">
-        <v>6626179</v>
+        <v>6626052</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3335,32 +2947,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129670656</v>
+        <v>129716221</v>
       </c>
       <c r="B25" t="n">
-        <v>100987</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3370,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651804</v>
+        <v>651948</v>
       </c>
       <c r="R25" t="n">
-        <v>6626213</v>
+        <v>6626068</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3400,12 +3012,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,44 +3032,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129670638</v>
+        <v>129716568</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3079,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651788</v>
+        <v>651940</v>
       </c>
       <c r="R26" t="n">
-        <v>6626118</v>
+        <v>6626011</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3497,17 +3109,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,44 +3129,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129670588</v>
+        <v>129717100</v>
       </c>
       <c r="B27" t="n">
-        <v>92324</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3569,10 +3176,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651868</v>
+        <v>651840</v>
       </c>
       <c r="R27" t="n">
-        <v>6626205</v>
+        <v>6626075</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3599,12 +3206,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,44 +3226,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129670620</v>
+        <v>129717137</v>
       </c>
       <c r="B28" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3273,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651894</v>
+        <v>651809</v>
       </c>
       <c r="R28" t="n">
-        <v>6626133</v>
+        <v>6626096</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3696,12 +3303,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,22 +3323,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129670577</v>
+        <v>129729563</v>
       </c>
       <c r="B29" t="n">
-        <v>91606</v>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,13 +3370,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651934</v>
+        <v>651787</v>
       </c>
       <c r="R29" t="n">
-        <v>6626035</v>
+        <v>6626109</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3793,12 +3400,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,22 +3420,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129670582</v>
+        <v>129729564</v>
       </c>
       <c r="B30" t="n">
-        <v>91606</v>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3860,13 +3467,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651839</v>
+        <v>651819</v>
       </c>
       <c r="R30" t="n">
-        <v>6626178</v>
+        <v>6626182</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3890,12 +3497,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,44 +3517,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129670625</v>
+        <v>129729565</v>
       </c>
       <c r="B31" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3957,13 +3564,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651793</v>
+        <v>651830</v>
       </c>
       <c r="R31" t="n">
-        <v>6626135</v>
+        <v>6626219</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3987,12 +3594,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4007,22 +3614,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129670592</v>
+        <v>129729566</v>
       </c>
       <c r="B32" t="n">
-        <v>91627</v>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,21 +3637,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,13 +3661,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651842</v>
+        <v>651831</v>
       </c>
       <c r="R32" t="n">
-        <v>6626152</v>
+        <v>6626182</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4084,12 +3691,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4104,44 +3711,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129670657</v>
+        <v>129729567</v>
       </c>
       <c r="B33" t="n">
-        <v>92259</v>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4151,13 +3758,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651836</v>
+        <v>651833</v>
       </c>
       <c r="R33" t="n">
-        <v>6626075</v>
+        <v>6626148</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4181,12 +3788,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4201,44 +3808,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670651</v>
+        <v>129729568</v>
       </c>
       <c r="B34" t="n">
-        <v>92256</v>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,13 +3855,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651804</v>
+        <v>651923</v>
       </c>
       <c r="R34" t="n">
-        <v>6626204</v>
+        <v>6626013</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4278,12 +3885,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4298,22 +3905,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670585</v>
+        <v>129670603</v>
       </c>
       <c r="B35" t="n">
-        <v>91606</v>
+        <v>92369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,21 +3928,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4345,10 +3952,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651912</v>
+        <v>651922</v>
       </c>
       <c r="R35" t="n">
-        <v>6626052</v>
+        <v>6626001</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4407,10 +4014,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670601</v>
+        <v>129670605</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>92369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4418,21 +4025,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4049,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651723</v>
+        <v>651938</v>
       </c>
       <c r="R36" t="n">
-        <v>6626229</v>
+        <v>6626032</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4478,11 +4085,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,32 +4111,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129670644</v>
+        <v>129670606</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>92369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4146,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651725</v>
+        <v>651875</v>
       </c>
       <c r="R37" t="n">
-        <v>6626217</v>
+        <v>6626072</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4580,11 +4182,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4611,32 +4208,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129670640</v>
+        <v>129670607</v>
       </c>
       <c r="B38" t="n">
-        <v>98798</v>
+        <v>92369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4646,10 +4243,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651783</v>
+        <v>651794</v>
       </c>
       <c r="R38" t="n">
-        <v>6626130</v>
+        <v>6626119</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4708,14 +4305,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129670610</v>
+        <v>129670608</v>
       </c>
       <c r="B39" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4743,10 +4340,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651780</v>
+        <v>651799</v>
       </c>
       <c r="R39" t="n">
-        <v>6626169</v>
+        <v>6626199</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4805,10 +4402,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129670599</v>
+        <v>129670609</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>92369</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,21 +4413,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4437,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651890</v>
+        <v>651777</v>
       </c>
       <c r="R40" t="n">
-        <v>6626039</v>
+        <v>6626177</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4876,11 +4473,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,32 +4499,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129670647</v>
+        <v>129670610</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651851</v>
+        <v>651780</v>
       </c>
       <c r="R41" t="n">
-        <v>6626154</v>
+        <v>6626169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4978,11 +4570,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5009,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129670654</v>
+        <v>129670611</v>
       </c>
       <c r="B42" t="n">
-        <v>92256</v>
+        <v>92369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5044,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651893</v>
+        <v>651780</v>
       </c>
       <c r="R42" t="n">
-        <v>6626104</v>
+        <v>6626166</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5106,14 +4693,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129670619</v>
+        <v>129670612</v>
       </c>
       <c r="B43" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5141,10 +4728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651882</v>
+        <v>651783</v>
       </c>
       <c r="R43" t="n">
-        <v>6626177</v>
+        <v>6626160</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5203,10 +4790,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129670626</v>
+        <v>129670613</v>
       </c>
       <c r="B44" t="n">
-        <v>91904</v>
+        <v>92369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5214,21 +4801,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651935</v>
+        <v>651827</v>
       </c>
       <c r="R44" t="n">
-        <v>6626058</v>
+        <v>6626081</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5300,10 +4887,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129670627</v>
+        <v>129670614</v>
       </c>
       <c r="B45" t="n">
-        <v>91904</v>
+        <v>92369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5311,21 +4898,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +4922,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651922</v>
+        <v>651826</v>
       </c>
       <c r="R45" t="n">
-        <v>6626059</v>
+        <v>6626121</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5397,10 +4984,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129670649</v>
+        <v>129670615</v>
       </c>
       <c r="B46" t="n">
-        <v>83051</v>
+        <v>92369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +4995,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5019,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651934</v>
+        <v>651823</v>
       </c>
       <c r="R46" t="n">
-        <v>6626028</v>
+        <v>6626169</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5494,14 +5081,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129670608</v>
+        <v>129670616</v>
       </c>
       <c r="B47" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5529,10 +5116,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651799</v>
+        <v>651831</v>
       </c>
       <c r="R47" t="n">
-        <v>6626199</v>
+        <v>6626150</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5591,14 +5178,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129670613</v>
+        <v>129670617</v>
       </c>
       <c r="B48" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5626,10 +5213,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651827</v>
+        <v>651843</v>
       </c>
       <c r="R48" t="n">
-        <v>6626081</v>
+        <v>6626170</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5688,10 +5275,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129670590</v>
+        <v>129670618</v>
       </c>
       <c r="B49" t="n">
-        <v>91627</v>
+        <v>92369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,21 +5286,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5723,10 +5310,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651906</v>
+        <v>651850</v>
       </c>
       <c r="R49" t="n">
-        <v>6626033</v>
+        <v>6626173</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5785,32 +5372,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129670587</v>
+        <v>129670619</v>
       </c>
       <c r="B50" t="n">
-        <v>92324</v>
+        <v>92369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5407,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651796</v>
+        <v>651882</v>
       </c>
       <c r="R50" t="n">
-        <v>6626068</v>
+        <v>6626177</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5882,32 +5469,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129670637</v>
+        <v>129670620</v>
       </c>
       <c r="B51" t="n">
-        <v>98798</v>
+        <v>92369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5917,10 +5504,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651703</v>
+        <v>651894</v>
       </c>
       <c r="R51" t="n">
-        <v>6626171</v>
+        <v>6626133</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5953,11 +5540,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5984,10 +5566,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129670579</v>
+        <v>129670621</v>
       </c>
       <c r="B52" t="n">
-        <v>91606</v>
+        <v>92369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5995,21 +5577,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6019,10 +5601,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651794</v>
+        <v>651904</v>
       </c>
       <c r="R52" t="n">
-        <v>6626119</v>
+        <v>6626101</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6081,14 +5663,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129670621</v>
+        <v>129670622</v>
       </c>
       <c r="B53" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6116,10 +5698,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651904</v>
+        <v>651922</v>
       </c>
       <c r="R53" t="n">
-        <v>6626101</v>
+        <v>6626011</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6178,10 +5760,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129670628</v>
+        <v>129670623</v>
       </c>
       <c r="B54" t="n">
-        <v>91904</v>
+        <v>92369</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6189,21 +5771,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6213,10 +5795,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651867</v>
+        <v>651877</v>
       </c>
       <c r="R54" t="n">
-        <v>6626099</v>
+        <v>6626056</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6275,32 +5857,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129670650</v>
+        <v>129670624</v>
       </c>
       <c r="B55" t="n">
-        <v>92256</v>
+        <v>92369</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6310,10 +5892,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651923</v>
+        <v>651791</v>
       </c>
       <c r="R55" t="n">
-        <v>6626100</v>
+        <v>6626110</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6372,14 +5954,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129670609</v>
+        <v>129670625</v>
       </c>
       <c r="B56" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6407,10 +5989,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651777</v>
+        <v>651793</v>
       </c>
       <c r="R56" t="n">
-        <v>6626177</v>
+        <v>6626135</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6469,14 +6051,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129670622</v>
+        <v>129716641</v>
       </c>
       <c r="B57" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6504,7 +6086,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651922</v>
+        <v>651940</v>
       </c>
       <c r="R57" t="n">
         <v>6626011</v>
@@ -6534,12 +6116,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6554,22 +6136,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129670580</v>
+        <v>129716724</v>
       </c>
       <c r="B58" t="n">
-        <v>91606</v>
+        <v>92369</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6577,21 +6159,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6601,10 +6183,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651826</v>
+        <v>651937</v>
       </c>
       <c r="R58" t="n">
-        <v>6626121</v>
+        <v>6626030</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6631,12 +6213,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6651,26 +6233,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129670615</v>
+        <v>129717108</v>
       </c>
       <c r="B59" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6698,10 +6280,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651823</v>
+        <v>651840</v>
       </c>
       <c r="R59" t="n">
-        <v>6626169</v>
+        <v>6626075</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6728,12 +6310,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6748,22 +6330,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129670578</v>
+        <v>129717132</v>
       </c>
       <c r="B60" t="n">
-        <v>91606</v>
+        <v>92369</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6771,21 +6353,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6795,10 +6377,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651796</v>
+        <v>651809</v>
       </c>
       <c r="R60" t="n">
-        <v>6626108</v>
+        <v>6626096</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6825,12 +6407,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6845,26 +6427,26 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129670605</v>
+        <v>129718132</v>
       </c>
       <c r="B61" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6892,13 +6474,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651938</v>
+        <v>651797</v>
       </c>
       <c r="R61" t="n">
-        <v>6626032</v>
+        <v>6626076</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6922,12 +6504,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6942,22 +6524,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129670576</v>
+        <v>129729570</v>
       </c>
       <c r="B62" t="n">
-        <v>91606</v>
+        <v>92369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6965,21 +6547,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6989,13 +6571,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651928</v>
+        <v>651833</v>
       </c>
       <c r="R62" t="n">
-        <v>6626010</v>
+        <v>6626152</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7019,12 +6601,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7039,26 +6621,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129670623</v>
+        <v>129729571</v>
       </c>
       <c r="B63" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7086,13 +6668,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651877</v>
+        <v>651915</v>
       </c>
       <c r="R63" t="n">
-        <v>6626056</v>
+        <v>6626012</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7116,12 +6698,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7136,26 +6718,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129670624</v>
+        <v>129729572</v>
       </c>
       <c r="B64" t="n">
-        <v>92059</v>
+        <v>92369</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7183,13 +6765,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651791</v>
+        <v>651931</v>
       </c>
       <c r="R64" t="n">
-        <v>6626110</v>
+        <v>6626008</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7213,12 +6795,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7233,22 +6815,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129670572</v>
+        <v>129670650</v>
       </c>
       <c r="B65" t="n">
-        <v>91570</v>
+        <v>92564</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7256,21 +6838,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651860</v>
+        <v>651923</v>
       </c>
       <c r="R65" t="n">
-        <v>6626196</v>
+        <v>6626100</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7342,10 +6924,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129670645</v>
+        <v>129670651</v>
       </c>
       <c r="B66" t="n">
-        <v>4779</v>
+        <v>92564</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7353,21 +6935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7377,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651662</v>
+        <v>651804</v>
       </c>
       <c r="R66" t="n">
-        <v>6626158</v>
+        <v>6626204</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7413,11 +6995,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7444,10 +7021,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129670643</v>
+        <v>129670652</v>
       </c>
       <c r="B67" t="n">
-        <v>4779</v>
+        <v>92564</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7455,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7479,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651826</v>
+        <v>651866</v>
       </c>
       <c r="R67" t="n">
-        <v>6626121</v>
+        <v>6626192</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7515,11 +7092,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7546,32 +7118,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129670583</v>
+        <v>129670653</v>
       </c>
       <c r="B68" t="n">
-        <v>91606</v>
+        <v>92564</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651907</v>
+        <v>651890</v>
       </c>
       <c r="R68" t="n">
-        <v>6626130</v>
+        <v>6626144</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7643,32 +7215,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129670600</v>
+        <v>129670654</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>92564</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651666</v>
+        <v>651893</v>
       </c>
       <c r="R69" t="n">
-        <v>6626239</v>
+        <v>6626104</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7714,11 +7286,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,48 +7312,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129670635</v>
+        <v>60791717</v>
       </c>
       <c r="B70" t="n">
-        <v>98798</v>
+        <v>93205</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2058</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651924</v>
+        <v>651783</v>
       </c>
       <c r="R70" t="n">
-        <v>6626060</v>
+        <v>6626160</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7810,17 +7386,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2005-08-22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2005-08-22</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>Ca. 10 ex. under äldre gran i mossrik skog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7831,64 +7407,78 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129670574</v>
+        <v>60791718</v>
       </c>
       <c r="B71" t="n">
-        <v>91606</v>
+        <v>93205</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>2058</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651813</v>
+        <v>651662</v>
       </c>
       <c r="R71" t="n">
-        <v>6626139</v>
+        <v>6626163</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7912,17 +7502,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2005-08-22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2005-08-22</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tallåga</t>
+          <t>Ca. 30 ex. under äldre gran i mossrik skog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7933,48 +7523,53 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129670573</v>
+        <v>129670630</v>
       </c>
       <c r="B72" t="n">
-        <v>91606</v>
+        <v>91680</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7984,10 +7579,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651828</v>
+        <v>651671</v>
       </c>
       <c r="R72" t="n">
-        <v>6626081</v>
+        <v>6626205</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8046,10 +7641,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129670658</v>
+        <v>129670586</v>
       </c>
       <c r="B73" t="n">
-        <v>92259</v>
+        <v>92632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8057,21 +7652,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6031</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8081,10 +7676,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651860</v>
+        <v>651896</v>
       </c>
       <c r="R73" t="n">
-        <v>6626084</v>
+        <v>6626042</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8143,10 +7738,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129670629</v>
+        <v>129670587</v>
       </c>
       <c r="B74" t="n">
-        <v>97669</v>
+        <v>92632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8154,21 +7749,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8178,10 +7773,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651815</v>
+        <v>651796</v>
       </c>
       <c r="R74" t="n">
-        <v>6626081</v>
+        <v>6626068</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8240,10 +7835,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129670630</v>
+        <v>129670588</v>
       </c>
       <c r="B75" t="n">
-        <v>91379</v>
+        <v>92632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,21 +7846,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3215</v>
+        <v>3298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8275,7 +7870,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651671</v>
+        <v>651868</v>
       </c>
       <c r="R75" t="n">
         <v>6626205</v>
@@ -8337,48 +7932,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129670598</v>
+        <v>75905513</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>92333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651789</v>
+        <v>651828</v>
       </c>
       <c r="R76" t="n">
-        <v>6626199</v>
+        <v>6626045</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8402,17 +8006,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Flyg och landningsläte</t>
+          <t>1 dm2 på gren på levande tall, omkr. 113 cm.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8423,64 +8027,88 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Gren på levande tall. # Tall</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129670614</v>
+        <v>69524489</v>
       </c>
       <c r="B77" t="n">
-        <v>92059</v>
+        <v>93209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>4366</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651826</v>
+        <v>651792</v>
       </c>
       <c r="R77" t="n">
-        <v>6626121</v>
+        <v>6626180</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8504,12 +8132,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2005-08-22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2005-08-22</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8520,64 +8153,79 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129670659</v>
+        <v>95533022</v>
       </c>
       <c r="B78" t="n">
-        <v>92297</v>
+        <v>93215</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda, Lunsens NR, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651798</v>
+        <v>651648</v>
       </c>
       <c r="R78" t="n">
-        <v>6626111</v>
+        <v>6626170</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8601,12 +8249,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8621,60 +8269,69 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129670617</v>
+        <v>72088659</v>
       </c>
       <c r="B79" t="n">
-        <v>92059</v>
+        <v>91930</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651843</v>
+        <v>651696</v>
       </c>
       <c r="R79" t="n">
-        <v>6626170</v>
+        <v>6626219</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8698,12 +8355,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2004-04-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>2 ex. på äldre, levande tall, omkr. 136 cm.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8714,26 +8376,41 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Äldre, levande tall. # Tall</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129670581</v>
+        <v>72088660</v>
       </c>
       <c r="B80" t="n">
-        <v>91606</v>
+        <v>91930</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8741,37 +8418,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651836</v>
+        <v>651802</v>
       </c>
       <c r="R80" t="n">
-        <v>6626151</v>
+        <v>6626155</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8795,12 +8481,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2004-04-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>2 ex. på äldre, levande tall, omkr. 117 cm.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8811,64 +8502,88 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Äldre, levande tall. # Tall</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129670636</v>
+        <v>72088661</v>
       </c>
       <c r="B81" t="n">
-        <v>98798</v>
+        <v>91930</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651666</v>
+        <v>651672</v>
       </c>
       <c r="R81" t="n">
-        <v>6626156</v>
+        <v>6626144</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8892,17 +8607,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2002-11-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2002-11-18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>1 ex. på levande tall, omkr. 142 cm.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8913,48 +8628,63 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Levande tall. # Tall</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129670616</v>
+        <v>129670590</v>
       </c>
       <c r="B82" t="n">
-        <v>92059</v>
+        <v>91930</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8964,10 +8694,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651831</v>
+        <v>651906</v>
       </c>
       <c r="R82" t="n">
-        <v>6626150</v>
+        <v>6626033</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9026,32 +8756,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129670639</v>
+        <v>129670591</v>
       </c>
       <c r="B83" t="n">
-        <v>98798</v>
+        <v>91930</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9061,10 +8791,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651700</v>
+        <v>651709</v>
       </c>
       <c r="R83" t="n">
-        <v>6626184</v>
+        <v>6626216</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9097,11 +8827,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9128,32 +8853,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129670606</v>
+        <v>129670592</v>
       </c>
       <c r="B84" t="n">
-        <v>92059</v>
+        <v>91930</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +8888,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651875</v>
+        <v>651842</v>
       </c>
       <c r="R84" t="n">
-        <v>6626072</v>
+        <v>6626152</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9225,32 +8950,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129670646</v>
+        <v>129729569</v>
       </c>
       <c r="B85" t="n">
-        <v>4779</v>
+        <v>91930</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,13 +8985,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651847</v>
+        <v>651836</v>
       </c>
       <c r="R85" t="n">
-        <v>6626179</v>
+        <v>6626143</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9290,17 +9015,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9315,44 +9035,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129670591</v>
+        <v>129670572</v>
       </c>
       <c r="B86" t="n">
-        <v>91627</v>
+        <v>91872</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9362,10 +9082,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651709</v>
+        <v>651860</v>
       </c>
       <c r="R86" t="n">
-        <v>6626216</v>
+        <v>6626196</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9424,10 +9144,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129717141</v>
+        <v>129670657</v>
       </c>
       <c r="B87" t="n">
-        <v>5177</v>
+        <v>92567</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9435,21 +9155,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9459,10 +9179,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>651809</v>
+        <v>651836</v>
       </c>
       <c r="R87" t="n">
-        <v>6626096</v>
+        <v>6626075</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9489,12 +9209,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9509,44 +9229,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129718176</v>
+        <v>129670658</v>
       </c>
       <c r="B88" t="n">
-        <v>98820</v>
+        <v>92567</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9556,13 +9276,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>651797</v>
+        <v>651860</v>
       </c>
       <c r="R88" t="n">
-        <v>6626076</v>
+        <v>6626084</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9586,12 +9306,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9606,44 +9326,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129718132</v>
+        <v>129729579</v>
       </c>
       <c r="B89" t="n">
-        <v>92081</v>
+        <v>92567</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>6031</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9653,10 +9373,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>651797</v>
+        <v>651841</v>
       </c>
       <c r="R89" t="n">
-        <v>6626076</v>
+        <v>6626143</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9697,28 +9417,29 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129718056</v>
+        <v>129670598</v>
       </c>
       <c r="B90" t="n">
-        <v>105886</v>
+        <v>57950</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9726,21 +9447,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9750,10 +9471,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>651824</v>
+        <v>651789</v>
       </c>
       <c r="R90" t="n">
-        <v>6626153</v>
+        <v>6626199</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9780,12 +9501,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Flyg och landningsläte</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9800,44 +9526,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129716221</v>
+        <v>129670599</v>
       </c>
       <c r="B91" t="n">
-        <v>91628</v>
+        <v>57950</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9847,10 +9573,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651948</v>
+        <v>651890</v>
       </c>
       <c r="R91" t="n">
-        <v>6626068</v>
+        <v>6626039</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9877,12 +9603,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9897,44 +9628,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129717108</v>
+        <v>129670600</v>
       </c>
       <c r="B92" t="n">
-        <v>92081</v>
+        <v>57950</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9944,10 +9675,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651840</v>
+        <v>651666</v>
       </c>
       <c r="R92" t="n">
-        <v>6626075</v>
+        <v>6626239</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9974,12 +9705,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9994,44 +9730,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129717174</v>
+        <v>129670601</v>
       </c>
       <c r="B93" t="n">
-        <v>92047</v>
+        <v>57950</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6040186</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10041,10 +9777,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651792</v>
+        <v>651723</v>
       </c>
       <c r="R93" t="n">
-        <v>6626129</v>
+        <v>6626229</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10071,12 +9807,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10091,44 +9832,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129716933</v>
+        <v>129670602</v>
       </c>
       <c r="B94" t="n">
-        <v>91926</v>
+        <v>57950</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10138,10 +9879,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>651888</v>
+        <v>651892</v>
       </c>
       <c r="R94" t="n">
-        <v>6626032</v>
+        <v>6626058</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10168,12 +9909,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Landningsläte</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10188,12 +9934,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10203,7 +9949,7 @@
         <v>129716639</v>
       </c>
       <c r="B95" t="n">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10297,32 +10043,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129716926</v>
+        <v>129716946</v>
       </c>
       <c r="B96" t="n">
-        <v>91926</v>
+        <v>5179</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10332,10 +10078,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>651937</v>
+        <v>651888</v>
       </c>
       <c r="R96" t="n">
-        <v>6626030</v>
+        <v>6626032</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10394,10 +10140,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129716486</v>
+        <v>129717141</v>
       </c>
       <c r="B97" t="n">
-        <v>5197</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10405,21 +10151,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10429,10 +10175,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>651945</v>
+        <v>651809</v>
       </c>
       <c r="R97" t="n">
-        <v>6626052</v>
+        <v>6626096</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10491,48 +10237,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129716724</v>
+        <v>75811332</v>
       </c>
       <c r="B98" t="n">
-        <v>92081</v>
+        <v>4781</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>651937</v>
+        <v>651829</v>
       </c>
       <c r="R98" t="n">
-        <v>6626030</v>
+        <v>6626136</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10556,12 +10307,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 132 cm.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10572,70 +10328,71 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129717884</v>
+        <v>129670643</v>
       </c>
       <c r="B99" t="n">
-        <v>98820</v>
+        <v>4781</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651824</v>
+        <v>651826</v>
       </c>
       <c r="R99" t="n">
-        <v>6626153</v>
+        <v>6626121</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10662,12 +10419,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10682,22 +10444,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129717145</v>
+        <v>129670644</v>
       </c>
       <c r="B100" t="n">
-        <v>5197</v>
+        <v>4781</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10705,21 +10467,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10729,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651809</v>
+        <v>651725</v>
       </c>
       <c r="R100" t="n">
-        <v>6626096</v>
+        <v>6626217</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10759,12 +10521,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10779,22 +10546,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129716946</v>
+        <v>129670645</v>
       </c>
       <c r="B101" t="n">
-        <v>5177</v>
+        <v>4781</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10802,21 +10569,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10826,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651888</v>
+        <v>651662</v>
       </c>
       <c r="R101" t="n">
-        <v>6626032</v>
+        <v>6626158</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10856,12 +10623,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10876,44 +10648,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129717137</v>
+        <v>129670646</v>
       </c>
       <c r="B102" t="n">
-        <v>91628</v>
+        <v>4781</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10923,10 +10695,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651809</v>
+        <v>651847</v>
       </c>
       <c r="R102" t="n">
-        <v>6626096</v>
+        <v>6626179</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10953,12 +10725,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10973,69 +10750,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129717904</v>
+        <v>129670647</v>
       </c>
       <c r="B103" t="n">
-        <v>98820</v>
+        <v>4781</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>651836</v>
+        <v>651851</v>
       </c>
       <c r="R103" t="n">
-        <v>6626167</v>
+        <v>6626154</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11059,12 +10827,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11079,44 +10852,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129716568</v>
+        <v>129716486</v>
       </c>
       <c r="B104" t="n">
-        <v>91628</v>
+        <v>5199</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11126,10 +10899,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>651940</v>
+        <v>651945</v>
       </c>
       <c r="R104" t="n">
-        <v>6626011</v>
+        <v>6626052</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11188,32 +10961,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129717005</v>
+        <v>129717145</v>
       </c>
       <c r="B105" t="n">
-        <v>98820</v>
+        <v>5199</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11223,10 +10996,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>651874</v>
+        <v>651809</v>
       </c>
       <c r="R105" t="n">
-        <v>6626042</v>
+        <v>6626096</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11285,10 +11058,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129717132</v>
+        <v>76009482</v>
       </c>
       <c r="B106" t="n">
-        <v>92081</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11296,37 +11069,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651809</v>
+        <v>651782</v>
       </c>
       <c r="R106" t="n">
-        <v>6626096</v>
+        <v>6626120</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11350,12 +11123,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11370,60 +11148,60 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129717100</v>
+        <v>76009483</v>
       </c>
       <c r="B107" t="n">
-        <v>91628</v>
+        <v>99118</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651840</v>
+        <v>651802</v>
       </c>
       <c r="R107" t="n">
-        <v>6626075</v>
+        <v>6626170</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11447,12 +11225,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Några bladrosetter.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11467,22 +11250,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129716641</v>
+        <v>76009484</v>
       </c>
       <c r="B108" t="n">
-        <v>92081</v>
+        <v>99118</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11490,37 +11273,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Björklunda, Upl</t>
+          <t>Björklunda 2 km NO om Alsike kyrka, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651940</v>
+        <v>651782</v>
       </c>
       <c r="R108" t="n">
-        <v>6626011</v>
+        <v>6626160</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11544,12 +11327,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2004-04-27</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Några bladrosetter.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11564,44 +11352,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129729579</v>
+        <v>129670635</v>
       </c>
       <c r="B109" t="n">
-        <v>92291</v>
+        <v>99118</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11611,13 +11399,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651841</v>
+        <v>651924</v>
       </c>
       <c r="R109" t="n">
-        <v>6626143</v>
+        <v>6626060</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11641,12 +11429,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11655,51 +11448,50 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129729569</v>
+        <v>129670636</v>
       </c>
       <c r="B110" t="n">
-        <v>91659</v>
+        <v>99118</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11709,13 +11501,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651836</v>
+        <v>651666</v>
       </c>
       <c r="R110" t="n">
-        <v>6626143</v>
+        <v>6626156</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11739,12 +11531,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11759,22 +11556,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129729573</v>
+        <v>129670637</v>
       </c>
       <c r="B111" t="n">
-        <v>92091</v>
+        <v>99118</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11782,21 +11579,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11806,13 +11603,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>651931</v>
+        <v>651703</v>
       </c>
       <c r="R111" t="n">
-        <v>6626008</v>
+        <v>6626171</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11836,12 +11633,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11856,44 +11658,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129729567</v>
+        <v>129670638</v>
       </c>
       <c r="B112" t="n">
-        <v>91638</v>
+        <v>99118</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11903,13 +11705,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>651833</v>
+        <v>651788</v>
       </c>
       <c r="R112" t="n">
-        <v>6626148</v>
+        <v>6626118</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11933,12 +11735,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11953,22 +11760,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129729577</v>
+        <v>129670639</v>
       </c>
       <c r="B113" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12000,13 +11807,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>651837</v>
+        <v>651700</v>
       </c>
       <c r="R113" t="n">
-        <v>6626143</v>
+        <v>6626184</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12030,12 +11837,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12050,44 +11862,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129729576</v>
+        <v>129670640</v>
       </c>
       <c r="B114" t="n">
-        <v>91936</v>
+        <v>99118</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12097,13 +11909,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>651923</v>
+        <v>651783</v>
       </c>
       <c r="R114" t="n">
-        <v>6626013</v>
+        <v>6626130</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12127,12 +11939,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12147,44 +11959,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129729563</v>
+        <v>129670641</v>
       </c>
       <c r="B115" t="n">
-        <v>91638</v>
+        <v>99118</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12194,13 +12006,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>651787</v>
+        <v>651782</v>
       </c>
       <c r="R115" t="n">
-        <v>6626109</v>
+        <v>6626159</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12224,12 +12036,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12244,44 +12056,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129729565</v>
+        <v>129717005</v>
       </c>
       <c r="B116" t="n">
-        <v>91638</v>
+        <v>99118</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12291,13 +12103,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>651830</v>
+        <v>651874</v>
       </c>
       <c r="R116" t="n">
-        <v>6626219</v>
+        <v>6626042</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12341,60 +12153,69 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129729575</v>
+        <v>129717884</v>
       </c>
       <c r="B117" t="n">
-        <v>91936</v>
+        <v>99118</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651890</v>
+        <v>651824</v>
       </c>
       <c r="R117" t="n">
-        <v>6626043</v>
+        <v>6626153</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12438,22 +12259,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129729570</v>
+        <v>129717904</v>
       </c>
       <c r="B118" t="n">
-        <v>92091</v>
+        <v>99118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12461,34 +12282,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björklunda, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651833</v>
+        <v>651836</v>
       </c>
       <c r="R118" t="n">
-        <v>6626152</v>
+        <v>6626167</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12535,22 +12365,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129729571</v>
+        <v>129718176</v>
       </c>
       <c r="B119" t="n">
-        <v>92091</v>
+        <v>99118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12558,21 +12388,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12582,10 +12412,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>651915</v>
+        <v>651797</v>
       </c>
       <c r="R119" t="n">
-        <v>6626012</v>
+        <v>6626076</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12632,44 +12462,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129729566</v>
+        <v>129729577</v>
       </c>
       <c r="B120" t="n">
-        <v>91638</v>
+        <v>99118</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12679,10 +12509,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>651831</v>
+        <v>651837</v>
       </c>
       <c r="R120" t="n">
-        <v>6626182</v>
+        <v>6626143</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12741,32 +12571,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129729564</v>
+        <v>129718056</v>
       </c>
       <c r="B121" t="n">
-        <v>91638</v>
+        <v>106243</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12776,13 +12606,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>651819</v>
+        <v>651824</v>
       </c>
       <c r="R121" t="n">
-        <v>6626182</v>
+        <v>6626153</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12826,44 +12656,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129729568</v>
+        <v>129670629</v>
       </c>
       <c r="B122" t="n">
-        <v>91638</v>
+        <v>97983</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12873,13 +12703,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>651923</v>
+        <v>651815</v>
       </c>
       <c r="R122" t="n">
-        <v>6626013</v>
+        <v>6626081</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12903,12 +12733,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12923,15 +12753,306 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Beke Regelin, Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129670655</v>
+      </c>
+      <c r="B123" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>651655</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6626179</v>
+      </c>
+      <c r="S123" t="n">
+        <v>15</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129670656</v>
+      </c>
+      <c r="B124" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>651804</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6626213</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129717174</v>
+      </c>
+      <c r="B125" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Björklunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>651792</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6626129</v>
+      </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Linnea Ingelsbo, Majken Ekstrand, Jennica Andersson, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46302-2025 artfynd.xlsx
+++ b/artfynd/A 46302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AZ125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88956906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670649</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670626</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670627</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670628</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716753</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716933</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729575</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729576</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670659</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670573</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,6 +1937,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670574</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670575</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,6 +2141,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670576</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2168,6 +2243,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670577</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2265,6 +2345,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2362,6 +2447,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670579</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2459,6 +2549,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670580</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2556,6 +2651,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670581</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2653,6 +2753,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670582</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2750,6 +2855,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670583</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2847,6 +2957,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670584</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2944,6 +3059,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670585</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3041,6 +3161,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716221</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3138,6 +3263,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716568</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3235,6 +3365,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717100</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3332,6 +3467,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717137</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3429,6 +3569,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729563</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3526,6 +3671,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729564</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3623,6 +3773,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729565</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3720,6 +3875,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729566</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3817,6 +3977,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729567</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3914,6 +4079,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729568</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4011,6 +4181,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670603</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4108,6 +4283,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670605</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4205,6 +4385,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670606</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4302,6 +4487,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670607</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4399,6 +4589,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670608</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4496,6 +4691,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670609</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4593,6 +4793,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670610</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4690,6 +4895,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670611</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4787,6 +4997,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670612</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4884,6 +5099,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670613</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4981,6 +5201,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670614</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5078,6 +5303,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670615</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5175,6 +5405,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670616</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5272,6 +5507,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670617</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5369,6 +5609,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670618</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5466,6 +5711,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670619</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5563,6 +5813,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670620</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5660,6 +5915,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670621</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5757,6 +6017,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670622</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5854,6 +6119,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670623</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5951,6 +6221,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670624</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6048,6 +6323,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670625</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6145,6 +6425,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716641</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6242,6 +6527,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716724</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6339,6 +6629,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717108</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6436,6 +6731,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717132</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6533,6 +6833,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129718132</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6630,6 +6935,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729570</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6727,6 +7037,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729571</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6824,6 +7139,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729572</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6921,6 +7241,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670650</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7018,6 +7343,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670651</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7115,6 +7445,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670652</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7212,6 +7547,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670653</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7309,6 +7649,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670654</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7425,6 +7770,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791717</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7541,6 +7891,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791718</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7638,6 +7993,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670630</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7735,6 +8095,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670586</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7832,6 +8197,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670587</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7929,6 +8299,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670588</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8055,6 +8430,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75905513</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8171,6 +8551,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69524489</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8278,6 +8663,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95533022</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8404,6 +8794,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72088659</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8530,6 +8925,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72088660</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8656,6 +9056,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72088661</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8753,6 +9158,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670590</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8850,6 +9260,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670591</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8947,6 +9362,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670592</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9044,6 +9464,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729569</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9141,6 +9566,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670572</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9238,6 +9668,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670657</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9335,6 +9770,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670658</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9433,6 +9873,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729579</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9535,6 +9980,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670598</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9637,6 +10087,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670599</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9739,6 +10194,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670600</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9841,6 +10301,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670601</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9943,6 +10408,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670602</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10040,6 +10510,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716639</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10137,6 +10612,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716946</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10234,6 +10714,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717141</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10351,6 +10836,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75811332</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10453,6 +10943,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670643</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10555,6 +11050,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670644</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10657,6 +11157,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670645</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10759,6 +11264,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670646</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10861,6 +11371,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670647</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10958,6 +11473,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716486</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11055,6 +11575,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717145</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11157,6 +11682,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76009482</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11259,6 +11789,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76009483</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11361,6 +11896,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76009484</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11463,6 +12003,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670635</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11565,6 +12110,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670636</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11667,6 +12217,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670637</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11769,6 +12324,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670638</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11871,6 +12431,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670639</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11968,6 +12533,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670640</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12065,6 +12635,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670641</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12162,6 +12737,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717005</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12268,6 +12848,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717884</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12374,6 +12959,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717904</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12471,6 +13061,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129718176</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12568,6 +13163,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129729577</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12665,6 +13265,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129718056</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12762,6 +13367,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670629</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12859,6 +13469,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670655</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12956,6 +13571,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670656</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13053,8 +13673,139 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717174</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>